--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/SOPORTES DE MEDICION/soportes de medicon.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/SOPORTES DE MEDICION/soportes de medicon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SCRIPT PDFS\SOPORTES DE MEDICION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\SOPORTES DE MEDICION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D45BCFE-4817-4CD7-8378-73356CB0A6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CACBC49-9AEE-4D54-B00C-FF9737164D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Hoja1!$A$1:$I$6</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="769">
   <si>
     <t>NIT</t>
   </si>
@@ -2251,27 +2259,6 @@
     <t>CEDULA PACIENTE</t>
   </si>
   <si>
-    <t>NOMBRE DEL PACIENTE</t>
-  </si>
-  <si>
-    <t>¿Usted recibió atención por parte de la ips MEDICAL SOLUTIONS COLOMBIA SA?</t>
-  </si>
-  <si>
-    <t>¿Teniendo en cuenta la respuesta anterior, por favor elija una de las siguientes opciones indicando por cualespecialidad fue atendido?</t>
-  </si>
-  <si>
-    <t>Teniendo en cuenta su experiencia con la atención brindada por el proveedor, por favor califique en una escala del 1 al 5 la atención recibida en donde 1 es “Malo” y 5 es “Excelente” los siguiente...</t>
-  </si>
-  <si>
-    <t>¿Que tanto se sintio escuchado(a) y comprendido(a) por el profesional que le atendió?</t>
-  </si>
-  <si>
-    <t>¿La información y orientación que recibio fue clara y fácil de entender?</t>
-  </si>
-  <si>
-    <t>¿Qué tan fácil fue agendar la cita?</t>
-  </si>
-  <si>
     <t>contrato</t>
   </si>
   <si>
@@ -2281,32 +2268,89 @@
     <t>Si</t>
   </si>
   <si>
-    <t>Psicología</t>
-  </si>
-  <si>
-    <t>Medicina general</t>
-  </si>
-  <si>
-    <t>WILMAR CARLOS GONZALEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROBERTO CARLOS </t>
-  </si>
-  <si>
-    <t>FELIPE FERNANDEZ</t>
-  </si>
-  <si>
-    <t>LINA URREGO</t>
-  </si>
-  <si>
-    <t>BLANCA  FERNANDEZ</t>
+    <t>mes evaluado</t>
+  </si>
+  <si>
+    <t>febrero 2026</t>
+  </si>
+  <si>
+    <t>NOMBRE DEL PACIENTE </t>
+  </si>
+  <si>
+    <t>El servicio o entrega ya fue realizado</t>
+  </si>
+  <si>
+    <t>LA PRÓTESIS,ORTESIS Y/O INSUMO ENTREGADO CUMPLE CON LAS ESPECIFICACIONES TÉCNICAS DADAS   POR EL MÉDICO TRATANTE</t>
+  </si>
+  <si>
+    <t>¿LA PRÓTESIS, ORTESIS Y/O INSUMO LE HA GENERADO ALGUNA LESIÓN DURANTE SU USO?</t>
+  </si>
+  <si>
+    <t>4. OPORTUNIDAD EN LA ATENCIÓN PRESTADA POR LA IPS</t>
+  </si>
+  <si>
+    <t>5. CALIDAD EN EL SERVICIO PRESTADO POR PARTE DEL PROFESIONAL Y/O PERSONAL ADMINISTRATIVO</t>
+  </si>
+  <si>
+    <t>6. INFRAESTRUCTURA Y DOTACIÓN DE LAS INSTALACIONES DE LA IPS</t>
+  </si>
+  <si>
+    <t>Observaciones, por favor poner una observacion puntual que notifique el usuario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRES FELIPE GONZALEZ MONROY </t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUSTAVO  CHAPARRO BOTELLO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIGUEL ANGEL SANCHEZ GARCIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIO ARNULFO PUERTA GARZON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JABER  ESTRADA ZAPATA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIANELA  PANTALEON PINTO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS ALBERTO MENDEZ TORRES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOELIA  PENCUA SAMBONY </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDWAR ESNEIDER HERNANDEZ MORALES </t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El usuario indica que el 20 de marzo tiene la entrega de los insumos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICTOR ERNESTO ARBOLEDA BERRIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">El usuario indica que aun no le han hecho la entrega de los insumos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILLINGTON  VEGA CESPEDES </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2424,7 +2468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2498,32 +2542,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2830,214 +2868,681 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" style="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="21.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="21.5703125" style="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" style="32" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="46.5703125" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="21.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="133.5" customHeight="1">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
         <v>739</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="28" t="s">
+        <v>745</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>743</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>746</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>747</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>748</v>
+      </c>
+      <c r="G1" s="28" t="s">
+        <v>749</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>750</v>
+      </c>
+      <c r="I1" s="28" t="s">
+        <v>751</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>752</v>
+      </c>
+      <c r="K1" s="30" t="s">
         <v>740</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="L1" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="D1" s="27" t="s">
+    </row>
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="28">
+        <v>1055963451</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>753</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E2" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="E1" s="28" t="s">
-        <v>743</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>744</v>
-      </c>
-      <c r="G1" s="28" t="s">
-        <v>745</v>
-      </c>
-      <c r="H1" s="28" t="s">
-        <v>746</v>
-      </c>
-      <c r="I1" s="27" t="s">
-        <v>747</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>748</v>
-      </c>
-      <c r="K1" s="25"/>
-    </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A2" s="28">
-        <v>1032374386</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>752</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>749</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>750</v>
-      </c>
-      <c r="E2" s="28">
-        <v>5</v>
-      </c>
-      <c r="F2" s="28">
-        <v>5</v>
-      </c>
+      <c r="F2" s="28"/>
       <c r="G2" s="28">
         <v>5</v>
       </c>
       <c r="H2" s="28">
         <v>5</v>
       </c>
-      <c r="I2" s="29" t="s">
-        <v>639</v>
-      </c>
-      <c r="J2" s="29" t="s">
-        <v>640</v>
-      </c>
-      <c r="K2" s="25"/>
-    </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="31.5" customHeight="1">
+      <c r="I2" s="28">
+        <v>4</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K2" t="s">
+        <v>525</v>
+      </c>
+      <c r="L2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="28">
-        <v>1032374387</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>753</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>749</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>751</v>
-      </c>
-      <c r="E3" s="28">
-        <v>5</v>
-      </c>
-      <c r="F3" s="28">
-        <v>5</v>
-      </c>
+        <v>12718993</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>756</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F3" s="28"/>
       <c r="G3" s="28">
         <v>5</v>
       </c>
       <c r="H3" s="28">
         <v>5</v>
       </c>
-      <c r="I3" s="29" t="s">
-        <v>639</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>640</v>
-      </c>
-      <c r="K3" s="25"/>
-    </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" ht="31.5" customHeight="1">
+      <c r="I3" s="28">
+        <v>5</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K3" t="s">
+        <v>525</v>
+      </c>
+      <c r="L3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28">
-        <v>103237438</v>
-      </c>
-      <c r="B4" s="27" t="s">
+        <v>12718993</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>756</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D4" s="28" t="s">
         <v>754</v>
       </c>
-      <c r="C4" s="27" t="s">
-        <v>749</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>750</v>
-      </c>
-      <c r="E4" s="28">
-        <v>5</v>
-      </c>
-      <c r="F4" s="28">
-        <v>5</v>
-      </c>
+      <c r="E4" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F4" s="28"/>
       <c r="G4" s="28">
         <v>5</v>
       </c>
       <c r="H4" s="28">
         <v>5</v>
       </c>
-      <c r="I4" s="29" t="s">
-        <v>639</v>
-      </c>
-      <c r="J4" s="29" t="s">
-        <v>640</v>
-      </c>
-      <c r="K4" s="25"/>
-    </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" ht="19.5" customHeight="1">
+      <c r="I4" s="28">
+        <v>5</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K4" t="s">
+        <v>525</v>
+      </c>
+      <c r="L4" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28">
-        <v>1032374389</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>755</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>749</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>751</v>
-      </c>
-      <c r="E5" s="28">
-        <v>5</v>
-      </c>
-      <c r="F5" s="28">
-        <v>5</v>
-      </c>
+        <v>1006822134</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>757</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F5" s="28"/>
       <c r="G5" s="28">
         <v>5</v>
       </c>
       <c r="H5" s="28">
         <v>5</v>
       </c>
-      <c r="I5" s="29" t="s">
-        <v>639</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>640</v>
-      </c>
-      <c r="K5" s="25"/>
-    </row>
-    <row r="6" spans="1:11" s="1" customFormat="1" ht="31.5" customHeight="1">
+      <c r="I5" s="28">
+        <v>5</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K5" t="s">
+        <v>525</v>
+      </c>
+      <c r="L5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28">
-        <v>1032374390</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>756</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>749</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>751</v>
-      </c>
-      <c r="E6" s="28">
-        <v>5</v>
-      </c>
-      <c r="F6" s="28">
-        <v>5</v>
-      </c>
+        <v>1006822134</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>757</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F6" s="28"/>
       <c r="G6" s="28">
         <v>5</v>
       </c>
       <c r="H6" s="28">
         <v>5</v>
       </c>
-      <c r="I6" s="29" t="s">
-        <v>639</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>640</v>
-      </c>
-      <c r="K6" s="25"/>
+      <c r="I6" s="28">
+        <v>5</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K6" t="s">
+        <v>525</v>
+      </c>
+      <c r="L6" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="28">
+        <v>98603739</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>758</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28">
+        <v>5</v>
+      </c>
+      <c r="H7" s="28">
+        <v>5</v>
+      </c>
+      <c r="I7" s="28">
+        <v>5</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K7" t="s">
+        <v>683</v>
+      </c>
+      <c r="L7" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>98603739</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>758</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28">
+        <v>5</v>
+      </c>
+      <c r="H8" s="28">
+        <v>5</v>
+      </c>
+      <c r="I8" s="28">
+        <v>5</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K8" t="s">
+        <v>683</v>
+      </c>
+      <c r="L8" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
+        <v>71388052</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>759</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28">
+        <v>4</v>
+      </c>
+      <c r="H9" s="28">
+        <v>4</v>
+      </c>
+      <c r="I9" s="28">
+        <v>4</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K9" t="s">
+        <v>683</v>
+      </c>
+      <c r="L9" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
+        <v>71388052</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>759</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28">
+        <v>4</v>
+      </c>
+      <c r="H10" s="28">
+        <v>4</v>
+      </c>
+      <c r="I10" s="28">
+        <v>4</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K10" t="s">
+        <v>683</v>
+      </c>
+      <c r="L10" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
+        <v>60360054</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>760</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28">
+        <v>5</v>
+      </c>
+      <c r="H11" s="28">
+        <v>5</v>
+      </c>
+      <c r="I11" s="28">
+        <v>5</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K11" t="s">
+        <v>583</v>
+      </c>
+      <c r="L11" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
+        <v>60360054</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>760</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28">
+        <v>5</v>
+      </c>
+      <c r="H12" s="28">
+        <v>5</v>
+      </c>
+      <c r="I12" s="28">
+        <v>5</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K12" t="s">
+        <v>583</v>
+      </c>
+      <c r="L12" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
+        <v>60360054</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>760</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28">
+        <v>5</v>
+      </c>
+      <c r="H13" s="28">
+        <v>5</v>
+      </c>
+      <c r="I13" s="28">
+        <v>5</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K13" t="s">
+        <v>583</v>
+      </c>
+      <c r="L13" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>92496452</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>761</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28">
+        <v>5</v>
+      </c>
+      <c r="H14" s="28">
+        <v>5</v>
+      </c>
+      <c r="I14" s="28">
+        <v>5</v>
+      </c>
+      <c r="J14" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K14" t="s">
+        <v>583</v>
+      </c>
+      <c r="L14" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
+        <v>98603739</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>758</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28">
+        <v>5</v>
+      </c>
+      <c r="H15" s="28">
+        <v>5</v>
+      </c>
+      <c r="I15" s="28">
+        <v>5</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K15" t="s">
+        <v>683</v>
+      </c>
+      <c r="L15" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>25480654</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>762</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28">
+        <v>5</v>
+      </c>
+      <c r="H16" s="28">
+        <v>5</v>
+      </c>
+      <c r="I16" s="28">
+        <v>5</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="K16" t="s">
+        <v>339</v>
+      </c>
+      <c r="L16" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
+        <v>1032367507</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>763</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>764</v>
+      </c>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28" t="s">
+        <v>765</v>
+      </c>
+      <c r="K17" t="s">
+        <v>339</v>
+      </c>
+      <c r="L17" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
+        <v>1102800990</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>766</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>764</v>
+      </c>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28" t="s">
+        <v>767</v>
+      </c>
+      <c r="K18" t="s">
+        <v>339</v>
+      </c>
+      <c r="L18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>5978935</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>768</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>764</v>
+      </c>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28" t="s">
+        <v>767</v>
+      </c>
+      <c r="K19" t="s">
+        <v>339</v>
+      </c>
+      <c r="L19" t="s">
+        <v>340</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3050,14 +3555,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C371"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="22" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" style="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5703125" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3068,7 +3573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>900220590</v>
       </c>
@@ -3079,7 +3584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>891855847</v>
       </c>
@@ -3090,7 +3595,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1">
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>890801026</v>
       </c>
@@ -3101,7 +3606,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1">
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>41471570</v>
       </c>
@@ -3112,7 +3617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>900352592</v>
       </c>
@@ -3123,7 +3628,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18.75" customHeight="1">
+    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>900385628</v>
       </c>
@@ -3134,7 +3639,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>832010240</v>
       </c>
@@ -3145,7 +3650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>899999161</v>
       </c>
@@ -3156,7 +3661,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+    <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>900119357</v>
       </c>
@@ -3167,7 +3672,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18.75" customHeight="1">
+    <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>830114167</v>
       </c>
@@ -3178,7 +3683,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18.75" customHeight="1">
+    <row r="12" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>79781903</v>
       </c>
@@ -3189,7 +3694,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18.75" customHeight="1">
+    <row r="13" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>891190011</v>
       </c>
@@ -3200,7 +3705,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+    <row r="14" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>891401643</v>
       </c>
@@ -3211,7 +3716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+    <row r="15" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>800174851</v>
       </c>
@@ -3222,7 +3727,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+    <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>800193490</v>
       </c>
@@ -3233,7 +3738,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18.75" customHeight="1">
+    <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>900420664</v>
       </c>
@@ -3244,7 +3749,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18.75" customHeight="1">
+    <row r="18" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>80041361</v>
       </c>
@@ -3255,7 +3760,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+    <row r="19" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>801001406</v>
       </c>
@@ -3266,7 +3771,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18.75" customHeight="1">
+    <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>860053761</v>
       </c>
@@ -3277,7 +3782,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18.75" customHeight="1">
+    <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>19274667</v>
       </c>
@@ -3288,7 +3793,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18.75" customHeight="1">
+    <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>890701718</v>
       </c>
@@ -3299,7 +3804,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18.75" customHeight="1">
+    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>800209891</v>
       </c>
@@ -3310,7 +3815,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>810003245</v>
       </c>
@@ -3321,7 +3826,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18.75" customHeight="1">
+    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>900649963</v>
       </c>
@@ -3332,7 +3837,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18.75" customHeight="1">
+    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>52794734</v>
       </c>
@@ -3343,7 +3848,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18.75" customHeight="1">
+    <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>800231215</v>
       </c>
@@ -3354,7 +3859,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18.75" customHeight="1">
+    <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>900691301</v>
       </c>
@@ -3365,7 +3870,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18.75" customHeight="1">
+    <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>800006509</v>
       </c>
@@ -3376,7 +3881,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18.75" customHeight="1">
+    <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>900193162</v>
       </c>
@@ -3387,7 +3892,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18.75" customHeight="1">
+    <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>890807591</v>
       </c>
@@ -3398,7 +3903,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18.75" customHeight="1">
+    <row r="32" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>900144408</v>
       </c>
@@ -3409,7 +3914,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18.75" customHeight="1">
+    <row r="33" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>860010783</v>
       </c>
@@ -3420,7 +3925,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18.75" customHeight="1">
+    <row r="34" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>900691056</v>
       </c>
@@ -3431,7 +3936,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18.75" customHeight="1">
+    <row r="35" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>901060053</v>
       </c>
@@ -3442,7 +3947,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18.75" customHeight="1">
+    <row r="36" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>900215983</v>
       </c>
@@ -3453,7 +3958,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18.75" customHeight="1">
+    <row r="37" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>900129308</v>
       </c>
@@ -3464,7 +3969,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18.75" customHeight="1">
+    <row r="38" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>892000264</v>
       </c>
@@ -3475,7 +3980,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18.75" customHeight="1">
+    <row r="39" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>800218979</v>
       </c>
@@ -3486,7 +3991,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18.75" customHeight="1">
+    <row r="40" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>891855029</v>
       </c>
@@ -3497,7 +4002,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18.75" customHeight="1">
+    <row r="41" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>900142282</v>
       </c>
@@ -3508,7 +4013,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18.75" customHeight="1">
+    <row r="42" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>860006745</v>
       </c>
@@ -3519,7 +4024,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18.75" customHeight="1">
+    <row r="43" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>890702369</v>
       </c>
@@ -3530,7 +4035,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18.75" customHeight="1">
+    <row r="44" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>800017308</v>
       </c>
@@ -3541,7 +4046,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18.75" customHeight="1">
+    <row r="45" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <v>890000992</v>
       </c>
@@ -3552,7 +4057,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18.75" customHeight="1">
+    <row r="46" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
         <v>830511298</v>
       </c>
@@ -3563,7 +4068,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18.75" customHeight="1">
+    <row r="47" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>832001411</v>
       </c>
@@ -3574,7 +4079,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18.75" customHeight="1">
+    <row r="48" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>809010893</v>
       </c>
@@ -3585,7 +4090,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18.75" customHeight="1">
+    <row r="49" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>900714297</v>
       </c>
@@ -3596,7 +4101,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18.75" customHeight="1">
+    <row r="50" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12">
         <v>900034131</v>
       </c>
@@ -3607,7 +4112,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18.75" customHeight="1">
+    <row r="51" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>860015536</v>
       </c>
@@ -3618,7 +4123,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18.75" customHeight="1">
+    <row r="52" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>900211460</v>
       </c>
@@ -3629,7 +4134,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18.75" customHeight="1">
+    <row r="53" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
         <v>860090566</v>
       </c>
@@ -3640,7 +4145,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18.75" customHeight="1">
+    <row r="54" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <v>891800335</v>
       </c>
@@ -3651,7 +4156,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18.75" customHeight="1">
+    <row r="55" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <v>900454994</v>
       </c>
@@ -3662,7 +4167,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18.75" customHeight="1">
+    <row r="56" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>820003431</v>
       </c>
@@ -3673,7 +4178,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18.75" customHeight="1">
+    <row r="57" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
         <v>830070284</v>
       </c>
@@ -3684,7 +4189,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18.75" customHeight="1">
+    <row r="58" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
         <v>890703630</v>
       </c>
@@ -3695,7 +4200,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18.75" customHeight="1">
+    <row r="59" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
         <v>800032418</v>
       </c>
@@ -3706,7 +4211,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18.75" customHeight="1">
+    <row r="60" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <v>900211477</v>
       </c>
@@ -3717,7 +4222,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18.75" customHeight="1">
+    <row r="61" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
         <v>900004894</v>
       </c>
@@ -3728,7 +4233,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18.75" customHeight="1">
+    <row r="62" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
         <v>901061505</v>
       </c>
@@ -3739,7 +4244,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18.75" customHeight="1">
+    <row r="63" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
         <v>901622460</v>
       </c>
@@ -3750,7 +4255,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18.75" customHeight="1">
+    <row r="64" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <v>828000386</v>
       </c>
@@ -3761,7 +4266,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18.75" customHeight="1">
+    <row r="65" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
         <v>891200679</v>
       </c>
@@ -3772,7 +4277,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18.75" customHeight="1">
+    <row r="66" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <v>79451044</v>
       </c>
@@ -3783,7 +4288,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18.75" customHeight="1">
+    <row r="67" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
         <v>860035992</v>
       </c>
@@ -3794,7 +4299,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18.75" customHeight="1">
+    <row r="68" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <v>900217648</v>
       </c>
@@ -3805,7 +4310,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18.75" customHeight="1">
+    <row r="69" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
         <v>900130936</v>
       </c>
@@ -3816,7 +4321,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18.75" customHeight="1">
+    <row r="70" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
         <v>890805923</v>
       </c>
@@ -3827,7 +4332,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18.75" customHeight="1">
+    <row r="71" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <v>900470918</v>
       </c>
@@ -3838,7 +4343,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18.75" customHeight="1">
+    <row r="72" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
         <v>900236728</v>
       </c>
@@ -3849,7 +4354,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18.75" customHeight="1">
+    <row r="73" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
         <v>844004197</v>
       </c>
@@ -3860,7 +4365,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18.75" customHeight="1">
+    <row r="74" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>900175697</v>
       </c>
@@ -3871,7 +4376,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18.75" customHeight="1">
+    <row r="75" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
         <v>820003850</v>
       </c>
@@ -3882,7 +4387,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18.75" customHeight="1">
+    <row r="76" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
         <v>830073010</v>
       </c>
@@ -3893,7 +4398,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18.75" customHeight="1">
+    <row r="77" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
         <v>860015888</v>
       </c>
@@ -3904,7 +4409,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18.75" customHeight="1">
+    <row r="78" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7">
         <v>900210981</v>
       </c>
@@ -3915,7 +4420,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18.75" customHeight="1">
+    <row r="79" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7">
         <v>901011962</v>
       </c>
@@ -3926,7 +4431,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18.75" customHeight="1">
+    <row r="80" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
         <v>900118059</v>
       </c>
@@ -3937,7 +4442,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18.75" customHeight="1">
+    <row r="81" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
         <v>901447598</v>
       </c>
@@ -3948,7 +4453,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18.75" customHeight="1">
+    <row r="82" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
         <v>901163080</v>
       </c>
@@ -3959,7 +4464,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18.75" customHeight="1">
+    <row r="83" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7">
         <v>900559103</v>
       </c>
@@ -3970,7 +4475,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="18.75" customHeight="1">
+    <row r="84" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
         <v>891480000</v>
       </c>
@@ -3981,7 +4486,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18.75" customHeight="1">
+    <row r="85" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7">
         <v>900971006</v>
       </c>
@@ -3992,7 +4497,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18.75" customHeight="1">
+    <row r="86" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7">
         <v>900420751</v>
       </c>
@@ -4003,7 +4508,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="18.75" customHeight="1">
+    <row r="87" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7">
         <v>901102510</v>
       </c>
@@ -4014,7 +4519,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="18.75" customHeight="1">
+    <row r="88" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
         <v>800044967</v>
       </c>
@@ -4025,7 +4530,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="18.75" customHeight="1">
+    <row r="89" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7">
         <v>832000744</v>
       </c>
@@ -4036,7 +4541,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="18.75" customHeight="1">
+    <row r="90" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
         <v>901631369</v>
       </c>
@@ -4047,7 +4552,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="18.75" customHeight="1">
+    <row r="91" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="7">
         <v>830010671</v>
       </c>
@@ -4058,7 +4563,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18.75" customHeight="1">
+    <row r="92" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7">
         <v>900769055</v>
       </c>
@@ -4069,7 +4574,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18.75" customHeight="1">
+    <row r="93" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="7">
         <v>820001181</v>
       </c>
@@ -4080,7 +4585,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18.75" customHeight="1">
+    <row r="94" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7">
         <v>891201578</v>
       </c>
@@ -4091,7 +4596,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18.75" customHeight="1">
+    <row r="95" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="7">
         <v>901011387</v>
       </c>
@@ -4102,7 +4607,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="18.75" customHeight="1">
+    <row r="96" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7">
         <v>891480036</v>
       </c>
@@ -4113,7 +4618,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18.75" customHeight="1">
+    <row r="97" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7">
         <v>900491982</v>
       </c>
@@ -4124,7 +4629,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18.75" customHeight="1">
+    <row r="98" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
         <v>832003167</v>
       </c>
@@ -4135,7 +4640,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="18.75" customHeight="1">
+    <row r="99" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="7">
         <v>846000253</v>
       </c>
@@ -4146,7 +4651,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="18.75" customHeight="1">
+    <row r="100" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7">
         <v>900138555</v>
       </c>
@@ -4157,7 +4662,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="18.75" customHeight="1">
+    <row r="101" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="7">
         <v>826002694</v>
       </c>
@@ -4168,7 +4673,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="18.75" customHeight="1">
+    <row r="102" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="7">
         <v>830027158</v>
       </c>
@@ -4179,7 +4684,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="18.75" customHeight="1">
+    <row r="103" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="7">
         <v>900132642</v>
       </c>
@@ -4190,7 +4695,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="18.75" customHeight="1">
+    <row r="104" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="7">
         <v>901182731</v>
       </c>
@@ -4201,7 +4706,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="18.75" customHeight="1">
+    <row r="105" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="7">
         <v>900415353</v>
       </c>
@@ -4212,7 +4717,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="18.75" customHeight="1">
+    <row r="106" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
         <v>901386786</v>
       </c>
@@ -4223,7 +4728,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="18.75" customHeight="1">
+    <row r="107" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="7">
         <v>890701353</v>
       </c>
@@ -4234,7 +4739,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="18.75" customHeight="1">
+    <row r="108" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="7">
         <v>890706833</v>
       </c>
@@ -4245,7 +4750,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="18.75" customHeight="1">
+    <row r="109" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="7">
         <v>809002913</v>
       </c>
@@ -4256,7 +4761,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="18.75" customHeight="1">
+    <row r="110" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="7">
         <v>900958115</v>
       </c>
@@ -4267,7 +4772,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="18.75" customHeight="1">
+    <row r="111" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="7">
         <v>900876789</v>
       </c>
@@ -4278,7 +4783,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="18.75" customHeight="1">
+    <row r="112" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="7">
         <v>800082446</v>
       </c>
@@ -4289,7 +4794,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="18.75" customHeight="1">
+    <row r="113" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="7">
         <v>816007055</v>
       </c>
@@ -4300,7 +4805,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="18.75" customHeight="1">
+    <row r="114" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7">
         <v>900912423</v>
       </c>
@@ -4311,7 +4816,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="18.75" customHeight="1">
+    <row r="115" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="7">
         <v>900826841</v>
       </c>
@@ -4322,7 +4827,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="18.75" customHeight="1">
+    <row r="116" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
         <v>901091739</v>
       </c>
@@ -4333,7 +4838,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="18.75" customHeight="1">
+    <row r="117" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="7">
         <v>900215698</v>
       </c>
@@ -4344,7 +4849,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="18.75" customHeight="1">
+    <row r="118" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="7">
         <v>901392384</v>
       </c>
@@ -4355,7 +4860,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="18.75" customHeight="1">
+    <row r="119" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="7">
         <v>828000073</v>
       </c>
@@ -4366,7 +4871,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="18.75" customHeight="1">
+    <row r="120" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="7">
         <v>901352353</v>
       </c>
@@ -4377,7 +4882,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="18.75" customHeight="1">
+    <row r="121" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="7">
         <v>900999027</v>
       </c>
@@ -4388,7 +4893,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="18.75" customHeight="1">
+    <row r="122" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="7">
         <v>800074996</v>
       </c>
@@ -4399,7 +4904,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="18.75" customHeight="1">
+    <row r="123" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="7">
         <v>901680794</v>
       </c>
@@ -4410,7 +4915,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="18.75" customHeight="1">
+    <row r="124" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="7">
         <v>900477525</v>
       </c>
@@ -4421,7 +4926,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="18.75" customHeight="1">
+    <row r="125" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="7">
         <v>900532173</v>
       </c>
@@ -4432,7 +4937,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="18.75" customHeight="1">
+    <row r="126" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="7">
         <v>900702090</v>
       </c>
@@ -4443,7 +4948,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="18.75" customHeight="1">
+    <row r="127" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="7">
         <v>890701033</v>
       </c>
@@ -4454,7 +4959,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="18.75" customHeight="1">
+    <row r="128" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="7">
         <v>900800269</v>
       </c>
@@ -4465,7 +4970,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="18.75" customHeight="1">
+    <row r="129" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="7">
         <v>901606280</v>
       </c>
@@ -4476,7 +4981,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="18.75" customHeight="1">
+    <row r="130" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="7">
         <v>900342271</v>
       </c>
@@ -4487,7 +4992,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="18.75" customHeight="1">
+    <row r="131" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="7">
         <v>800162035</v>
       </c>
@@ -4498,7 +5003,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="18.75" customHeight="1">
+    <row r="132" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="7">
         <v>800146679</v>
       </c>
@@ -4509,7 +5014,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="18.75" customHeight="1">
+    <row r="133" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="7">
         <v>901470470</v>
       </c>
@@ -4520,7 +5025,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="18.75" customHeight="1">
+    <row r="134" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="15">
         <v>890701010</v>
       </c>
@@ -4531,7 +5036,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="18.75" customHeight="1">
+    <row r="135" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="7">
         <v>800234796</v>
       </c>
@@ -4542,7 +5047,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="18.75" customHeight="1">
+    <row r="136" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="7">
         <v>900959048</v>
       </c>
@@ -4553,7 +5058,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="18.75" customHeight="1">
+    <row r="137" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="7">
         <v>890801758</v>
       </c>
@@ -4564,7 +5069,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="18.75" customHeight="1">
+    <row r="138" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="7">
         <v>805019730</v>
       </c>
@@ -4575,7 +5080,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="18.75" customHeight="1">
+    <row r="139" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="7">
         <v>820002596</v>
       </c>
@@ -4586,7 +5091,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="18.75" customHeight="1">
+    <row r="140" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="7">
         <v>900373445</v>
       </c>
@@ -4597,7 +5102,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="18.75" customHeight="1">
+    <row r="141" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="7">
         <v>900301238</v>
       </c>
@@ -4608,7 +5113,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="18.75" customHeight="1">
+    <row r="142" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="7">
         <v>900296178</v>
       </c>
@@ -4619,7 +5124,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="18.75" customHeight="1">
+    <row r="143" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="7">
         <v>900341409</v>
       </c>
@@ -4630,7 +5135,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="18.75" customHeight="1">
+    <row r="144" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="7">
         <v>813001952</v>
       </c>
@@ -4641,7 +5146,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="18.75" customHeight="1">
+    <row r="145" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="7">
         <v>800227072</v>
       </c>
@@ -4652,7 +5157,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="18.75" customHeight="1">
+    <row r="146" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="7">
         <v>800036400</v>
       </c>
@@ -4663,7 +5168,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="18.75" customHeight="1">
+    <row r="147" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="7">
         <v>809009066</v>
       </c>
@@ -4674,7 +5179,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="18.75" customHeight="1">
+    <row r="148" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="7">
         <v>900563603</v>
       </c>
@@ -4685,7 +5190,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="18.75" customHeight="1">
+    <row r="149" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="7">
         <v>890001006</v>
       </c>
@@ -4696,7 +5201,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="18.75" customHeight="1">
+    <row r="150" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="7">
         <v>901119103</v>
       </c>
@@ -4707,7 +5212,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="18.75" customHeight="1">
+    <row r="151" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="7">
         <v>900240354</v>
       </c>
@@ -4718,7 +5223,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="18.75" customHeight="1">
+    <row r="152" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="7">
         <v>900504265</v>
       </c>
@@ -4729,7 +5234,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="18.75" customHeight="1">
+    <row r="153" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="7">
         <v>813002940</v>
       </c>
@@ -4740,7 +5245,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="18.75" customHeight="1">
+    <row r="154" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="7">
         <v>830027578</v>
       </c>
@@ -4751,7 +5256,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="18.75" customHeight="1">
+    <row r="155" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="7">
         <v>822006595</v>
       </c>
@@ -4762,7 +5267,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="18.75" customHeight="1">
+    <row r="156" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="7">
         <v>900510844</v>
       </c>
@@ -4773,7 +5278,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="18.75" customHeight="1">
+    <row r="157" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="7">
         <v>900573146</v>
       </c>
@@ -4784,7 +5289,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="18.75" customHeight="1">
+    <row r="158" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="7">
         <v>890701459</v>
       </c>
@@ -4795,7 +5300,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="18.75" customHeight="1">
+    <row r="159" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="7">
         <v>900355585</v>
       </c>
@@ -4806,7 +5311,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="18.75" customHeight="1">
+    <row r="160" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="7">
         <v>860039726</v>
       </c>
@@ -4817,7 +5322,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="18.75" customHeight="1">
+    <row r="161" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="7">
         <v>800201496</v>
       </c>
@@ -4828,7 +5333,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="18.75" customHeight="1">
+    <row r="162" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="7">
         <v>891800395</v>
       </c>
@@ -4839,7 +5344,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="18.75" customHeight="1">
+    <row r="163" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="7">
         <v>900103925</v>
       </c>
@@ -4850,7 +5355,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="18.75" customHeight="1">
+    <row r="164" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="7">
         <v>800254850</v>
       </c>
@@ -4861,7 +5366,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="18.75" customHeight="1">
+    <row r="165" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="7">
         <v>830514240</v>
       </c>
@@ -4872,7 +5377,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="18.75" customHeight="1">
+    <row r="166" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="7">
         <v>900966154</v>
       </c>
@@ -4883,7 +5388,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="18.75" customHeight="1">
+    <row r="167" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="7">
         <v>892000501</v>
       </c>
@@ -4894,7 +5399,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="18.75" customHeight="1">
+    <row r="168" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="7">
         <v>860011298</v>
       </c>
@@ -4905,7 +5410,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="18.75" customHeight="1">
+    <row r="169" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="7">
         <v>820005389</v>
       </c>
@@ -4916,7 +5421,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="18.75" customHeight="1">
+    <row r="170" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="7">
         <v>830039229</v>
       </c>
@@ -4927,7 +5432,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="18.75" customHeight="1">
+    <row r="171" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="7">
         <v>900448997</v>
       </c>
@@ -4938,7 +5443,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="18.75" customHeight="1">
+    <row r="172" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="7">
         <v>900716387</v>
       </c>
@@ -4949,7 +5454,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="18.75" customHeight="1">
+    <row r="173" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="7">
         <v>901495569</v>
       </c>
@@ -4960,7 +5465,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="18.75" customHeight="1">
+    <row r="174" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="7">
         <v>900578105</v>
       </c>
@@ -4971,7 +5476,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="18.75" customHeight="1">
+    <row r="175" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="7">
         <v>79785257</v>
       </c>
@@ -4982,7 +5487,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="18.75" customHeight="1">
+    <row r="176" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="7">
         <v>80727490</v>
       </c>
@@ -4993,7 +5498,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="18.75" customHeight="1">
+    <row r="177" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="7">
         <v>809006003</v>
       </c>
@@ -5004,7 +5509,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="18.75" customHeight="1">
+    <row r="178" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="7">
         <v>832000464</v>
       </c>
@@ -5015,7 +5520,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="18.75" customHeight="1">
+    <row r="179" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="7">
         <v>900267104</v>
       </c>
@@ -5026,7 +5531,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="18.75" customHeight="1">
+    <row r="180" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="7">
         <v>830141132</v>
       </c>
@@ -5037,7 +5542,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="18.75" customHeight="1">
+    <row r="181" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="7">
         <v>890000600</v>
       </c>
@@ -5048,7 +5553,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="18.75" customHeight="1">
+    <row r="182" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="7">
         <v>899999063</v>
       </c>
@@ -5059,7 +5564,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="18.75" customHeight="1">
+    <row r="183" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="7">
         <v>890801517</v>
       </c>
@@ -5070,7 +5575,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="18.75" customHeight="1">
+    <row r="184" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="7">
         <v>900482620</v>
       </c>
@@ -5081,7 +5586,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="18.75" customHeight="1">
+    <row r="185" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="7">
         <v>891856161</v>
       </c>
@@ -5092,7 +5597,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="18.75" customHeight="1">
+    <row r="186" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="7">
         <v>892000458</v>
       </c>
@@ -5103,7 +5608,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="18.75" customHeight="1">
+    <row r="187" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="7">
         <v>900451858</v>
       </c>
@@ -5114,7 +5619,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="18.75" customHeight="1">
+    <row r="188" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="7">
         <v>800219192</v>
       </c>
@@ -5125,7 +5630,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="18.75" customHeight="1">
+    <row r="189" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="7">
         <v>832002436</v>
       </c>
@@ -5136,7 +5641,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="18.75" customHeight="1">
+    <row r="190" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="7">
         <v>832001966</v>
       </c>
@@ -5147,7 +5652,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="18.75" customHeight="1">
+    <row r="191" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="7">
         <v>900841132</v>
       </c>
@@ -5158,7 +5663,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="18.75" customHeight="1">
+    <row r="192" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="7">
         <v>900588182</v>
       </c>
@@ -5169,7 +5674,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="18.75" customHeight="1">
+    <row r="193" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="7">
         <v>826002144</v>
       </c>
@@ -5180,7 +5685,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="18.75" customHeight="1">
+    <row r="194" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="7">
         <v>846003067</v>
       </c>
@@ -5191,7 +5696,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="18.75" customHeight="1">
+    <row r="195" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="7">
         <v>900241765</v>
       </c>
@@ -5202,7 +5707,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="18.75" customHeight="1">
+    <row r="196" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="7">
         <v>900521595</v>
       </c>
@@ -5213,7 +5718,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="18.75" customHeight="1">
+    <row r="197" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="7">
         <v>816003270</v>
       </c>
@@ -5224,7 +5729,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="18.75" customHeight="1">
+    <row r="198" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="7">
         <v>890704555</v>
       </c>
@@ -5235,7 +5740,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="18.75" customHeight="1">
+    <row r="199" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="7">
         <v>900232301</v>
       </c>
@@ -5246,7 +5751,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="18.75" customHeight="1">
+    <row r="200" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="7">
         <v>830143831</v>
       </c>
@@ -5257,7 +5762,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="18.75" customHeight="1">
+    <row r="201" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="7">
         <v>800099652</v>
       </c>
@@ -5268,7 +5773,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="18.75" customHeight="1">
+    <row r="202" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="7">
         <v>891800570</v>
       </c>
@@ -5279,7 +5784,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="18.75" customHeight="1">
+    <row r="203" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="7">
         <v>892099421</v>
       </c>
@@ -5290,7 +5795,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="18.75" customHeight="1">
+    <row r="204" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="7">
         <v>900438068</v>
       </c>
@@ -5301,7 +5806,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="18.75" customHeight="1">
+    <row r="205" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="7">
         <v>860037950</v>
       </c>
@@ -5312,7 +5817,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="18.75" customHeight="1">
+    <row r="206" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="7">
         <v>890702408</v>
       </c>
@@ -5323,7 +5828,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="18.75" customHeight="1">
+    <row r="207" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="7">
         <v>1015392989</v>
       </c>
@@ -5334,7 +5839,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="18.75" customHeight="1">
+    <row r="208" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="7">
         <v>899999032</v>
       </c>
@@ -5345,7 +5850,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="18.75" customHeight="1">
+    <row r="209" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="7">
         <v>881862576</v>
       </c>
@@ -5356,7 +5861,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="18.75" customHeight="1">
+    <row r="210" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="7">
         <v>52411325</v>
       </c>
@@ -5367,7 +5872,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="18.75" customHeight="1">
+    <row r="211" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="7">
         <v>901544725</v>
       </c>
@@ -5378,7 +5883,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="18.75" customHeight="1">
+    <row r="212" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="7">
         <v>830009112</v>
       </c>
@@ -5389,7 +5894,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="18.75" customHeight="1">
+    <row r="213" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="7">
         <v>900614302</v>
       </c>
@@ -5400,7 +5905,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="18.75" customHeight="1">
+    <row r="214" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="7">
         <v>900055393</v>
       </c>
@@ -5411,7 +5916,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="18.75" customHeight="1">
+    <row r="215" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="7">
         <v>1020720272</v>
       </c>
@@ -5422,7 +5927,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="18.75" customHeight="1">
+    <row r="216" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="7">
         <v>844001355</v>
       </c>
@@ -5433,7 +5938,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="18.75" customHeight="1">
+    <row r="217" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="7">
         <v>801001440</v>
       </c>
@@ -5444,7 +5949,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="18.75" customHeight="1">
+    <row r="218" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="7">
         <v>800037021</v>
       </c>
@@ -5455,7 +5960,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="18.75" customHeight="1">
+    <row r="219" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="7">
         <v>19457462</v>
       </c>
@@ -5466,7 +5971,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="18.75" customHeight="1">
+    <row r="220" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="7">
         <v>890802356</v>
       </c>
@@ -5477,7 +5982,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="18.75" customHeight="1">
+    <row r="221" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="7">
         <v>890801719</v>
       </c>
@@ -5488,7 +5993,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="18.75" customHeight="1">
+    <row r="222" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="7">
         <v>901408039</v>
       </c>
@@ -5499,7 +6004,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="18.75" customHeight="1">
+    <row r="223" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="7">
         <v>860002541</v>
       </c>
@@ -5510,7 +6015,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="18.75" customHeight="1">
+    <row r="224" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="7">
         <v>900342064</v>
       </c>
@@ -5521,7 +6026,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="18.75" customHeight="1">
+    <row r="225" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="7">
         <v>890801035</v>
       </c>
@@ -5532,7 +6037,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="18.75" customHeight="1">
+    <row r="226" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="7">
         <v>802011972</v>
       </c>
@@ -5543,7 +6048,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="18.75" customHeight="1">
+    <row r="227" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="7">
         <v>900407200</v>
       </c>
@@ -5554,7 +6059,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="18.75" customHeight="1">
+    <row r="228" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="7">
         <v>813010145</v>
       </c>
@@ -5565,7 +6070,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="18.75" customHeight="1">
+    <row r="229" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="7">
         <v>860070301</v>
       </c>
@@ -5576,7 +6081,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="18.75" customHeight="1">
+    <row r="230" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="7">
         <v>890700666</v>
       </c>
@@ -5587,7 +6092,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="18.75" customHeight="1">
+    <row r="231" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="7">
         <v>900308007</v>
       </c>
@@ -5598,7 +6103,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="18.75" customHeight="1">
+    <row r="232" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="7">
         <v>891856372</v>
       </c>
@@ -5609,7 +6114,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="18.75" customHeight="1">
+    <row r="233" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="7">
         <v>800065396</v>
       </c>
@@ -5620,7 +6125,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="18.75" customHeight="1">
+    <row r="234" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="7">
         <v>901223046</v>
       </c>
@@ -5631,7 +6136,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="18.75" customHeight="1">
+    <row r="235" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="7">
         <v>809010402</v>
       </c>
@@ -5642,7 +6147,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="18.75" customHeight="1">
+    <row r="236" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="7">
         <v>891800231</v>
       </c>
@@ -5653,7 +6158,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="18.75" customHeight="1">
+    <row r="237" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="7">
         <v>800119574</v>
       </c>
@@ -5664,7 +6169,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="18.75" customHeight="1">
+    <row r="238" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="7">
         <v>80170827</v>
       </c>
@@ -5675,7 +6180,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="18.75" customHeight="1">
+    <row r="239" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="7">
         <v>10286175</v>
       </c>
@@ -5686,7 +6191,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="18.75" customHeight="1">
+    <row r="240" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="7">
         <v>900454188</v>
       </c>
@@ -5697,7 +6202,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="18.75" customHeight="1">
+    <row r="241" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="7">
         <v>900057926</v>
       </c>
@@ -5708,7 +6213,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="18.75" customHeight="1">
+    <row r="242" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="7">
         <v>844001911</v>
       </c>
@@ -5719,7 +6224,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="18.75" customHeight="1">
+    <row r="243" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="7">
         <v>900526144</v>
       </c>
@@ -5730,7 +6235,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="18.75" customHeight="1">
+    <row r="244" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="7">
         <v>900828394</v>
       </c>
@@ -5741,7 +6246,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="18.75" customHeight="1">
+    <row r="245" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="7">
         <v>844001287</v>
       </c>
@@ -5752,7 +6257,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="18.75" customHeight="1">
+    <row r="246" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="7">
         <v>900431131</v>
       </c>
@@ -5763,7 +6268,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="18.75" customHeight="1">
+    <row r="247" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="7">
         <v>800037979</v>
       </c>
@@ -5774,7 +6279,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="18.75" customHeight="1">
+    <row r="248" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="7">
         <v>890601210</v>
       </c>
@@ -5785,7 +6290,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="18.75" customHeight="1">
+    <row r="249" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="7">
         <v>801001969</v>
       </c>
@@ -5796,7 +6301,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="18.75" customHeight="1">
+    <row r="250" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="7">
         <v>890801944</v>
       </c>
@@ -5807,7 +6312,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="18.75" customHeight="1">
+    <row r="251" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="7">
         <v>19419315</v>
       </c>
@@ -5818,7 +6323,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="18.75" customHeight="1">
+    <row r="252" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="7">
         <v>900371613</v>
       </c>
@@ -5829,7 +6334,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="18.75" customHeight="1">
+    <row r="253" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="7">
         <v>860015905</v>
       </c>
@@ -5840,7 +6345,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="18.75" customHeight="1">
+    <row r="254" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="7">
         <v>900488920</v>
       </c>
@@ -5851,7 +6356,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="18.75" customHeight="1">
+    <row r="255" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="7">
         <v>810000913</v>
       </c>
@@ -5862,7 +6367,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="18.75" customHeight="1">
+    <row r="256" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="7">
         <v>900471504</v>
       </c>
@@ -5873,7 +6378,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="18.75" customHeight="1">
+    <row r="257" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="7">
         <v>844003225</v>
       </c>
@@ -5884,7 +6389,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="18.75" customHeight="1">
+    <row r="258" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="7">
         <v>830075393</v>
       </c>
@@ -5895,7 +6400,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="18.75" customHeight="1">
+    <row r="259" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="7">
         <v>900058218</v>
       </c>
@@ -5906,7 +6411,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="18.75" customHeight="1">
+    <row r="260" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="7">
         <v>901295822</v>
       </c>
@@ -5917,7 +6422,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="18.75" customHeight="1">
+    <row r="261" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>900381555</v>
       </c>
@@ -5928,7 +6433,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="18.75" customHeight="1">
+    <row r="262" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="7">
         <v>830117846</v>
       </c>
@@ -5939,7 +6444,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="18.75" customHeight="1">
+    <row r="263" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="7">
         <v>901017982</v>
       </c>
@@ -5950,7 +6455,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="18.75" customHeight="1">
+    <row r="264" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>900314301</v>
       </c>
@@ -5961,7 +6466,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="18.75" customHeight="1">
+    <row r="265" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>901881050</v>
       </c>
@@ -5972,7 +6477,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="18.75" customHeight="1">
+    <row r="266" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>891180134</v>
       </c>
@@ -5983,7 +6488,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="18.75" customHeight="1">
+    <row r="267" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="7">
         <v>900407111</v>
       </c>
@@ -5994,7 +6499,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="18.75" customHeight="1">
+    <row r="268" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>900112820</v>
       </c>
@@ -6005,7 +6510,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="18.75" customHeight="1">
+    <row r="269" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="7">
         <v>901169422</v>
       </c>
@@ -6016,7 +6521,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="18.75" customHeight="1">
+    <row r="270" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>900108793</v>
       </c>
@@ -6027,7 +6532,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="18.75" customHeight="1">
+    <row r="271" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="7">
         <v>900576170</v>
       </c>
@@ -6038,7 +6543,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="18.75" customHeight="1">
+    <row r="272" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>891180268</v>
       </c>
@@ -6049,7 +6554,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="18.75" customHeight="1">
+    <row r="273" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="7">
         <v>900678145</v>
       </c>
@@ -6060,7 +6565,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="18.75" customHeight="1">
+    <row r="274" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="7">
         <v>900627725</v>
       </c>
@@ -6071,7 +6576,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="18.75" customHeight="1">
+    <row r="275" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="7">
         <v>891411743</v>
       </c>
@@ -6082,7 +6587,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="18.75" customHeight="1">
+    <row r="276" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="7">
         <v>900077520</v>
       </c>
@@ -6093,7 +6598,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="18.75" customHeight="1">
+    <row r="277" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>900958564</v>
       </c>
@@ -6104,7 +6609,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="18.75" customHeight="1">
+    <row r="278" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="7">
         <v>800200789</v>
       </c>
@@ -6115,7 +6620,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="18.75" customHeight="1">
+    <row r="279" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="7">
         <v>900061048</v>
       </c>
@@ -6126,7 +6631,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="18.75" customHeight="1">
+    <row r="280" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="7">
         <v>901127904</v>
       </c>
@@ -6137,7 +6642,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="18.75" customHeight="1">
+    <row r="281" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="7">
         <v>890801562</v>
       </c>
@@ -6148,7 +6653,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="18.75" customHeight="1">
+    <row r="282" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4">
         <v>80055710</v>
       </c>
@@ -6159,7 +6664,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="18.75" customHeight="1">
+    <row r="283" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="7">
         <v>79442674</v>
       </c>
@@ -6170,7 +6675,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="18.75" customHeight="1">
+    <row r="284" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4">
         <v>891856507</v>
       </c>
@@ -6181,7 +6686,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="18.75" customHeight="1">
+    <row r="285" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="7">
         <v>900231829</v>
       </c>
@@ -6192,7 +6697,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="18.75" customHeight="1">
+    <row r="286" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="7">
         <v>900171988</v>
       </c>
@@ -6203,7 +6708,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="18.75" customHeight="1">
+    <row r="287" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="7">
         <v>891180098</v>
       </c>
@@ -6214,7 +6719,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="18.75" customHeight="1">
+    <row r="288" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="7">
         <v>845000038</v>
       </c>
@@ -6225,7 +6730,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="18.75" customHeight="1">
+    <row r="289" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4">
         <v>900817788</v>
       </c>
@@ -6236,7 +6741,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="18.75" customHeight="1">
+    <row r="290" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4">
         <v>899999147</v>
       </c>
@@ -6247,7 +6752,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="18.75" customHeight="1">
+    <row r="291" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4">
         <v>900419180</v>
       </c>
@@ -6258,7 +6763,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="18.75" customHeight="1">
+    <row r="292" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="7">
         <v>830119200</v>
       </c>
@@ -6269,7 +6774,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="18.75" customHeight="1">
+    <row r="293" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="7">
         <v>890801495</v>
       </c>
@@ -6280,7 +6785,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="18.75" customHeight="1">
+    <row r="294" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4">
         <v>900582598</v>
       </c>
@@ -6291,7 +6796,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="18.75" customHeight="1">
+    <row r="295" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>890802036</v>
       </c>
@@ -6302,7 +6807,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="18.75" customHeight="1">
+    <row r="296" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="7">
         <v>900462440</v>
       </c>
@@ -6313,7 +6818,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="18.75" customHeight="1">
+    <row r="297" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>846000474</v>
       </c>
@@ -6324,7 +6829,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="18.75" customHeight="1">
+    <row r="298" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="7">
         <v>800000118</v>
       </c>
@@ -6335,7 +6840,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="18.75" customHeight="1">
+    <row r="299" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>900211468</v>
       </c>
@@ -6346,7 +6851,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="18.75" customHeight="1">
+    <row r="300" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
         <v>891855438</v>
       </c>
@@ -6357,7 +6862,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="18.75" customHeight="1">
+    <row r="301" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="7">
         <v>19364579</v>
       </c>
@@ -6368,7 +6873,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="18.75" customHeight="1">
+    <row r="302" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="7">
         <v>900004059</v>
       </c>
@@ -6379,7 +6884,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="18.75" customHeight="1">
+    <row r="303" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="7">
         <v>846003357</v>
       </c>
@@ -6390,7 +6895,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="18.75" customHeight="1">
+    <row r="304" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="7">
         <v>901457374</v>
       </c>
@@ -6401,7 +6906,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="18.75" customHeight="1">
+    <row r="305" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>830005028</v>
       </c>
@@ -6412,7 +6917,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="18.75" customHeight="1">
+    <row r="306" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
         <v>900606412</v>
       </c>
@@ -6423,7 +6928,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="18.75" customHeight="1">
+    <row r="307" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="7">
         <v>830113849</v>
       </c>
@@ -6434,7 +6939,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="18.75" customHeight="1">
+    <row r="308" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
         <v>900232628</v>
       </c>
@@ -6445,7 +6950,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="18.75" customHeight="1">
+    <row r="309" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="7">
         <v>890706823</v>
       </c>
@@ -6456,7 +6961,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="18.75" customHeight="1">
+    <row r="310" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="7">
         <v>901105417</v>
       </c>
@@ -6467,7 +6972,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="18.75" customHeight="1">
+    <row r="311" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="7">
         <v>800037202</v>
       </c>
@@ -6478,7 +6983,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="18.75" customHeight="1">
+    <row r="312" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="7">
         <v>80412859</v>
       </c>
@@ -6489,7 +6994,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="18.75" customHeight="1">
+    <row r="313" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="15">
         <v>800180553</v>
       </c>
@@ -6500,7 +7005,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="18.75" customHeight="1">
+    <row r="314" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="7">
         <v>891411381</v>
       </c>
@@ -6511,7 +7016,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="18.75" customHeight="1">
+    <row r="315" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="7">
         <v>814003448</v>
       </c>
@@ -6522,7 +7027,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="18.75" customHeight="1">
+    <row r="316" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="7">
         <v>891180026</v>
       </c>
@@ -6533,7 +7038,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="18.75" customHeight="1">
+    <row r="317" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="7">
         <v>900233110</v>
       </c>
@@ -6544,7 +7049,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="18.75" customHeight="1">
+    <row r="318" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="7">
         <v>860013570</v>
       </c>
@@ -6555,7 +7060,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="18.75" customHeight="1">
+    <row r="319" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="7">
         <v>901652147</v>
       </c>
@@ -6566,7 +7071,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="18.75" customHeight="1">
+    <row r="320" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="7">
         <v>901439163</v>
       </c>
@@ -6577,7 +7082,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="18.75" customHeight="1">
+    <row r="321" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="7">
         <v>822000946</v>
       </c>
@@ -6588,7 +7093,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="18.75" customHeight="1">
+    <row r="322" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="7">
         <v>810001466</v>
       </c>
@@ -6599,7 +7104,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="18.75" customHeight="1">
+    <row r="323" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="7">
         <v>900547903</v>
       </c>
@@ -6610,7 +7115,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="18.75" customHeight="1">
+    <row r="324" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="7">
         <v>800228215</v>
       </c>
@@ -6621,7 +7126,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="18.75" customHeight="1">
+    <row r="325" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="7">
         <v>890802978</v>
       </c>
@@ -6632,7 +7137,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="18.75" customHeight="1">
+    <row r="326" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="7">
         <v>800135582</v>
       </c>
@@ -6643,7 +7148,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="18.75" customHeight="1">
+    <row r="327" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="7">
         <v>900364721</v>
       </c>
@@ -6654,7 +7159,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="18.75" customHeight="1">
+    <row r="328" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="7">
         <v>899999123</v>
       </c>
@@ -6665,7 +7170,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="18.75" customHeight="1">
+    <row r="329" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="7">
         <v>890801099</v>
       </c>
@@ -6676,7 +7181,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="18.75" customHeight="1">
+    <row r="330" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="7">
         <v>830018305</v>
       </c>
@@ -6687,7 +7192,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="18.75" customHeight="1">
+    <row r="331" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="7">
         <v>809001482</v>
       </c>
@@ -6698,7 +7203,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="18.75" customHeight="1">
+    <row r="332" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="7">
         <v>900685235</v>
       </c>
@@ -6709,7 +7214,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="18.75" customHeight="1">
+    <row r="333" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="7">
         <v>800191101</v>
       </c>
@@ -6720,7 +7225,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="18.75" customHeight="1">
+    <row r="334" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="7">
         <v>891409981</v>
       </c>
@@ -6731,7 +7236,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="18.75" customHeight="1">
+    <row r="335" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="7">
         <v>900073806</v>
       </c>
@@ -6742,7 +7247,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="18.75" customHeight="1">
+    <row r="336" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="7">
         <v>900493064</v>
       </c>
@@ -6753,7 +7258,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="18.75" customHeight="1">
+    <row r="337" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="7">
         <v>800231235</v>
       </c>
@@ -6764,7 +7269,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="18.75" customHeight="1">
+    <row r="338" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="7">
         <v>860007373</v>
       </c>
@@ -6775,7 +7280,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="18.75" customHeight="1">
+    <row r="339" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="7">
         <v>900848340</v>
       </c>
@@ -6786,7 +7291,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="18.75" customHeight="1">
+    <row r="340" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
         <v>900115642</v>
       </c>
@@ -6797,7 +7302,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="18.75" customHeight="1">
+    <row r="341" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="7">
         <v>79533241</v>
       </c>
@@ -6808,7 +7313,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="18.75" customHeight="1">
+    <row r="342" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
         <v>830502282</v>
       </c>
@@ -6819,7 +7324,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="18.75" customHeight="1">
+    <row r="343" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="7">
         <v>900081643</v>
       </c>
@@ -6830,7 +7335,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="18.75" customHeight="1">
+    <row r="344" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="7">
         <v>891855039</v>
       </c>
@@ -6841,7 +7346,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="18.75" customHeight="1">
+    <row r="345" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="7">
         <v>805017681</v>
       </c>
@@ -6852,7 +7357,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="18.75" customHeight="1">
+    <row r="346" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="7">
         <v>820002248</v>
       </c>
@@ -6863,7 +7368,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="18.75" customHeight="1">
+    <row r="347" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="7">
         <v>860024026</v>
       </c>
@@ -6874,7 +7379,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="18.75" customHeight="1">
+    <row r="348" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="7">
         <v>71394225</v>
       </c>
@@ -6885,7 +7390,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="18.75" customHeight="1">
+    <row r="349" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="7">
         <v>832008321</v>
       </c>
@@ -6896,7 +7401,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="18.75" customHeight="1">
+    <row r="350" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="7">
         <v>901632467</v>
       </c>
@@ -6907,7 +7412,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="18.75" customHeight="1">
+    <row r="351" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="7">
         <v>891180117</v>
       </c>
@@ -6918,7 +7423,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="18.75" customHeight="1">
+    <row r="352" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="7">
         <v>900759329</v>
       </c>
@@ -6929,7 +7434,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="18.75" customHeight="1">
+    <row r="353" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="7">
         <v>891800644</v>
       </c>
@@ -6940,7 +7445,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="18.75" customHeight="1">
+    <row r="354" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="4">
         <v>800254132</v>
       </c>
@@ -6951,7 +7456,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="18.75" customHeight="1">
+    <row r="355" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="7">
         <v>899999158</v>
       </c>
@@ -6962,7 +7467,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="18.75" customHeight="1">
+    <row r="356" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="4">
         <v>79624744</v>
       </c>
@@ -6973,7 +7478,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="18.75" customHeight="1">
+    <row r="357" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="7">
         <v>891409390</v>
       </c>
@@ -6984,7 +7489,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="18.75" customHeight="1">
+    <row r="358" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="7">
         <v>890680014</v>
       </c>
@@ -6995,7 +7500,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="18.75" customHeight="1">
+    <row r="359" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="7">
         <v>809006690</v>
       </c>
@@ -7006,7 +7511,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="18.75" customHeight="1">
+    <row r="360" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="7">
         <v>900213617</v>
       </c>
@@ -7017,7 +7522,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="18.75" customHeight="1">
+    <row r="361" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4">
         <v>900423816</v>
       </c>
@@ -7028,7 +7533,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="18.75" customHeight="1">
+    <row r="362" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4">
         <v>860015929</v>
       </c>
@@ -7039,7 +7544,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="18.75" customHeight="1">
+    <row r="363" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4">
         <v>890806490</v>
       </c>
@@ -7050,7 +7555,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="18.75" customHeight="1">
+    <row r="364" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4">
         <v>860006626</v>
       </c>
@@ -7061,7 +7566,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="18.75" customHeight="1">
+    <row r="365" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4">
         <v>813005295</v>
       </c>
@@ -7072,7 +7577,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="18.75" customHeight="1">
+    <row r="366" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4">
         <v>846001425</v>
       </c>
@@ -7083,7 +7588,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="18.75" customHeight="1">
+    <row r="367" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4">
         <v>800139366</v>
       </c>
@@ -7094,7 +7599,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="18.75" customHeight="1">
+    <row r="368" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4">
         <v>816005003</v>
       </c>
@@ -7105,7 +7610,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="18.75" customHeight="1">
+    <row r="369" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="4">
         <v>900435790</v>
       </c>
@@ -7116,12 +7621,12 @@
         <v>738</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="18.75" customHeight="1">
+    <row r="370" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="19"/>
       <c r="B370" s="20"/>
       <c r="C370" s="21"/>
     </row>
-    <row r="371" spans="1:3" ht="18.75" customHeight="1">
+    <row r="371" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="19"/>
       <c r="B371" s="20"/>
       <c r="C371" s="21"/>

--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/SOPORTES DE MEDICION/soportes de medicon.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/SOPORTES DE MEDICION/soportes de medicon.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\SOPORTES DE MEDICION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CACBC49-9AEE-4D54-B00C-FF9737164D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE10DEBF-3D5E-4B24-B3A6-DD5142306A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Hoja1!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Hoja1!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja3!$A$1:$C$374</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="776">
   <si>
     <t>NIT</t>
   </si>
@@ -2259,98 +2261,119 @@
     <t>CEDULA PACIENTE</t>
   </si>
   <si>
-    <t>contrato</t>
-  </si>
-  <si>
-    <t>Razon Social</t>
-  </si>
-  <si>
     <t>Si</t>
   </si>
   <si>
-    <t>mes evaluado</t>
-  </si>
-  <si>
-    <t>febrero 2026</t>
-  </si>
-  <si>
     <t>NOMBRE DEL PACIENTE </t>
   </si>
   <si>
+    <t>0092-2026</t>
+  </si>
+  <si>
+    <t>OTTO BOCK HEALTHCARE ANDINA S.A.S</t>
+  </si>
+  <si>
+    <t>0116-2026</t>
+  </si>
+  <si>
+    <t>CENTRO INTEGRAL DE REHABILITACION DE COLOMBIA - CIREC</t>
+  </si>
+  <si>
+    <t>0125-2026</t>
+  </si>
+  <si>
+    <t>LABORATORIO DE ORTESIS Y PROTESIS GILETE Y CIA LIMITADA</t>
+  </si>
+  <si>
+    <t>0380-2026</t>
+  </si>
+  <si>
+    <t>CLINICA COLSANITAS SA</t>
+  </si>
+  <si>
+    <t>0381-2026</t>
+  </si>
+  <si>
+    <t>CENTRO MEDICO OFTALMOLOGICO Y LABORATORIO CLINICO ANDRADE NARVAEZ SOCIEDAD POR ACCIONES SIMPLIFICADA COLCAN S.A.S.</t>
+  </si>
+  <si>
+    <t>0492-2026</t>
+  </si>
+  <si>
+    <t>IMEDHEALTH S.A.S. IPS</t>
+  </si>
+  <si>
+    <t>0496-2026</t>
+  </si>
+  <si>
+    <t>ALIANZA DE AMBULANCIAS MEDICA SAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAZON SOCIAL </t>
+  </si>
+  <si>
+    <t>Periodo evaluado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS ALBERTO MENDEZ TORRES </t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDWIN LEANDRO GALLEGO CARDONA </t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USUARIO INDICA QUE ESTAN EN PROCESO DE FABRICACION DE LA PROTESIS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ELIAS SANABRIA PULIDO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">USUARIO INDICA QUE EL 5 MAYO TIENE JUNTA DE PROTESIS POR LO CUAL 5 DIAS ANTES LE HACEN EL MONTAJE DEL KIT </t>
+  </si>
+  <si>
+    <t>FLOWER  MOLINA  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">USURIO INDICA QUE NO HUBO ATENCION, YA QUE EN LA IPS LE HICIERON SABER QUE ESTA JUNTA NO EXISTE PIDIO SOPORTE YA QUE NO VIVE EN BOGOTA Y LA IPS NO LE GENERO ESTE SOPORTE Y HASTA EL DIA DE HOY NO LE HAN DADO RESPUESTA </t>
+  </si>
+  <si>
+    <t>MARZO 2026.</t>
+  </si>
+  <si>
     <t>El servicio o entrega ya fue realizado</t>
   </si>
   <si>
+    <t>¿LA PRÓTESIS, ORTESIS Y/O INSUMO LE HA GENERADO ALGUNA LESIÓN DURANTE SU USO?</t>
+  </si>
+  <si>
+    <t>4. OPORTUNIDAD EN LA ATENCIÓN PRESTADA POR LA IPS</t>
+  </si>
+  <si>
+    <t>5. CALIDAD EN EL SERVICIO PRESTADO POR PARTE DEL PROFESIONAL Y/O PERSONAL ADMINISTRATIVO</t>
+  </si>
+  <si>
+    <t>6. INFRAESTRUCTURA Y DOTACIÓN DE LAS INSTALACIONES DE LA IPS</t>
+  </si>
+  <si>
+    <t>Observaciones, por favor poner una observacion puntual que notifique el usuario.</t>
+  </si>
+  <si>
     <t>LA PRÓTESIS,ORTESIS Y/O INSUMO ENTREGADO CUMPLE CON LAS ESPECIFICACIONES TÉCNICAS DADAS   POR EL MÉDICO TRATANTE</t>
-  </si>
-  <si>
-    <t>¿LA PRÓTESIS, ORTESIS Y/O INSUMO LE HA GENERADO ALGUNA LESIÓN DURANTE SU USO?</t>
-  </si>
-  <si>
-    <t>4. OPORTUNIDAD EN LA ATENCIÓN PRESTADA POR LA IPS</t>
-  </si>
-  <si>
-    <t>5. CALIDAD EN EL SERVICIO PRESTADO POR PARTE DEL PROFESIONAL Y/O PERSONAL ADMINISTRATIVO</t>
-  </si>
-  <si>
-    <t>6. INFRAESTRUCTURA Y DOTACIÓN DE LAS INSTALACIONES DE LA IPS</t>
-  </si>
-  <si>
-    <t>Observaciones, por favor poner una observacion puntual que notifique el usuario.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANDRES FELIPE GONZALEZ MONROY </t>
-  </si>
-  <si>
-    <t>si</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GUSTAVO  CHAPARRO BOTELLO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIGUEL ANGEL SANCHEZ GARCIA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FABIO ARNULFO PUERTA GARZON </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JABER  ESTRADA ZAPATA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIANELA  PANTALEON PINTO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUIS ALBERTO MENDEZ TORRES </t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOELIA  PENCUA SAMBONY </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDWAR ESNEIDER HERNANDEZ MORALES </t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario indica que el 20 de marzo tiene la entrega de los insumos </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VICTOR ERNESTO ARBOLEDA BERRIO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">El usuario indica que aun no le han hecho la entrega de los insumos </t>
-  </si>
-  <si>
-    <t xml:space="preserve">WILLINGTON  VEGA CESPEDES </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2390,13 +2413,17 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Century Gothic"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2433,8 +2460,26 @@
         <fgColor rgb="FFCAEDFB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E6A2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2464,11 +2509,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2548,26 +2621,99 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2868,7 +3014,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" style="25" bestFit="1" customWidth="1"/>
@@ -2876,672 +3022,149 @@
     <col min="3" max="3" width="21.5703125" style="26" customWidth="1"/>
     <col min="4" max="4" width="21.5703125" style="26" bestFit="1" customWidth="1"/>
     <col min="5" max="8" width="21.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="32.7109375" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:12" s="27" customFormat="1" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
         <v>739</v>
       </c>
-      <c r="B1" s="28" t="s">
-        <v>745</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>743</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>746</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>747</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>748</v>
-      </c>
-      <c r="G1" s="28" t="s">
-        <v>749</v>
-      </c>
-      <c r="H1" s="28" t="s">
-        <v>750</v>
-      </c>
-      <c r="I1" s="28" t="s">
-        <v>751</v>
-      </c>
-      <c r="J1" s="28" t="s">
-        <v>752</v>
-      </c>
-      <c r="K1" s="30" t="s">
+      <c r="B1" s="27" t="s">
+        <v>741</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>769</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>775</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>770</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>771</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>772</v>
+      </c>
+      <c r="I1" t="s">
+        <v>773</v>
+      </c>
+      <c r="J1" t="s">
+        <v>774</v>
+      </c>
+      <c r="K1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="27" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="25">
+        <v>92496452</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>758</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>768</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>759</v>
+      </c>
+      <c r="E2" s="25" t="s">
         <v>740</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28">
-        <v>1055963451</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>753</v>
-      </c>
-      <c r="C2" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28">
+      <c r="G2" s="25">
         <v>5</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="25">
         <v>5</v>
       </c>
-      <c r="I2" s="28">
-        <v>4</v>
-      </c>
-      <c r="J2" s="28" t="s">
-        <v>755</v>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2" t="s">
+        <v>760</v>
       </c>
       <c r="K2" t="s">
-        <v>525</v>
+        <v>583</v>
       </c>
       <c r="L2" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28">
-        <v>12718993</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>756</v>
-      </c>
-      <c r="C3" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28">
-        <v>5</v>
-      </c>
-      <c r="H3" s="28">
-        <v>5</v>
-      </c>
-      <c r="I3" s="28">
-        <v>5</v>
-      </c>
-      <c r="J3" s="28" t="s">
-        <v>755</v>
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="25">
+        <v>1053770020</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>761</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>768</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>762</v>
+      </c>
+      <c r="J3" t="s">
+        <v>763</v>
       </c>
       <c r="K3" t="s">
-        <v>525</v>
+        <v>583</v>
       </c>
       <c r="L3" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
-        <v>12718993</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>756</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28">
-        <v>5</v>
-      </c>
-      <c r="H4" s="28">
-        <v>5</v>
-      </c>
-      <c r="I4" s="28">
-        <v>5</v>
-      </c>
-      <c r="J4" s="28" t="s">
-        <v>755</v>
+        <v>584</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="25">
+        <v>79043668</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>764</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>768</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>762</v>
+      </c>
+      <c r="J4" t="s">
+        <v>765</v>
       </c>
       <c r="K4" t="s">
-        <v>525</v>
+        <v>583</v>
       </c>
       <c r="L4" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28">
-        <v>1006822134</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>757</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28">
-        <v>5</v>
-      </c>
-      <c r="H5" s="28">
-        <v>5</v>
-      </c>
-      <c r="I5" s="28">
-        <v>5</v>
-      </c>
-      <c r="J5" s="28" t="s">
-        <v>755</v>
+        <v>584</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="25">
+        <v>16256537</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>766</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>768</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>762</v>
+      </c>
+      <c r="J5" t="s">
+        <v>767</v>
       </c>
       <c r="K5" t="s">
-        <v>525</v>
+        <v>583</v>
       </c>
       <c r="L5" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
-        <v>1006822134</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>757</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28">
-        <v>5</v>
-      </c>
-      <c r="H6" s="28">
-        <v>5</v>
-      </c>
-      <c r="I6" s="28">
-        <v>5</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="K6" t="s">
-        <v>525</v>
-      </c>
-      <c r="L6" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
-        <v>98603739</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>758</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28">
-        <v>5</v>
-      </c>
-      <c r="H7" s="28">
-        <v>5</v>
-      </c>
-      <c r="I7" s="28">
-        <v>5</v>
-      </c>
-      <c r="J7" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="K7" t="s">
-        <v>683</v>
-      </c>
-      <c r="L7" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
-        <v>98603739</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>758</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28">
-        <v>5</v>
-      </c>
-      <c r="H8" s="28">
-        <v>5</v>
-      </c>
-      <c r="I8" s="28">
-        <v>5</v>
-      </c>
-      <c r="J8" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="K8" t="s">
-        <v>683</v>
-      </c>
-      <c r="L8" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
-        <v>71388052</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>759</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28">
-        <v>4</v>
-      </c>
-      <c r="H9" s="28">
-        <v>4</v>
-      </c>
-      <c r="I9" s="28">
-        <v>4</v>
-      </c>
-      <c r="J9" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="K9" t="s">
-        <v>683</v>
-      </c>
-      <c r="L9" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
-        <v>71388052</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>759</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28">
-        <v>4</v>
-      </c>
-      <c r="H10" s="28">
-        <v>4</v>
-      </c>
-      <c r="I10" s="28">
-        <v>4</v>
-      </c>
-      <c r="J10" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="K10" t="s">
-        <v>683</v>
-      </c>
-      <c r="L10" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="28">
-        <v>60360054</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>760</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28">
-        <v>5</v>
-      </c>
-      <c r="H11" s="28">
-        <v>5</v>
-      </c>
-      <c r="I11" s="28">
-        <v>5</v>
-      </c>
-      <c r="J11" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="K11" t="s">
-        <v>583</v>
-      </c>
-      <c r="L11" t="s">
         <v>584</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
-        <v>60360054</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>760</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28">
-        <v>5</v>
-      </c>
-      <c r="H12" s="28">
-        <v>5</v>
-      </c>
-      <c r="I12" s="28">
-        <v>5</v>
-      </c>
-      <c r="J12" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="K12" t="s">
-        <v>583</v>
-      </c>
-      <c r="L12" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="28">
-        <v>60360054</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>760</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28">
-        <v>5</v>
-      </c>
-      <c r="H13" s="28">
-        <v>5</v>
-      </c>
-      <c r="I13" s="28">
-        <v>5</v>
-      </c>
-      <c r="J13" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="K13" t="s">
-        <v>583</v>
-      </c>
-      <c r="L13" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
-        <v>92496452</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>761</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28">
-        <v>5</v>
-      </c>
-      <c r="H14" s="28">
-        <v>5</v>
-      </c>
-      <c r="I14" s="28">
-        <v>5</v>
-      </c>
-      <c r="J14" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="K14" t="s">
-        <v>583</v>
-      </c>
-      <c r="L14" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="28">
-        <v>98603739</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>758</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28">
-        <v>5</v>
-      </c>
-      <c r="H15" s="28">
-        <v>5</v>
-      </c>
-      <c r="I15" s="28">
-        <v>5</v>
-      </c>
-      <c r="J15" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="K15" t="s">
-        <v>683</v>
-      </c>
-      <c r="L15" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
-        <v>25480654</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>762</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>742</v>
-      </c>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28">
-        <v>5</v>
-      </c>
-      <c r="H16" s="28">
-        <v>5</v>
-      </c>
-      <c r="I16" s="28">
-        <v>5</v>
-      </c>
-      <c r="J16" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="K16" t="s">
-        <v>339</v>
-      </c>
-      <c r="L16" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="28">
-        <v>1032367507</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>763</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>764</v>
-      </c>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28" t="s">
-        <v>765</v>
-      </c>
-      <c r="K17" t="s">
-        <v>339</v>
-      </c>
-      <c r="L17" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
-        <v>1102800990</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>766</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>764</v>
-      </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28" t="s">
-        <v>767</v>
-      </c>
-      <c r="K18" t="s">
-        <v>339</v>
-      </c>
-      <c r="L18" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="28">
-        <v>5978935</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>768</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>744</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>764</v>
-      </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28" t="s">
-        <v>767</v>
-      </c>
-      <c r="K19" t="s">
-        <v>339</v>
-      </c>
-      <c r="L19" t="s">
-        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -3550,6 +3173,4152 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA89662-6597-440B-93CF-3E4C4E5F4B95}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:C374"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" style="23" customWidth="1"/>
+    <col min="2" max="2" width="52.28515625" style="24" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" style="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="31">
+        <v>900220590</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="31">
+        <v>891855847</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="31">
+        <v>890801026</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31">
+        <v>41471570</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="31">
+        <v>900352592</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="31">
+        <v>900385628</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="31">
+        <v>832010240</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="31">
+        <v>899999161</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="31">
+        <v>900119357</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="31">
+        <v>830114167</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="31">
+        <v>79781903</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="31">
+        <v>891190011</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="31">
+        <v>891401643</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="31">
+        <v>800174851</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="31">
+        <v>800193490</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="31">
+        <v>900420664</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="31">
+        <v>80041361</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="31">
+        <v>830109997</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>743</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="31">
+        <v>860053761</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="31">
+        <v>19274667</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="31">
+        <v>890701718</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="31">
+        <v>800209891</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="31">
+        <v>860066767</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>745</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="31">
+        <v>810003245</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="31">
+        <v>800085883</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>747</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="31">
+        <v>900649963</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="31">
+        <v>52794734</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="31">
+        <v>800231215</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="31">
+        <v>900691301</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="31">
+        <v>800006509</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="31">
+        <v>900193162</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="31">
+        <v>890807591</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="31">
+        <v>900144408</v>
+      </c>
+      <c r="B34" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="31">
+        <v>860010783</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="31">
+        <v>900691056</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="31">
+        <v>901060053</v>
+      </c>
+      <c r="B37" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="31">
+        <v>900215983</v>
+      </c>
+      <c r="B38" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="31">
+        <v>900129308</v>
+      </c>
+      <c r="B39" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="31">
+        <v>892000264</v>
+      </c>
+      <c r="B40" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="31">
+        <v>800218979</v>
+      </c>
+      <c r="B41" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="31">
+        <v>891855029</v>
+      </c>
+      <c r="B42" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="31">
+        <v>900142282</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="31">
+        <v>860006745</v>
+      </c>
+      <c r="B44" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="31">
+        <v>890702369</v>
+      </c>
+      <c r="B45" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="30" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="31">
+        <v>800017308</v>
+      </c>
+      <c r="B46" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="31">
+        <v>890000992</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="31">
+        <v>830511298</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="31">
+        <v>832001411</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="31">
+        <v>809010893</v>
+      </c>
+      <c r="B50" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" s="30" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="31">
+        <v>900714297</v>
+      </c>
+      <c r="B51" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="31">
+        <v>900034131</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="31">
+        <v>860015536</v>
+      </c>
+      <c r="B53" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="31">
+        <v>900211460</v>
+      </c>
+      <c r="B54" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C54" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="31">
+        <v>860090566</v>
+      </c>
+      <c r="B55" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="31">
+        <v>891800335</v>
+      </c>
+      <c r="B56" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="31">
+        <v>900454994</v>
+      </c>
+      <c r="B57" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="31">
+        <v>820003431</v>
+      </c>
+      <c r="B58" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="C58" s="30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="31">
+        <v>830070284</v>
+      </c>
+      <c r="B59" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="C59" s="30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="31">
+        <v>890703630</v>
+      </c>
+      <c r="B60" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C60" s="30" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="31">
+        <v>800032418</v>
+      </c>
+      <c r="B61" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C61" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="31">
+        <v>900211477</v>
+      </c>
+      <c r="B62" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C62" s="30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="31">
+        <v>900004894</v>
+      </c>
+      <c r="B63" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C63" s="30" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="31">
+        <v>901061505</v>
+      </c>
+      <c r="B64" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C64" s="30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="31">
+        <v>901622460</v>
+      </c>
+      <c r="B65" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C65" s="30" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="31">
+        <v>828000386</v>
+      </c>
+      <c r="B66" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" s="30" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="31">
+        <v>891200679</v>
+      </c>
+      <c r="B67" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C67" s="30" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="31">
+        <v>79451044</v>
+      </c>
+      <c r="B68" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" s="30" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="31">
+        <v>860035992</v>
+      </c>
+      <c r="B69" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" s="30" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="31">
+        <v>900217648</v>
+      </c>
+      <c r="B70" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="31">
+        <v>900130936</v>
+      </c>
+      <c r="B71" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="C71" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="31">
+        <v>890805923</v>
+      </c>
+      <c r="B72" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="C72" s="30" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="31">
+        <v>900470918</v>
+      </c>
+      <c r="B73" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="C73" s="30" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="31">
+        <v>900236728</v>
+      </c>
+      <c r="B74" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="C74" s="30" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="31">
+        <v>844004197</v>
+      </c>
+      <c r="B75" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="C75" s="30" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="31">
+        <v>900175697</v>
+      </c>
+      <c r="B76" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C76" s="30" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="31">
+        <v>820003850</v>
+      </c>
+      <c r="B77" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="C77" s="30" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="31">
+        <v>830073010</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" s="30" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="31">
+        <v>860015888</v>
+      </c>
+      <c r="B79" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="31">
+        <v>900210981</v>
+      </c>
+      <c r="B80" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C80" s="30" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="31">
+        <v>901011962</v>
+      </c>
+      <c r="B81" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C81" s="34" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="31">
+        <v>900118059</v>
+      </c>
+      <c r="B82" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="C82" s="30" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="31">
+        <v>901447598</v>
+      </c>
+      <c r="B83" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="C83" s="30" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="31">
+        <v>901163080</v>
+      </c>
+      <c r="B84" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C84" s="30" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="31">
+        <v>900559103</v>
+      </c>
+      <c r="B85" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="C85" s="34" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="31">
+        <v>891480000</v>
+      </c>
+      <c r="B86" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="C86" s="30" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="31">
+        <v>900971006</v>
+      </c>
+      <c r="B87" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="C87" s="30" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="31">
+        <v>900420751</v>
+      </c>
+      <c r="B88" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="C88" s="30" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="31">
+        <v>901102510</v>
+      </c>
+      <c r="B89" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="C89" s="30" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="31">
+        <v>800044967</v>
+      </c>
+      <c r="B90" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="C90" s="30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="31">
+        <v>832000744</v>
+      </c>
+      <c r="B91" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="C91" s="30" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="31">
+        <v>901631369</v>
+      </c>
+      <c r="B92" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="C92" s="30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="31">
+        <v>830010671</v>
+      </c>
+      <c r="B93" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="C93" s="30" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="31">
+        <v>900769055</v>
+      </c>
+      <c r="B94" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="C94" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="31">
+        <v>820001181</v>
+      </c>
+      <c r="B95" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="C95" s="30" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="31">
+        <v>891201578</v>
+      </c>
+      <c r="B96" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="C96" s="30" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="31">
+        <v>901011387</v>
+      </c>
+      <c r="B97" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="C97" s="30" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="31">
+        <v>891480036</v>
+      </c>
+      <c r="B98" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="C98" s="30" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="31">
+        <v>900491982</v>
+      </c>
+      <c r="B99" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C99" s="30" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="31">
+        <v>832003167</v>
+      </c>
+      <c r="B100" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C100" s="30" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="31">
+        <v>846000253</v>
+      </c>
+      <c r="B101" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="C101" s="30" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="31">
+        <v>800149384</v>
+      </c>
+      <c r="B102" s="32" t="s">
+        <v>749</v>
+      </c>
+      <c r="C102" s="30" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="31">
+        <v>900138555</v>
+      </c>
+      <c r="B103" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="C103" s="34" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="31">
+        <v>800066001</v>
+      </c>
+      <c r="B104" s="32" t="s">
+        <v>751</v>
+      </c>
+      <c r="C104" s="30" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="31">
+        <v>826002694</v>
+      </c>
+      <c r="B105" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="C105" s="30" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="31">
+        <v>830027158</v>
+      </c>
+      <c r="B106" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="C106" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="31">
+        <v>900132642</v>
+      </c>
+      <c r="B107" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="C107" s="30" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="31">
+        <v>901182731</v>
+      </c>
+      <c r="B108" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="C108" s="30" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="31">
+        <v>900415353</v>
+      </c>
+      <c r="B109" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="C109" s="30" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="31">
+        <v>901386786</v>
+      </c>
+      <c r="B110" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="C110" s="30" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="31">
+        <v>890701353</v>
+      </c>
+      <c r="B111" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="C111" s="30" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="31">
+        <v>890706833</v>
+      </c>
+      <c r="B112" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="C112" s="30" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="31">
+        <v>809002913</v>
+      </c>
+      <c r="B113" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="C113" s="34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="31">
+        <v>900958115</v>
+      </c>
+      <c r="B114" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="C114" s="30" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="31">
+        <v>900876789</v>
+      </c>
+      <c r="B115" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="C115" s="30" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="31">
+        <v>800082446</v>
+      </c>
+      <c r="B116" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="C116" s="30" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="31">
+        <v>816007055</v>
+      </c>
+      <c r="B117" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="C117" s="30" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="31">
+        <v>900912423</v>
+      </c>
+      <c r="B118" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="C118" s="30" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="31">
+        <v>900826841</v>
+      </c>
+      <c r="B119" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="C119" s="30" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="31">
+        <v>901091739</v>
+      </c>
+      <c r="B120" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="C120" s="30" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="31">
+        <v>900215698</v>
+      </c>
+      <c r="B121" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C121" s="30" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="31">
+        <v>901392384</v>
+      </c>
+      <c r="B122" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="C122" s="30" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="31">
+        <v>828000073</v>
+      </c>
+      <c r="B123" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="C123" s="30" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="31">
+        <v>901352353</v>
+      </c>
+      <c r="B124" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="C124" s="30" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="31">
+        <v>900999027</v>
+      </c>
+      <c r="B125" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="C125" s="30" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="31">
+        <v>800074996</v>
+      </c>
+      <c r="B126" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="C126" s="30" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="31">
+        <v>901680794</v>
+      </c>
+      <c r="B127" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="C127" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="31">
+        <v>900477525</v>
+      </c>
+      <c r="B128" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C128" s="30" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="31">
+        <v>900532173</v>
+      </c>
+      <c r="B129" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="C129" s="30" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="31">
+        <v>900702090</v>
+      </c>
+      <c r="B130" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="C130" s="30" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="31">
+        <v>890701033</v>
+      </c>
+      <c r="B131" s="35" t="s">
+        <v>254</v>
+      </c>
+      <c r="C131" s="34" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="31">
+        <v>901625767</v>
+      </c>
+      <c r="B132" s="32" t="s">
+        <v>753</v>
+      </c>
+      <c r="C132" s="30" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="31">
+        <v>900800269</v>
+      </c>
+      <c r="B133" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="C133" s="30" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="31">
+        <v>901606280</v>
+      </c>
+      <c r="B134" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C134" s="30" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="31">
+        <v>830508610</v>
+      </c>
+      <c r="B135" s="32" t="s">
+        <v>755</v>
+      </c>
+      <c r="C135" s="30" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="31">
+        <v>900342271</v>
+      </c>
+      <c r="B136" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="C136" s="30" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="31">
+        <v>800162035</v>
+      </c>
+      <c r="B137" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="C137" s="30" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="31">
+        <v>800146679</v>
+      </c>
+      <c r="B138" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="C138" s="30" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="31">
+        <v>901470470</v>
+      </c>
+      <c r="B139" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C139" s="30" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="31">
+        <v>800234796</v>
+      </c>
+      <c r="B140" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="C140" s="30" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="31">
+        <v>900959048</v>
+      </c>
+      <c r="B141" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C141" s="30" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="31">
+        <v>890801758</v>
+      </c>
+      <c r="B142" s="33" t="s">
+        <v>274</v>
+      </c>
+      <c r="C142" s="30" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="31">
+        <v>805019730</v>
+      </c>
+      <c r="B143" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="C143" s="30" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="31">
+        <v>820002596</v>
+      </c>
+      <c r="B144" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="C144" s="30" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="31">
+        <v>900373445</v>
+      </c>
+      <c r="B145" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="C145" s="30" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="31">
+        <v>900301238</v>
+      </c>
+      <c r="B146" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="C146" s="30" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="31">
+        <v>900296178</v>
+      </c>
+      <c r="B147" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="C147" s="30" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="31">
+        <v>900341409</v>
+      </c>
+      <c r="B148" s="33" t="s">
+        <v>286</v>
+      </c>
+      <c r="C148" s="30" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="31">
+        <v>813001952</v>
+      </c>
+      <c r="B149" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="C149" s="30" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="31">
+        <v>800227072</v>
+      </c>
+      <c r="B150" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="C150" s="30" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="31">
+        <v>800036400</v>
+      </c>
+      <c r="B151" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="C151" s="30" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="31">
+        <v>809009066</v>
+      </c>
+      <c r="B152" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="C152" s="30" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="31">
+        <v>900563603</v>
+      </c>
+      <c r="B153" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="C153" s="30" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="31">
+        <v>890001006</v>
+      </c>
+      <c r="B154" s="32" t="s">
+        <v>298</v>
+      </c>
+      <c r="C154" s="30" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="31">
+        <v>901119103</v>
+      </c>
+      <c r="B155" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="C155" s="30" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="31">
+        <v>900240354</v>
+      </c>
+      <c r="B156" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="C156" s="30" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="31">
+        <v>900504265</v>
+      </c>
+      <c r="B157" s="33" t="s">
+        <v>304</v>
+      </c>
+      <c r="C157" s="30" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="31">
+        <v>813002940</v>
+      </c>
+      <c r="B158" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="C158" s="30" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="31">
+        <v>830027578</v>
+      </c>
+      <c r="B159" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="C159" s="30" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="31">
+        <v>822006595</v>
+      </c>
+      <c r="B160" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="C160" s="30" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="31">
+        <v>900510844</v>
+      </c>
+      <c r="B161" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="C161" s="30" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="31">
+        <v>900573146</v>
+      </c>
+      <c r="B162" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="C162" s="30" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="31">
+        <v>890701459</v>
+      </c>
+      <c r="B163" s="33" t="s">
+        <v>316</v>
+      </c>
+      <c r="C163" s="34" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="31">
+        <v>900355585</v>
+      </c>
+      <c r="B164" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="C164" s="30" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="31">
+        <v>860039726</v>
+      </c>
+      <c r="B165" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="C165" s="30" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="31">
+        <v>800201496</v>
+      </c>
+      <c r="B166" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="C166" s="30" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="31">
+        <v>891800395</v>
+      </c>
+      <c r="B167" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="C167" s="30" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="31">
+        <v>900103925</v>
+      </c>
+      <c r="B168" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="C168" s="30" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="31">
+        <v>800254850</v>
+      </c>
+      <c r="B169" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="C169" s="30" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="31">
+        <v>830514240</v>
+      </c>
+      <c r="B170" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="C170" s="30" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="31">
+        <v>900966154</v>
+      </c>
+      <c r="B171" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="C171" s="30" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="31">
+        <v>892000501</v>
+      </c>
+      <c r="B172" s="33" t="s">
+        <v>334</v>
+      </c>
+      <c r="C172" s="30" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="31">
+        <v>860011298</v>
+      </c>
+      <c r="B173" s="33" t="s">
+        <v>336</v>
+      </c>
+      <c r="C173" s="30" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="31">
+        <v>820005389</v>
+      </c>
+      <c r="B174" s="32" t="s">
+        <v>338</v>
+      </c>
+      <c r="C174" s="30" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="31">
+        <v>830039229</v>
+      </c>
+      <c r="B175" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="C175" s="30" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="31">
+        <v>900448997</v>
+      </c>
+      <c r="B176" s="33" t="s">
+        <v>342</v>
+      </c>
+      <c r="C176" s="30" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="31">
+        <v>900716387</v>
+      </c>
+      <c r="B177" s="33" t="s">
+        <v>344</v>
+      </c>
+      <c r="C177" s="30" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="31">
+        <v>901495569</v>
+      </c>
+      <c r="B178" s="33" t="s">
+        <v>346</v>
+      </c>
+      <c r="C178" s="30" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="31">
+        <v>900578105</v>
+      </c>
+      <c r="B179" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="C179" s="30" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="31">
+        <v>79785257</v>
+      </c>
+      <c r="B180" s="33" t="s">
+        <v>350</v>
+      </c>
+      <c r="C180" s="30" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="31">
+        <v>80727490</v>
+      </c>
+      <c r="B181" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="C181" s="30" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="31">
+        <v>809006003</v>
+      </c>
+      <c r="B182" s="37" t="s">
+        <v>354</v>
+      </c>
+      <c r="C182" s="34" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="38">
+        <v>832000464</v>
+      </c>
+      <c r="B183" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="C183" s="30" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="15.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="31">
+        <v>900267104</v>
+      </c>
+      <c r="B184" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="C184" s="39" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="31">
+        <v>830141132</v>
+      </c>
+      <c r="B185" s="33" t="s">
+        <v>360</v>
+      </c>
+      <c r="C185" s="30" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="31">
+        <v>890000600</v>
+      </c>
+      <c r="B186" s="32" t="s">
+        <v>362</v>
+      </c>
+      <c r="C186" s="30" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="31">
+        <v>899999063</v>
+      </c>
+      <c r="B187" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="C187" s="30" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="31">
+        <v>890801517</v>
+      </c>
+      <c r="B188" s="33" t="s">
+        <v>366</v>
+      </c>
+      <c r="C188" s="30" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="31">
+        <v>900482620</v>
+      </c>
+      <c r="B189" s="33" t="s">
+        <v>368</v>
+      </c>
+      <c r="C189" s="30" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="31">
+        <v>891856161</v>
+      </c>
+      <c r="B190" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="C190" s="30" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="31">
+        <v>892000458</v>
+      </c>
+      <c r="B191" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="C191" s="30" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="31">
+        <v>900451858</v>
+      </c>
+      <c r="B192" s="33" t="s">
+        <v>374</v>
+      </c>
+      <c r="C192" s="30" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="31">
+        <v>800219192</v>
+      </c>
+      <c r="B193" s="32" t="s">
+        <v>376</v>
+      </c>
+      <c r="C193" s="30" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="31">
+        <v>832002436</v>
+      </c>
+      <c r="B194" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="C194" s="30" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="31">
+        <v>832001966</v>
+      </c>
+      <c r="B195" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="C195" s="30" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="31">
+        <v>900841132</v>
+      </c>
+      <c r="B196" s="33" t="s">
+        <v>382</v>
+      </c>
+      <c r="C196" s="30" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="31">
+        <v>900588182</v>
+      </c>
+      <c r="B197" s="33" t="s">
+        <v>384</v>
+      </c>
+      <c r="C197" s="30" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="31">
+        <v>826002144</v>
+      </c>
+      <c r="B198" s="33" t="s">
+        <v>386</v>
+      </c>
+      <c r="C198" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="31">
+        <v>846003067</v>
+      </c>
+      <c r="B199" s="33" t="s">
+        <v>388</v>
+      </c>
+      <c r="C199" s="30" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="31">
+        <v>900241765</v>
+      </c>
+      <c r="B200" s="33" t="s">
+        <v>390</v>
+      </c>
+      <c r="C200" s="30" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="31">
+        <v>900521595</v>
+      </c>
+      <c r="B201" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="C201" s="30" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="31">
+        <v>816003270</v>
+      </c>
+      <c r="B202" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="C202" s="30" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="31">
+        <v>890704555</v>
+      </c>
+      <c r="B203" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="C203" s="30" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="31">
+        <v>900232301</v>
+      </c>
+      <c r="B204" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="C204" s="30" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="31">
+        <v>830143831</v>
+      </c>
+      <c r="B205" s="33" t="s">
+        <v>400</v>
+      </c>
+      <c r="C205" s="30" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="31">
+        <v>800099652</v>
+      </c>
+      <c r="B206" s="33" t="s">
+        <v>402</v>
+      </c>
+      <c r="C206" s="30" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="31">
+        <v>891800570</v>
+      </c>
+      <c r="B207" s="32" t="s">
+        <v>404</v>
+      </c>
+      <c r="C207" s="30" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="31">
+        <v>892099421</v>
+      </c>
+      <c r="B208" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="C208" s="30" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="31">
+        <v>900438068</v>
+      </c>
+      <c r="B209" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="C209" s="30" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="31">
+        <v>860037950</v>
+      </c>
+      <c r="B210" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="C210" s="30" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="31">
+        <v>890702408</v>
+      </c>
+      <c r="B211" s="33" t="s">
+        <v>412</v>
+      </c>
+      <c r="C211" s="34" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="31">
+        <v>1015392989</v>
+      </c>
+      <c r="B212" s="33" t="s">
+        <v>414</v>
+      </c>
+      <c r="C212" s="34" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="31">
+        <v>899999032</v>
+      </c>
+      <c r="B213" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="C213" s="30" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="31">
+        <v>881862576</v>
+      </c>
+      <c r="B214" s="32" t="s">
+        <v>418</v>
+      </c>
+      <c r="C214" s="30" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="31">
+        <v>52411325</v>
+      </c>
+      <c r="B215" s="33" t="s">
+        <v>420</v>
+      </c>
+      <c r="C215" s="30" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="31">
+        <v>901544725</v>
+      </c>
+      <c r="B216" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="C216" s="30" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="31">
+        <v>830009112</v>
+      </c>
+      <c r="B217" s="33" t="s">
+        <v>424</v>
+      </c>
+      <c r="C217" s="30" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="31">
+        <v>900614302</v>
+      </c>
+      <c r="B218" s="33" t="s">
+        <v>426</v>
+      </c>
+      <c r="C218" s="30" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="31">
+        <v>900055393</v>
+      </c>
+      <c r="B219" s="33" t="s">
+        <v>428</v>
+      </c>
+      <c r="C219" s="30" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="31">
+        <v>1020720272</v>
+      </c>
+      <c r="B220" s="33" t="s">
+        <v>430</v>
+      </c>
+      <c r="C220" s="30" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="31">
+        <v>844001355</v>
+      </c>
+      <c r="B221" s="33" t="s">
+        <v>432</v>
+      </c>
+      <c r="C221" s="30" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="31">
+        <v>801001440</v>
+      </c>
+      <c r="B222" s="32" t="s">
+        <v>434</v>
+      </c>
+      <c r="C222" s="30" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="31">
+        <v>800037021</v>
+      </c>
+      <c r="B223" s="33" t="s">
+        <v>436</v>
+      </c>
+      <c r="C223" s="30" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="31">
+        <v>19457462</v>
+      </c>
+      <c r="B224" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="C224" s="30" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="31">
+        <v>890802356</v>
+      </c>
+      <c r="B225" s="33" t="s">
+        <v>440</v>
+      </c>
+      <c r="C225" s="30" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="31">
+        <v>890801719</v>
+      </c>
+      <c r="B226" s="33" t="s">
+        <v>442</v>
+      </c>
+      <c r="C226" s="30" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="31">
+        <v>901408039</v>
+      </c>
+      <c r="B227" s="33" t="s">
+        <v>444</v>
+      </c>
+      <c r="C227" s="30" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="31">
+        <v>860002541</v>
+      </c>
+      <c r="B228" s="33" t="s">
+        <v>446</v>
+      </c>
+      <c r="C228" s="30" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="31">
+        <v>900342064</v>
+      </c>
+      <c r="B229" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="C229" s="30" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="31">
+        <v>890801035</v>
+      </c>
+      <c r="B230" s="33" t="s">
+        <v>450</v>
+      </c>
+      <c r="C230" s="30" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="31">
+        <v>802011972</v>
+      </c>
+      <c r="B231" s="33" t="s">
+        <v>452</v>
+      </c>
+      <c r="C231" s="30" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="31">
+        <v>900407200</v>
+      </c>
+      <c r="B232" s="33" t="s">
+        <v>454</v>
+      </c>
+      <c r="C232" s="30" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="31">
+        <v>813010145</v>
+      </c>
+      <c r="B233" s="33" t="s">
+        <v>456</v>
+      </c>
+      <c r="C233" s="30" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="31">
+        <v>860070301</v>
+      </c>
+      <c r="B234" s="33" t="s">
+        <v>458</v>
+      </c>
+      <c r="C234" s="30" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="31">
+        <v>890700666</v>
+      </c>
+      <c r="B235" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="C235" s="30" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="31">
+        <v>900308007</v>
+      </c>
+      <c r="B236" s="35" t="s">
+        <v>462</v>
+      </c>
+      <c r="C236" s="30" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="31">
+        <v>891856372</v>
+      </c>
+      <c r="B237" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="C237" s="30" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="31">
+        <v>800065396</v>
+      </c>
+      <c r="B238" s="33" t="s">
+        <v>466</v>
+      </c>
+      <c r="C238" s="30" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="31">
+        <v>901223046</v>
+      </c>
+      <c r="B239" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="C239" s="34" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="31">
+        <v>809010402</v>
+      </c>
+      <c r="B240" s="33" t="s">
+        <v>470</v>
+      </c>
+      <c r="C240" s="30" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="31">
+        <v>891800231</v>
+      </c>
+      <c r="B241" s="32" t="s">
+        <v>472</v>
+      </c>
+      <c r="C241" s="30" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="31">
+        <v>800119574</v>
+      </c>
+      <c r="B242" s="33" t="s">
+        <v>474</v>
+      </c>
+      <c r="C242" s="30" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="31">
+        <v>80170827</v>
+      </c>
+      <c r="B243" s="33" t="s">
+        <v>476</v>
+      </c>
+      <c r="C243" s="30" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="31">
+        <v>10286175</v>
+      </c>
+      <c r="B244" s="32" t="s">
+        <v>478</v>
+      </c>
+      <c r="C244" s="30" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="31">
+        <v>900454188</v>
+      </c>
+      <c r="B245" s="35" t="s">
+        <v>480</v>
+      </c>
+      <c r="C245" s="30" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="31">
+        <v>900057926</v>
+      </c>
+      <c r="B246" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="C246" s="30" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="31">
+        <v>844001911</v>
+      </c>
+      <c r="B247" s="33" t="s">
+        <v>484</v>
+      </c>
+      <c r="C247" s="30" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="31">
+        <v>900526144</v>
+      </c>
+      <c r="B248" s="33" t="s">
+        <v>486</v>
+      </c>
+      <c r="C248" s="30" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="31">
+        <v>900828394</v>
+      </c>
+      <c r="B249" s="35" t="s">
+        <v>488</v>
+      </c>
+      <c r="C249" s="30" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A250" s="31">
+        <v>844001287</v>
+      </c>
+      <c r="B250" s="33" t="s">
+        <v>490</v>
+      </c>
+      <c r="C250" s="30" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="31">
+        <v>900431131</v>
+      </c>
+      <c r="B251" s="33" t="s">
+        <v>492</v>
+      </c>
+      <c r="C251" s="30" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A252" s="31">
+        <v>800037979</v>
+      </c>
+      <c r="B252" s="35" t="s">
+        <v>494</v>
+      </c>
+      <c r="C252" s="30" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A253" s="31">
+        <v>890601210</v>
+      </c>
+      <c r="B253" s="32" t="s">
+        <v>496</v>
+      </c>
+      <c r="C253" s="30" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A254" s="31">
+        <v>801001969</v>
+      </c>
+      <c r="B254" s="32" t="s">
+        <v>498</v>
+      </c>
+      <c r="C254" s="30" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A255" s="31">
+        <v>890801944</v>
+      </c>
+      <c r="B255" s="32" t="s">
+        <v>500</v>
+      </c>
+      <c r="C255" s="30" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A256" s="31">
+        <v>19419315</v>
+      </c>
+      <c r="B256" s="33" t="s">
+        <v>502</v>
+      </c>
+      <c r="C256" s="30" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A257" s="31">
+        <v>900371613</v>
+      </c>
+      <c r="B257" s="32" t="s">
+        <v>504</v>
+      </c>
+      <c r="C257" s="30" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A258" s="31">
+        <v>860015905</v>
+      </c>
+      <c r="B258" s="33" t="s">
+        <v>506</v>
+      </c>
+      <c r="C258" s="34" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A259" s="31">
+        <v>900488920</v>
+      </c>
+      <c r="B259" s="35" t="s">
+        <v>508</v>
+      </c>
+      <c r="C259" s="30" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A260" s="31">
+        <v>810000913</v>
+      </c>
+      <c r="B260" s="35" t="s">
+        <v>510</v>
+      </c>
+      <c r="C260" s="30" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A261" s="31">
+        <v>900471504</v>
+      </c>
+      <c r="B261" s="33" t="s">
+        <v>512</v>
+      </c>
+      <c r="C261" s="34" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="31">
+        <v>844003225</v>
+      </c>
+      <c r="B262" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="C262" s="30" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A263" s="31">
+        <v>830075393</v>
+      </c>
+      <c r="B263" s="33" t="s">
+        <v>516</v>
+      </c>
+      <c r="C263" s="34" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A264" s="31">
+        <v>900058218</v>
+      </c>
+      <c r="B264" s="32" t="s">
+        <v>518</v>
+      </c>
+      <c r="C264" s="30" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A265" s="31">
+        <v>901295822</v>
+      </c>
+      <c r="B265" s="33" t="s">
+        <v>520</v>
+      </c>
+      <c r="C265" s="30" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A266" s="31">
+        <v>900381555</v>
+      </c>
+      <c r="B266" s="32" t="s">
+        <v>522</v>
+      </c>
+      <c r="C266" s="30" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A267" s="31">
+        <v>830117846</v>
+      </c>
+      <c r="B267" s="33" t="s">
+        <v>524</v>
+      </c>
+      <c r="C267" s="34" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A268" s="31">
+        <v>901017982</v>
+      </c>
+      <c r="B268" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="C268" s="30" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A269" s="31">
+        <v>900314301</v>
+      </c>
+      <c r="B269" s="32" t="s">
+        <v>528</v>
+      </c>
+      <c r="C269" s="30" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A270" s="31">
+        <v>901881050</v>
+      </c>
+      <c r="B270" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="C270" s="30" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A271" s="31">
+        <v>891180134</v>
+      </c>
+      <c r="B271" s="32" t="s">
+        <v>532</v>
+      </c>
+      <c r="C271" s="30" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A272" s="31">
+        <v>900407111</v>
+      </c>
+      <c r="B272" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="C272" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A273" s="31">
+        <v>900112820</v>
+      </c>
+      <c r="B273" s="32" t="s">
+        <v>536</v>
+      </c>
+      <c r="C273" s="30" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A274" s="40">
+        <v>901169422</v>
+      </c>
+      <c r="B274" s="33" t="s">
+        <v>538</v>
+      </c>
+      <c r="C274" s="30" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A275" s="31">
+        <v>900108793</v>
+      </c>
+      <c r="B275" s="32" t="s">
+        <v>540</v>
+      </c>
+      <c r="C275" s="30" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A276" s="31">
+        <v>900576170</v>
+      </c>
+      <c r="B276" s="33" t="s">
+        <v>542</v>
+      </c>
+      <c r="C276" s="30" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A277" s="31">
+        <v>891180268</v>
+      </c>
+      <c r="B277" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="C277" s="30" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A278" s="31">
+        <v>900678145</v>
+      </c>
+      <c r="B278" s="32" t="s">
+        <v>546</v>
+      </c>
+      <c r="C278" s="30" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A279" s="31">
+        <v>900627725</v>
+      </c>
+      <c r="B279" s="33" t="s">
+        <v>548</v>
+      </c>
+      <c r="C279" s="30" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A280" s="31">
+        <v>891411743</v>
+      </c>
+      <c r="B280" s="33" t="s">
+        <v>550</v>
+      </c>
+      <c r="C280" s="30" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A281" s="31">
+        <v>900077520</v>
+      </c>
+      <c r="B281" s="33" t="s">
+        <v>552</v>
+      </c>
+      <c r="C281" s="34" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A282" s="31">
+        <v>900958564</v>
+      </c>
+      <c r="B282" s="32" t="s">
+        <v>554</v>
+      </c>
+      <c r="C282" s="30" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A283" s="31">
+        <v>800200789</v>
+      </c>
+      <c r="B283" s="33" t="s">
+        <v>556</v>
+      </c>
+      <c r="C283" s="30" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A284" s="31">
+        <v>900061048</v>
+      </c>
+      <c r="B284" s="33" t="s">
+        <v>558</v>
+      </c>
+      <c r="C284" s="30" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A285" s="31">
+        <v>901127904</v>
+      </c>
+      <c r="B285" s="33" t="s">
+        <v>560</v>
+      </c>
+      <c r="C285" s="30" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A286" s="31">
+        <v>890801562</v>
+      </c>
+      <c r="B286" s="32" t="s">
+        <v>562</v>
+      </c>
+      <c r="C286" s="30" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A287" s="31">
+        <v>80055710</v>
+      </c>
+      <c r="B287" s="32" t="s">
+        <v>564</v>
+      </c>
+      <c r="C287" s="30" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A288" s="31">
+        <v>79442674</v>
+      </c>
+      <c r="B288" s="33" t="s">
+        <v>566</v>
+      </c>
+      <c r="C288" s="30" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A289" s="31">
+        <v>891856507</v>
+      </c>
+      <c r="B289" s="32" t="s">
+        <v>568</v>
+      </c>
+      <c r="C289" s="30" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A290" s="31">
+        <v>900231829</v>
+      </c>
+      <c r="B290" s="33" t="s">
+        <v>570</v>
+      </c>
+      <c r="C290" s="30" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A291" s="31">
+        <v>900171988</v>
+      </c>
+      <c r="B291" s="32" t="s">
+        <v>572</v>
+      </c>
+      <c r="C291" s="30" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A292" s="31">
+        <v>891180098</v>
+      </c>
+      <c r="B292" s="33" t="s">
+        <v>574</v>
+      </c>
+      <c r="C292" s="30" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A293" s="31">
+        <v>845000038</v>
+      </c>
+      <c r="B293" s="33" t="s">
+        <v>576</v>
+      </c>
+      <c r="C293" s="30" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A294" s="31">
+        <v>900817788</v>
+      </c>
+      <c r="B294" s="32" t="s">
+        <v>578</v>
+      </c>
+      <c r="C294" s="30" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A295" s="31">
+        <v>899999147</v>
+      </c>
+      <c r="B295" s="32" t="s">
+        <v>580</v>
+      </c>
+      <c r="C295" s="30" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A296" s="31">
+        <v>900419180</v>
+      </c>
+      <c r="B296" s="32" t="s">
+        <v>582</v>
+      </c>
+      <c r="C296" s="30" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="31">
+        <v>830119200</v>
+      </c>
+      <c r="B297" s="33" t="s">
+        <v>584</v>
+      </c>
+      <c r="C297" s="30" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A298" s="31">
+        <v>890801495</v>
+      </c>
+      <c r="B298" s="33" t="s">
+        <v>586</v>
+      </c>
+      <c r="C298" s="30" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A299" s="31">
+        <v>900582598</v>
+      </c>
+      <c r="B299" s="32" t="s">
+        <v>588</v>
+      </c>
+      <c r="C299" s="30" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A300" s="31">
+        <v>890802036</v>
+      </c>
+      <c r="B300" s="32" t="s">
+        <v>590</v>
+      </c>
+      <c r="C300" s="30" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A301" s="31">
+        <v>900462440</v>
+      </c>
+      <c r="B301" s="33" t="s">
+        <v>592</v>
+      </c>
+      <c r="C301" s="30" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A302" s="31">
+        <v>846000474</v>
+      </c>
+      <c r="B302" s="32" t="s">
+        <v>594</v>
+      </c>
+      <c r="C302" s="30" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A303" s="31">
+        <v>800000118</v>
+      </c>
+      <c r="B303" s="32" t="s">
+        <v>596</v>
+      </c>
+      <c r="C303" s="30" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A304" s="31">
+        <v>900211468</v>
+      </c>
+      <c r="B304" s="32" t="s">
+        <v>598</v>
+      </c>
+      <c r="C304" s="30" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A305" s="31">
+        <v>891855438</v>
+      </c>
+      <c r="B305" s="32" t="s">
+        <v>600</v>
+      </c>
+      <c r="C305" s="30" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A306" s="31">
+        <v>19364579</v>
+      </c>
+      <c r="B306" s="33" t="s">
+        <v>602</v>
+      </c>
+      <c r="C306" s="30" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A307" s="31">
+        <v>900004059</v>
+      </c>
+      <c r="B307" s="32" t="s">
+        <v>604</v>
+      </c>
+      <c r="C307" s="34" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A308" s="31">
+        <v>846003357</v>
+      </c>
+      <c r="B308" s="32" t="s">
+        <v>606</v>
+      </c>
+      <c r="C308" s="30" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A309" s="31">
+        <v>901457374</v>
+      </c>
+      <c r="B309" s="33" t="s">
+        <v>608</v>
+      </c>
+      <c r="C309" s="30" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A310" s="31">
+        <v>830005028</v>
+      </c>
+      <c r="B310" s="32" t="s">
+        <v>610</v>
+      </c>
+      <c r="C310" s="30" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A311" s="31">
+        <v>900606412</v>
+      </c>
+      <c r="B311" s="32" t="s">
+        <v>612</v>
+      </c>
+      <c r="C311" s="30" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A312" s="31">
+        <v>830113849</v>
+      </c>
+      <c r="B312" s="33" t="s">
+        <v>614</v>
+      </c>
+      <c r="C312" s="30" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A313" s="31">
+        <v>900232628</v>
+      </c>
+      <c r="B313" s="32" t="s">
+        <v>616</v>
+      </c>
+      <c r="C313" s="30" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A314" s="31">
+        <v>890706823</v>
+      </c>
+      <c r="B314" s="32" t="s">
+        <v>618</v>
+      </c>
+      <c r="C314" s="30" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A315" s="31">
+        <v>901105417</v>
+      </c>
+      <c r="B315" s="33" t="s">
+        <v>620</v>
+      </c>
+      <c r="C315" s="30" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A316" s="31">
+        <v>800037202</v>
+      </c>
+      <c r="B316" s="33" t="s">
+        <v>622</v>
+      </c>
+      <c r="C316" s="30" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A317" s="38">
+        <v>80412859</v>
+      </c>
+      <c r="B317" s="33" t="s">
+        <v>624</v>
+      </c>
+      <c r="C317" s="30" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A318" s="31">
+        <v>800180553</v>
+      </c>
+      <c r="B318" s="42" t="s">
+        <v>626</v>
+      </c>
+      <c r="C318" s="41" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A319" s="31">
+        <v>891411381</v>
+      </c>
+      <c r="B319" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="C319" s="30" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A320" s="31">
+        <v>814003448</v>
+      </c>
+      <c r="B320" s="32" t="s">
+        <v>630</v>
+      </c>
+      <c r="C320" s="30" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A321" s="31">
+        <v>891180026</v>
+      </c>
+      <c r="B321" s="33" t="s">
+        <v>632</v>
+      </c>
+      <c r="C321" s="30" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A322" s="31">
+        <v>900233110</v>
+      </c>
+      <c r="B322" s="33" t="s">
+        <v>634</v>
+      </c>
+      <c r="C322" s="30" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A323" s="31">
+        <v>860013570</v>
+      </c>
+      <c r="B323" s="32" t="s">
+        <v>636</v>
+      </c>
+      <c r="C323" s="30" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A324" s="31">
+        <v>901652147</v>
+      </c>
+      <c r="B324" s="33" t="s">
+        <v>638</v>
+      </c>
+      <c r="C324" s="30" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A325" s="31">
+        <v>901439163</v>
+      </c>
+      <c r="B325" s="33" t="s">
+        <v>640</v>
+      </c>
+      <c r="C325" s="30" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A326" s="31">
+        <v>822000946</v>
+      </c>
+      <c r="B326" s="32" t="s">
+        <v>642</v>
+      </c>
+      <c r="C326" s="30" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A327" s="31">
+        <v>810001466</v>
+      </c>
+      <c r="B327" s="32" t="s">
+        <v>644</v>
+      </c>
+      <c r="C327" s="30" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A328" s="31">
+        <v>900547903</v>
+      </c>
+      <c r="B328" s="33" t="s">
+        <v>646</v>
+      </c>
+      <c r="C328" s="30" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A329" s="31">
+        <v>800228215</v>
+      </c>
+      <c r="B329" s="32" t="s">
+        <v>648</v>
+      </c>
+      <c r="C329" s="30" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A330" s="31">
+        <v>890802978</v>
+      </c>
+      <c r="B330" s="33" t="s">
+        <v>650</v>
+      </c>
+      <c r="C330" s="34" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A331" s="31">
+        <v>800135582</v>
+      </c>
+      <c r="B331" s="32" t="s">
+        <v>652</v>
+      </c>
+      <c r="C331" s="30" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A332" s="31">
+        <v>900364721</v>
+      </c>
+      <c r="B332" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="C332" s="30" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A333" s="31">
+        <v>899999123</v>
+      </c>
+      <c r="B333" s="32" t="s">
+        <v>656</v>
+      </c>
+      <c r="C333" s="30" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A334" s="31">
+        <v>890801099</v>
+      </c>
+      <c r="B334" s="33" t="s">
+        <v>658</v>
+      </c>
+      <c r="C334" s="30" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A335" s="31">
+        <v>830018305</v>
+      </c>
+      <c r="B335" s="32" t="s">
+        <v>660</v>
+      </c>
+      <c r="C335" s="30" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A336" s="31">
+        <v>809001482</v>
+      </c>
+      <c r="B336" s="33" t="s">
+        <v>662</v>
+      </c>
+      <c r="C336" s="30" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A337" s="31">
+        <v>900685235</v>
+      </c>
+      <c r="B337" s="32" t="s">
+        <v>664</v>
+      </c>
+      <c r="C337" s="30" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A338" s="31">
+        <v>800191101</v>
+      </c>
+      <c r="B338" s="32" t="s">
+        <v>666</v>
+      </c>
+      <c r="C338" s="30" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A339" s="31">
+        <v>891409981</v>
+      </c>
+      <c r="B339" s="33" t="s">
+        <v>668</v>
+      </c>
+      <c r="C339" s="30" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A340" s="31">
+        <v>900073806</v>
+      </c>
+      <c r="B340" s="33" t="s">
+        <v>670</v>
+      </c>
+      <c r="C340" s="30" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A341" s="31">
+        <v>900493064</v>
+      </c>
+      <c r="B341" s="32" t="s">
+        <v>672</v>
+      </c>
+      <c r="C341" s="30" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A342" s="31">
+        <v>800231235</v>
+      </c>
+      <c r="B342" s="33" t="s">
+        <v>674</v>
+      </c>
+      <c r="C342" s="30" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A343" s="31">
+        <v>860007373</v>
+      </c>
+      <c r="B343" s="32" t="s">
+        <v>676</v>
+      </c>
+      <c r="C343" s="30" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A344" s="31">
+        <v>900848340</v>
+      </c>
+      <c r="B344" s="32" t="s">
+        <v>678</v>
+      </c>
+      <c r="C344" s="30" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A345" s="31">
+        <v>900115642</v>
+      </c>
+      <c r="B345" s="32" t="s">
+        <v>680</v>
+      </c>
+      <c r="C345" s="30" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A346" s="31">
+        <v>79533241</v>
+      </c>
+      <c r="B346" s="32" t="s">
+        <v>682</v>
+      </c>
+      <c r="C346" s="30" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A347" s="31">
+        <v>830502282</v>
+      </c>
+      <c r="B347" s="32" t="s">
+        <v>684</v>
+      </c>
+      <c r="C347" s="30" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A348" s="31">
+        <v>900081643</v>
+      </c>
+      <c r="B348" s="33" t="s">
+        <v>686</v>
+      </c>
+      <c r="C348" s="34" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A349" s="31">
+        <v>891855039</v>
+      </c>
+      <c r="B349" s="32" t="s">
+        <v>688</v>
+      </c>
+      <c r="C349" s="30" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A350" s="31">
+        <v>805017681</v>
+      </c>
+      <c r="B350" s="33" t="s">
+        <v>690</v>
+      </c>
+      <c r="C350" s="30" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A351" s="31">
+        <v>820002248</v>
+      </c>
+      <c r="B351" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="C351" s="30" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A352" s="31">
+        <v>860024026</v>
+      </c>
+      <c r="B352" s="32" t="s">
+        <v>694</v>
+      </c>
+      <c r="C352" s="30" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A353" s="31">
+        <v>71394225</v>
+      </c>
+      <c r="B353" s="33" t="s">
+        <v>696</v>
+      </c>
+      <c r="C353" s="34" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A354" s="31">
+        <v>832008321</v>
+      </c>
+      <c r="B354" s="32" t="s">
+        <v>698</v>
+      </c>
+      <c r="C354" s="30" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A355" s="31">
+        <v>901632467</v>
+      </c>
+      <c r="B355" s="33" t="s">
+        <v>700</v>
+      </c>
+      <c r="C355" s="34" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A356" s="38">
+        <v>891180117</v>
+      </c>
+      <c r="B356" s="33" t="s">
+        <v>702</v>
+      </c>
+      <c r="C356" s="30" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" ht="15.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A357" s="31">
+        <v>900435790</v>
+      </c>
+      <c r="B357" s="32" t="s">
+        <v>738</v>
+      </c>
+      <c r="C357" s="39" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A358" s="31">
+        <v>900759329</v>
+      </c>
+      <c r="B358" s="33" t="s">
+        <v>704</v>
+      </c>
+      <c r="C358" s="30" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A359" s="31">
+        <v>891800644</v>
+      </c>
+      <c r="B359" s="32" t="s">
+        <v>706</v>
+      </c>
+      <c r="C359" s="30" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A360" s="31">
+        <v>800254132</v>
+      </c>
+      <c r="B360" s="32" t="s">
+        <v>708</v>
+      </c>
+      <c r="C360" s="30" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A361" s="31">
+        <v>899999158</v>
+      </c>
+      <c r="B361" s="32" t="s">
+        <v>710</v>
+      </c>
+      <c r="C361" s="30" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A362" s="31">
+        <v>79624744</v>
+      </c>
+      <c r="B362" s="32" t="s">
+        <v>712</v>
+      </c>
+      <c r="C362" s="30" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A363" s="31">
+        <v>891409390</v>
+      </c>
+      <c r="B363" s="33" t="s">
+        <v>714</v>
+      </c>
+      <c r="C363" s="30" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A364" s="31">
+        <v>890680014</v>
+      </c>
+      <c r="B364" s="32" t="s">
+        <v>716</v>
+      </c>
+      <c r="C364" s="30" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A365" s="31">
+        <v>809006690</v>
+      </c>
+      <c r="B365" s="33" t="s">
+        <v>718</v>
+      </c>
+      <c r="C365" s="30" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A366" s="31">
+        <v>900213617</v>
+      </c>
+      <c r="B366" s="33" t="s">
+        <v>720</v>
+      </c>
+      <c r="C366" s="30" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A367" s="31">
+        <v>900423816</v>
+      </c>
+      <c r="B367" s="32" t="s">
+        <v>722</v>
+      </c>
+      <c r="C367" s="30" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A368" s="31">
+        <v>860015929</v>
+      </c>
+      <c r="B368" s="32" t="s">
+        <v>724</v>
+      </c>
+      <c r="C368" s="30" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A369" s="31">
+        <v>890806490</v>
+      </c>
+      <c r="B369" s="32" t="s">
+        <v>726</v>
+      </c>
+      <c r="C369" s="30" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A370" s="31">
+        <v>860006626</v>
+      </c>
+      <c r="B370" s="32" t="s">
+        <v>728</v>
+      </c>
+      <c r="C370" s="30" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A371" s="31">
+        <v>813005295</v>
+      </c>
+      <c r="B371" s="32" t="s">
+        <v>730</v>
+      </c>
+      <c r="C371" s="30" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A372" s="44">
+        <v>846001425</v>
+      </c>
+      <c r="B372" s="45" t="s">
+        <v>732</v>
+      </c>
+      <c r="C372" s="43" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A373" s="31">
+        <v>800139366</v>
+      </c>
+      <c r="B373" s="32" t="s">
+        <v>734</v>
+      </c>
+      <c r="C373" s="30" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A374" s="31">
+        <v>816005003</v>
+      </c>
+      <c r="B374" s="32" t="s">
+        <v>736</v>
+      </c>
+      <c r="C374" s="30" t="s">
+        <v>735</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C374" xr:uid="{CCA89662-6597-440B-93CF-3E4C4E5F4B95}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="ORTOPROTESICOS ESPECIALIZADOS S.A.S."/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A375:A1048576 C375:C1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C316:C343 C2:C293 A2:A374">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C344 C354">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>

--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/SOPORTES DE MEDICION/soportes de medicon.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/SOPORTES DE MEDICION/soportes de medicon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\SOPORTES DE MEDICION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AGS\DESARROLLO\GITHUB\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\SOPORTES DE MEDICION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE10DEBF-3D5E-4B24-B3A6-DD5142306A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B168DAE8-BD46-4F5F-AD18-D4488C684B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Hoja2" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Hoja1!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Hoja1!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja3!$A$1:$C$374</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -30,16 +30,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="786">
   <si>
     <t>NIT</t>
   </si>
@@ -2258,15 +2259,9 @@
     <t>GESTION MEDICA EN SALUD SAS</t>
   </si>
   <si>
-    <t>CEDULA PACIENTE</t>
-  </si>
-  <si>
     <t>Si</t>
   </si>
   <si>
-    <t>NOMBRE DEL PACIENTE </t>
-  </si>
-  <si>
     <t>0092-2026</t>
   </si>
   <si>
@@ -2315,65 +2310,101 @@
     <t>Periodo evaluado</t>
   </si>
   <si>
-    <t xml:space="preserve">LUIS ALBERTO MENDEZ TORRES </t>
-  </si>
-  <si>
-    <t>si</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDWIN LEANDRO GALLEGO CARDONA </t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USUARIO INDICA QUE ESTAN EN PROCESO DE FABRICACION DE LA PROTESIS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOSE ELIAS SANABRIA PULIDO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">USUARIO INDICA QUE EL 5 MAYO TIENE JUNTA DE PROTESIS POR LO CUAL 5 DIAS ANTES LE HACEN EL MONTAJE DEL KIT </t>
-  </si>
-  <si>
-    <t>FLOWER  MOLINA  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">USURIO INDICA QUE NO HUBO ATENCION, YA QUE EN LA IPS LE HICIERON SABER QUE ESTA JUNTA NO EXISTE PIDIO SOPORTE YA QUE NO VIVE EN BOGOTA Y LA IPS NO LE GENERO ESTE SOPORTE Y HASTA EL DIA DE HOY NO LE HAN DADO RESPUESTA </t>
-  </si>
-  <si>
-    <t>MARZO 2026.</t>
-  </si>
-  <si>
-    <t>El servicio o entrega ya fue realizado</t>
-  </si>
-  <si>
-    <t>¿LA PRÓTESIS, ORTESIS Y/O INSUMO LE HA GENERADO ALGUNA LESIÓN DURANTE SU USO?</t>
-  </si>
-  <si>
-    <t>4. OPORTUNIDAD EN LA ATENCIÓN PRESTADA POR LA IPS</t>
-  </si>
-  <si>
-    <t>5. CALIDAD EN EL SERVICIO PRESTADO POR PARTE DEL PROFESIONAL Y/O PERSONAL ADMINISTRATIVO</t>
-  </si>
-  <si>
-    <t>6. INFRAESTRUCTURA Y DOTACIÓN DE LAS INSTALACIONES DE LA IPS</t>
-  </si>
-  <si>
-    <t>Observaciones, por favor poner una observacion puntual que notifique el usuario.</t>
-  </si>
-  <si>
-    <t>LA PRÓTESIS,ORTESIS Y/O INSUMO ENTREGADO CUMPLE CON LAS ESPECIFICACIONES TÉCNICAS DADAS   POR EL MÉDICO TRATANTE</t>
+    <t>ERIKA ANDREA CHAVES RIVERA</t>
+  </si>
+  <si>
+    <t>JHON FREDY RAMIREZ TANGARIFE</t>
+  </si>
+  <si>
+    <t>YAMIL ANTONIO JIMENEZ DIAZ</t>
+  </si>
+  <si>
+    <t>JUAN GABRIEL NIZO SANABRIA</t>
+  </si>
+  <si>
+    <t>VICTOR ANDRES SOTO HENAO</t>
+  </si>
+  <si>
+    <t>JUAN HEYLER LOPEZ MOSQUERA</t>
+  </si>
+  <si>
+    <t>VIVIANA LOPEZ PATIÑO</t>
+  </si>
+  <si>
+    <t>CHRISTIAN FERNANDO LONDOÑO ARIAS</t>
+  </si>
+  <si>
+    <t>MARIA MARGOTH OSPINA ARROYAVE</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS CAICEDO RAMIREZ</t>
+  </si>
+  <si>
+    <t>DARWIN ANDRES GONZALEZ RIVERA</t>
+  </si>
+  <si>
+    <t>ANDRES ALFONSO ZAMORA GOMEZ</t>
+  </si>
+  <si>
+    <t>GUILLERMO MORALES BARON</t>
+  </si>
+  <si>
+    <t>CALVO SAMUEL VARGAS</t>
+  </si>
+  <si>
+    <t>JOSE DELACRUZ AYALA BUENO</t>
+  </si>
+  <si>
+    <t>LEIDER ENRIQUE LLAMAS DIAZ</t>
+  </si>
+  <si>
+    <t>YOLANDA CAICEDO PRADO</t>
+  </si>
+  <si>
+    <t>MARIA DELSOCORRO GUASCA MORENO</t>
+  </si>
+  <si>
+    <t>YONY RAFAEL PALACIN ALTAHONA</t>
+  </si>
+  <si>
+    <t>CLARA INES AGUDELO HENAO</t>
+  </si>
+  <si>
+    <t>CARLOS ANDRES PEREZ CASTRO</t>
+  </si>
+  <si>
+    <t>ORLANDO CASTRO VEGA</t>
+  </si>
+  <si>
+    <t>"CEDULA PACIENTE "</t>
+  </si>
+  <si>
+    <t>NOMBRE DEL PACIENTE</t>
+  </si>
+  <si>
+    <t>Teniendo en cuenta su experiencia con la atención brindada por el proveedor, por favor califique en una escala del 1 al 5 la atención recibida en donde 1 es “Malo” y 5 es “Excelente” los siguientes at</t>
+  </si>
+  <si>
+    <t>Infraestructura y dotación de las instalaciones de la IPS o calidad de llamada.</t>
+  </si>
+  <si>
+    <t>Calidad en el servicio prestado por parte del profesional de salud</t>
+  </si>
+  <si>
+    <t>Teniendo en cuenta la respuesta anterior, por favor elija una de las siguientes opciones indicando el motivo por el cual no ha solicitado la programación del servicio.</t>
+  </si>
+  <si>
+    <t>I TRIMESTRE</t>
+  </si>
+  <si>
+    <t>Para la siguiente pregunta, por favor responda SI o NO  ¿Tuvo servicio con el prestador?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2541,7 +2572,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2677,6 +2708,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3014,8 +3051,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" style="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" style="26" bestFit="1" customWidth="1"/>
@@ -3025,150 +3062,699 @@
     <col min="10" max="10" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="27" customFormat="1" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:10" ht="150">
+      <c r="A1" s="47" t="s">
+        <v>778</v>
+      </c>
+      <c r="B1" s="47" t="s">
+        <v>779</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="D1" s="47" t="s">
+        <v>785</v>
+      </c>
+      <c r="E1" s="47" t="s">
+        <v>780</v>
+      </c>
+      <c r="F1" s="47" t="s">
+        <v>781</v>
+      </c>
+      <c r="G1" s="47" t="s">
+        <v>782</v>
+      </c>
+      <c r="H1" s="47" t="s">
+        <v>783</v>
+      </c>
+      <c r="I1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="27" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="30">
+      <c r="A2" s="46">
+        <v>1080000000</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>756</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D2" s="47" t="s">
         <v>739</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>741</v>
-      </c>
-      <c r="C1" s="28" t="s">
+      <c r="E2" s="47">
+        <v>5</v>
+      </c>
+      <c r="F2" s="47">
+        <v>5</v>
+      </c>
+      <c r="G2" s="47">
+        <v>5</v>
+      </c>
+      <c r="H2" s="47"/>
+      <c r="I2" t="s">
+        <v>421</v>
+      </c>
+      <c r="J2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="30">
+      <c r="A3" s="47">
+        <v>10189175</v>
+      </c>
+      <c r="B3" s="47" t="s">
         <v>757</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="C3" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D3" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E3" s="47">
+        <v>5</v>
+      </c>
+      <c r="F3" s="47">
+        <v>5</v>
+      </c>
+      <c r="G3" s="47">
+        <v>5</v>
+      </c>
+      <c r="H3" s="47"/>
+      <c r="I3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="30">
+      <c r="A4" s="47">
+        <v>12523155</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>758</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E4" s="47">
+        <v>5</v>
+      </c>
+      <c r="F4" s="47">
+        <v>5</v>
+      </c>
+      <c r="G4" s="47">
+        <v>5</v>
+      </c>
+      <c r="H4" s="47"/>
+      <c r="I4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30">
+      <c r="A5" s="46">
+        <v>1080000000</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>759</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E5" s="47">
+        <v>5</v>
+      </c>
+      <c r="F5" s="47">
+        <v>5</v>
+      </c>
+      <c r="G5" s="47">
+        <v>5</v>
+      </c>
+      <c r="H5" s="47"/>
+      <c r="I5" t="s">
+        <v>697</v>
+      </c>
+      <c r="J5" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="30">
+      <c r="A6" s="47">
+        <v>16229103</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>760</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E6" s="47">
+        <v>5</v>
+      </c>
+      <c r="F6" s="47">
+        <v>5</v>
+      </c>
+      <c r="G6" s="47">
+        <v>5</v>
+      </c>
+      <c r="H6" s="47"/>
+      <c r="I6" t="s">
+        <v>735</v>
+      </c>
+      <c r="J6" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="30">
+      <c r="A7" s="46">
+        <v>1080000000</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>761</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E7" s="47">
+        <v>5</v>
+      </c>
+      <c r="F7" s="47">
+        <v>5</v>
+      </c>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" t="s">
+        <v>735</v>
+      </c>
+      <c r="J7" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="30">
+      <c r="A8" s="47">
+        <v>43463667</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>762</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E8" s="47">
+        <v>5</v>
+      </c>
+      <c r="F8" s="47">
+        <v>5</v>
+      </c>
+      <c r="G8" s="47">
+        <v>5</v>
+      </c>
+      <c r="H8" s="47"/>
+      <c r="I8" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30">
+      <c r="A9" s="46">
+        <v>1090000000</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>763</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E9" s="47">
+        <v>5</v>
+      </c>
+      <c r="F9" s="47">
+        <v>5</v>
+      </c>
+      <c r="G9" s="47">
+        <v>5</v>
+      </c>
+      <c r="H9" s="47"/>
+      <c r="I9" t="s">
+        <v>89</v>
+      </c>
+      <c r="J9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="30">
+      <c r="A10" s="47">
+        <v>42732677</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>764</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E10" s="47">
+        <v>5</v>
+      </c>
+      <c r="F10" s="47">
+        <v>3</v>
+      </c>
+      <c r="G10" s="47">
+        <v>3</v>
+      </c>
+      <c r="H10" s="47"/>
+      <c r="I10" t="s">
+        <v>665</v>
+      </c>
+      <c r="J10" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="30">
+      <c r="A11" s="47">
+        <v>96355191</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>765</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E11" s="47">
+        <v>4</v>
+      </c>
+      <c r="F11" s="47">
+        <v>4</v>
+      </c>
+      <c r="G11" s="47">
+        <v>4</v>
+      </c>
+      <c r="H11" s="47"/>
+      <c r="I11" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="30">
+      <c r="A12" s="47">
+        <v>75094270</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>766</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E12" s="47">
+        <v>5</v>
+      </c>
+      <c r="F12" s="47">
+        <v>5</v>
+      </c>
+      <c r="G12" s="47">
+        <v>5</v>
+      </c>
+      <c r="H12" s="47"/>
+      <c r="I12" t="s">
+        <v>733</v>
+      </c>
+      <c r="J12" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="30">
+      <c r="A13" s="46">
+        <v>1080000000</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>767</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E13" s="47">
+        <v>5</v>
+      </c>
+      <c r="F13" s="47">
+        <v>5</v>
+      </c>
+      <c r="G13" s="47">
+        <v>5</v>
+      </c>
+      <c r="H13" s="47"/>
+      <c r="I13" t="s">
+        <v>709</v>
+      </c>
+      <c r="J13" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30">
+      <c r="A14" s="47">
+        <v>75034165</v>
+      </c>
+      <c r="B14" s="47" t="s">
+        <v>768</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E14" s="47">
+        <v>5</v>
+      </c>
+      <c r="F14" s="47">
+        <v>5</v>
+      </c>
+      <c r="G14" s="47">
+        <v>5</v>
+      </c>
+      <c r="H14" s="47"/>
+      <c r="I14" t="s">
+        <v>561</v>
+      </c>
+      <c r="J14" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="30">
+      <c r="A15" s="46">
+        <v>1060000000</v>
+      </c>
+      <c r="B15" s="47" t="s">
         <v>769</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="C15" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E15" s="47">
+        <v>5</v>
+      </c>
+      <c r="F15" s="47">
+        <v>5</v>
+      </c>
+      <c r="G15" s="47">
+        <v>5</v>
+      </c>
+      <c r="H15" s="47"/>
+      <c r="I15" t="s">
+        <v>273</v>
+      </c>
+      <c r="J15" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="30">
+      <c r="A16" s="47">
+        <v>15929970</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>770</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E16" s="47">
+        <v>5</v>
+      </c>
+      <c r="F16" s="47">
+        <v>3</v>
+      </c>
+      <c r="G16" s="47">
+        <v>4</v>
+      </c>
+      <c r="H16" s="47"/>
+      <c r="I16" t="s">
+        <v>273</v>
+      </c>
+      <c r="J16" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="30">
+      <c r="A17" s="46">
+        <v>1070000000</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>771</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E17" s="47">
+        <v>5</v>
+      </c>
+      <c r="F17" s="47">
+        <v>5</v>
+      </c>
+      <c r="G17" s="47">
+        <v>5</v>
+      </c>
+      <c r="H17" s="47"/>
+      <c r="I17" t="s">
+        <v>437</v>
+      </c>
+      <c r="J17" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="30">
+      <c r="A18" s="47">
+        <v>25364210</v>
+      </c>
+      <c r="B18" s="47" t="s">
+        <v>772</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E18" s="47">
+        <v>3</v>
+      </c>
+      <c r="F18" s="47">
+        <v>3</v>
+      </c>
+      <c r="G18" s="47">
+        <v>3</v>
+      </c>
+      <c r="H18" s="47"/>
+      <c r="I18" t="s">
+        <v>515</v>
+      </c>
+      <c r="J18" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="30">
+      <c r="A19" s="47">
+        <v>25280773</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>773</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E19" s="47">
+        <v>5</v>
+      </c>
+      <c r="F19" s="47">
+        <v>5</v>
+      </c>
+      <c r="G19" s="47">
+        <v>5</v>
+      </c>
+      <c r="H19" s="47"/>
+      <c r="I19" t="s">
+        <v>515</v>
+      </c>
+      <c r="J19" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="30">
+      <c r="A20" s="46">
+        <v>1130000000</v>
+      </c>
+      <c r="B20" s="47" t="s">
+        <v>774</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D20" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E20" s="47">
+        <v>5</v>
+      </c>
+      <c r="F20" s="47">
+        <v>5</v>
+      </c>
+      <c r="G20" s="47">
+        <v>5</v>
+      </c>
+      <c r="H20" s="47"/>
+      <c r="I20" t="s">
+        <v>319</v>
+      </c>
+      <c r="J20" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30">
+      <c r="A21" s="47">
+        <v>24580946</v>
+      </c>
+      <c r="B21" s="47" t="s">
         <v>775</v>
       </c>
-      <c r="F1" s="25" t="s">
-        <v>770</v>
-      </c>
-      <c r="G1" s="25" t="s">
-        <v>771</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>772</v>
-      </c>
-      <c r="I1" t="s">
-        <v>773</v>
-      </c>
-      <c r="J1" t="s">
-        <v>774</v>
-      </c>
-      <c r="K1" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="27" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="25">
-        <v>92496452</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>758</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>768</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>759</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>740</v>
-      </c>
-      <c r="G2" s="25">
+      <c r="C21" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D21" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E21" s="47">
         <v>5</v>
       </c>
-      <c r="H2" s="25">
+      <c r="F21" s="47">
         <v>5</v>
       </c>
-      <c r="I2">
+      <c r="G21" s="47">
         <v>5</v>
       </c>
-      <c r="J2" t="s">
-        <v>760</v>
-      </c>
-      <c r="K2" t="s">
-        <v>583</v>
-      </c>
-      <c r="L2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="25">
-        <v>1053770020</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>761</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>768</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>762</v>
-      </c>
-      <c r="J3" t="s">
-        <v>763</v>
-      </c>
-      <c r="K3" t="s">
-        <v>583</v>
-      </c>
-      <c r="L3" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="25">
-        <v>79043668</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>764</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>768</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>762</v>
-      </c>
-      <c r="J4" t="s">
-        <v>765</v>
-      </c>
-      <c r="K4" t="s">
-        <v>583</v>
-      </c>
-      <c r="L4" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="25">
-        <v>16256537</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>766</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>768</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>762</v>
-      </c>
-      <c r="J5" t="s">
-        <v>767</v>
-      </c>
-      <c r="K5" t="s">
-        <v>583</v>
-      </c>
-      <c r="L5" t="s">
-        <v>584</v>
+      <c r="H21" s="47"/>
+      <c r="I21" t="s">
+        <v>319</v>
+      </c>
+      <c r="J21" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="30">
+      <c r="A22" s="47">
+        <v>79794583</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>776</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D22" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E22" s="47">
+        <v>5</v>
+      </c>
+      <c r="F22" s="47">
+        <v>5</v>
+      </c>
+      <c r="G22" s="47">
+        <v>5</v>
+      </c>
+      <c r="H22" s="47"/>
+      <c r="I22" t="s">
+        <v>385</v>
+      </c>
+      <c r="J22" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="30">
+      <c r="A23" s="47">
+        <v>79496136</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>777</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D23" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E23" s="47">
+        <v>5</v>
+      </c>
+      <c r="F23" s="47">
+        <v>5</v>
+      </c>
+      <c r="G23" s="47">
+        <v>5</v>
+      </c>
+      <c r="H23" s="47"/>
+      <c r="I23" t="s">
+        <v>385</v>
+      </c>
+      <c r="J23" t="s">
+        <v>386</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3176,14 +3762,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA89662-6597-440B-93CF-3E4C4E5F4B95}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:C374"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="23" customWidth="1"/>
     <col min="2" max="2" width="52.28515625" style="24" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" style="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
@@ -3194,7 +3780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" hidden="1">
       <c r="A2" s="31">
         <v>900220590</v>
       </c>
@@ -3205,7 +3791,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" hidden="1">
       <c r="A3" s="31">
         <v>891855847</v>
       </c>
@@ -3216,7 +3802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" hidden="1">
       <c r="A4" s="31">
         <v>890801026</v>
       </c>
@@ -3227,7 +3813,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" hidden="1">
       <c r="A5" s="31">
         <v>41471570</v>
       </c>
@@ -3238,7 +3824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1">
       <c r="A6" s="31">
         <v>900352592</v>
       </c>
@@ -3249,7 +3835,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1">
       <c r="A7" s="31">
         <v>900385628</v>
       </c>
@@ -3260,7 +3846,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1">
       <c r="A8" s="31">
         <v>832010240</v>
       </c>
@@ -3271,7 +3857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1">
       <c r="A9" s="31">
         <v>899999161</v>
       </c>
@@ -3282,7 +3868,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1">
       <c r="A10" s="31">
         <v>900119357</v>
       </c>
@@ -3293,7 +3879,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1">
       <c r="A11" s="31">
         <v>830114167</v>
       </c>
@@ -3304,7 +3890,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1">
       <c r="A12" s="31">
         <v>79781903</v>
       </c>
@@ -3315,7 +3901,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1">
       <c r="A13" s="31">
         <v>891190011</v>
       </c>
@@ -3326,7 +3912,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" hidden="1">
       <c r="A14" s="31">
         <v>891401643</v>
       </c>
@@ -3337,7 +3923,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" hidden="1">
       <c r="A15" s="31">
         <v>800174851</v>
       </c>
@@ -3348,7 +3934,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" hidden="1">
       <c r="A16" s="31">
         <v>800193490</v>
       </c>
@@ -3359,7 +3945,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1">
       <c r="A17" s="31">
         <v>900420664</v>
       </c>
@@ -3370,7 +3956,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1">
       <c r="A18" s="31">
         <v>80041361</v>
       </c>
@@ -3381,18 +3967,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" hidden="1">
       <c r="A19" s="31">
         <v>830109997</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" hidden="1">
       <c r="A20" s="31">
         <v>860053761</v>
       </c>
@@ -3403,7 +3989,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" hidden="1">
       <c r="A21" s="31">
         <v>19274667</v>
       </c>
@@ -3414,7 +4000,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" hidden="1">
       <c r="A22" s="31">
         <v>890701718</v>
       </c>
@@ -3425,7 +4011,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1">
       <c r="A23" s="31">
         <v>800209891</v>
       </c>
@@ -3436,18 +4022,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" hidden="1">
       <c r="A24" s="31">
         <v>860066767</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" hidden="1">
       <c r="A25" s="31">
         <v>810003245</v>
       </c>
@@ -3458,18 +4044,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" hidden="1">
       <c r="A26" s="31">
         <v>800085883</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" hidden="1">
       <c r="A27" s="31">
         <v>900649963</v>
       </c>
@@ -3480,7 +4066,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" hidden="1">
       <c r="A28" s="31">
         <v>52794734</v>
       </c>
@@ -3491,7 +4077,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" hidden="1">
       <c r="A29" s="31">
         <v>800231215</v>
       </c>
@@ -3502,7 +4088,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" hidden="1">
       <c r="A30" s="31">
         <v>900691301</v>
       </c>
@@ -3513,7 +4099,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" hidden="1">
       <c r="A31" s="31">
         <v>800006509</v>
       </c>
@@ -3524,7 +4110,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" hidden="1">
       <c r="A32" s="31">
         <v>900193162</v>
       </c>
@@ -3535,7 +4121,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" hidden="1">
       <c r="A33" s="31">
         <v>890807591</v>
       </c>
@@ -3546,7 +4132,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" hidden="1">
       <c r="A34" s="31">
         <v>900144408</v>
       </c>
@@ -3557,7 +4143,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" hidden="1">
       <c r="A35" s="31">
         <v>860010783</v>
       </c>
@@ -3568,7 +4154,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" hidden="1">
       <c r="A36" s="31">
         <v>900691056</v>
       </c>
@@ -3579,7 +4165,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" hidden="1">
       <c r="A37" s="31">
         <v>901060053</v>
       </c>
@@ -3590,7 +4176,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" hidden="1">
       <c r="A38" s="31">
         <v>900215983</v>
       </c>
@@ -3601,7 +4187,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" hidden="1">
       <c r="A39" s="31">
         <v>900129308</v>
       </c>
@@ -3612,7 +4198,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" hidden="1">
       <c r="A40" s="31">
         <v>892000264</v>
       </c>
@@ -3623,7 +4209,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" hidden="1">
       <c r="A41" s="31">
         <v>800218979</v>
       </c>
@@ -3634,7 +4220,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" hidden="1">
       <c r="A42" s="31">
         <v>891855029</v>
       </c>
@@ -3645,7 +4231,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" hidden="1">
       <c r="A43" s="31">
         <v>900142282</v>
       </c>
@@ -3656,7 +4242,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" hidden="1">
       <c r="A44" s="31">
         <v>860006745</v>
       </c>
@@ -3667,7 +4253,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" hidden="1">
       <c r="A45" s="31">
         <v>890702369</v>
       </c>
@@ -3678,7 +4264,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" hidden="1">
       <c r="A46" s="31">
         <v>800017308</v>
       </c>
@@ -3689,7 +4275,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" hidden="1">
       <c r="A47" s="31">
         <v>890000992</v>
       </c>
@@ -3700,7 +4286,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" hidden="1">
       <c r="A48" s="31">
         <v>830511298</v>
       </c>
@@ -3711,7 +4297,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" hidden="1">
       <c r="A49" s="31">
         <v>832001411</v>
       </c>
@@ -3722,7 +4308,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" hidden="1">
       <c r="A50" s="31">
         <v>809010893</v>
       </c>
@@ -3733,7 +4319,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" hidden="1">
       <c r="A51" s="31">
         <v>900714297</v>
       </c>
@@ -3744,7 +4330,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" hidden="1">
       <c r="A52" s="31">
         <v>900034131</v>
       </c>
@@ -3755,7 +4341,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" hidden="1">
       <c r="A53" s="31">
         <v>860015536</v>
       </c>
@@ -3766,7 +4352,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" hidden="1">
       <c r="A54" s="31">
         <v>900211460</v>
       </c>
@@ -3777,7 +4363,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" hidden="1">
       <c r="A55" s="31">
         <v>860090566</v>
       </c>
@@ -3788,7 +4374,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" hidden="1">
       <c r="A56" s="31">
         <v>891800335</v>
       </c>
@@ -3799,7 +4385,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" hidden="1">
       <c r="A57" s="31">
         <v>900454994</v>
       </c>
@@ -3810,7 +4396,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" hidden="1">
       <c r="A58" s="31">
         <v>820003431</v>
       </c>
@@ -3821,7 +4407,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" hidden="1">
       <c r="A59" s="31">
         <v>830070284</v>
       </c>
@@ -3832,7 +4418,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" hidden="1">
       <c r="A60" s="31">
         <v>890703630</v>
       </c>
@@ -3843,7 +4429,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" hidden="1">
       <c r="A61" s="31">
         <v>800032418</v>
       </c>
@@ -3854,7 +4440,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" hidden="1">
       <c r="A62" s="31">
         <v>900211477</v>
       </c>
@@ -3865,7 +4451,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" hidden="1">
       <c r="A63" s="31">
         <v>900004894</v>
       </c>
@@ -3876,7 +4462,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" hidden="1">
       <c r="A64" s="31">
         <v>901061505</v>
       </c>
@@ -3887,7 +4473,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" hidden="1">
       <c r="A65" s="31">
         <v>901622460</v>
       </c>
@@ -3898,7 +4484,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" hidden="1">
       <c r="A66" s="31">
         <v>828000386</v>
       </c>
@@ -3909,7 +4495,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" hidden="1">
       <c r="A67" s="31">
         <v>891200679</v>
       </c>
@@ -3920,7 +4506,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" hidden="1">
       <c r="A68" s="31">
         <v>79451044</v>
       </c>
@@ -3931,7 +4517,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" hidden="1">
       <c r="A69" s="31">
         <v>860035992</v>
       </c>
@@ -3942,7 +4528,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" hidden="1">
       <c r="A70" s="31">
         <v>900217648</v>
       </c>
@@ -3953,7 +4539,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" hidden="1">
       <c r="A71" s="31">
         <v>900130936</v>
       </c>
@@ -3964,7 +4550,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" hidden="1">
       <c r="A72" s="31">
         <v>890805923</v>
       </c>
@@ -3975,7 +4561,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" hidden="1">
       <c r="A73" s="31">
         <v>900470918</v>
       </c>
@@ -3986,7 +4572,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" hidden="1">
       <c r="A74" s="31">
         <v>900236728</v>
       </c>
@@ -3997,7 +4583,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" hidden="1">
       <c r="A75" s="31">
         <v>844004197</v>
       </c>
@@ -4008,7 +4594,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" hidden="1">
       <c r="A76" s="31">
         <v>900175697</v>
       </c>
@@ -4019,7 +4605,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" hidden="1">
       <c r="A77" s="31">
         <v>820003850</v>
       </c>
@@ -4030,7 +4616,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" hidden="1">
       <c r="A78" s="31">
         <v>830073010</v>
       </c>
@@ -4041,7 +4627,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" hidden="1">
       <c r="A79" s="31">
         <v>860015888</v>
       </c>
@@ -4052,7 +4638,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" hidden="1">
       <c r="A80" s="31">
         <v>900210981</v>
       </c>
@@ -4063,7 +4649,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" hidden="1">
       <c r="A81" s="31">
         <v>901011962</v>
       </c>
@@ -4074,7 +4660,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" hidden="1">
       <c r="A82" s="31">
         <v>900118059</v>
       </c>
@@ -4085,7 +4671,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" hidden="1">
       <c r="A83" s="31">
         <v>901447598</v>
       </c>
@@ -4096,7 +4682,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" hidden="1">
       <c r="A84" s="31">
         <v>901163080</v>
       </c>
@@ -4107,7 +4693,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" hidden="1">
       <c r="A85" s="31">
         <v>900559103</v>
       </c>
@@ -4118,7 +4704,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" hidden="1">
       <c r="A86" s="31">
         <v>891480000</v>
       </c>
@@ -4129,7 +4715,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" hidden="1">
       <c r="A87" s="31">
         <v>900971006</v>
       </c>
@@ -4140,7 +4726,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" hidden="1">
       <c r="A88" s="31">
         <v>900420751</v>
       </c>
@@ -4151,7 +4737,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" hidden="1">
       <c r="A89" s="31">
         <v>901102510</v>
       </c>
@@ -4162,7 +4748,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" hidden="1">
       <c r="A90" s="31">
         <v>800044967</v>
       </c>
@@ -4173,7 +4759,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" hidden="1">
       <c r="A91" s="31">
         <v>832000744</v>
       </c>
@@ -4184,7 +4770,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" hidden="1">
       <c r="A92" s="31">
         <v>901631369</v>
       </c>
@@ -4195,7 +4781,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" hidden="1">
       <c r="A93" s="31">
         <v>830010671</v>
       </c>
@@ -4206,7 +4792,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" hidden="1">
       <c r="A94" s="31">
         <v>900769055</v>
       </c>
@@ -4217,7 +4803,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" hidden="1">
       <c r="A95" s="31">
         <v>820001181</v>
       </c>
@@ -4228,7 +4814,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" hidden="1">
       <c r="A96" s="31">
         <v>891201578</v>
       </c>
@@ -4239,7 +4825,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" hidden="1">
       <c r="A97" s="31">
         <v>901011387</v>
       </c>
@@ -4250,7 +4836,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" hidden="1">
       <c r="A98" s="31">
         <v>891480036</v>
       </c>
@@ -4261,7 +4847,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" hidden="1">
       <c r="A99" s="31">
         <v>900491982</v>
       </c>
@@ -4272,7 +4858,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" hidden="1">
       <c r="A100" s="31">
         <v>832003167</v>
       </c>
@@ -4283,7 +4869,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" hidden="1">
       <c r="A101" s="31">
         <v>846000253</v>
       </c>
@@ -4294,18 +4880,18 @@
         <v>197</v>
       </c>
     </row>
-    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" hidden="1">
       <c r="A102" s="31">
         <v>800149384</v>
       </c>
       <c r="B102" s="32" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C102" s="30" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" hidden="1">
       <c r="A103" s="31">
         <v>900138555</v>
       </c>
@@ -4316,18 +4902,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" hidden="1">
       <c r="A104" s="31">
         <v>800066001</v>
       </c>
       <c r="B104" s="32" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C104" s="30" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" hidden="1">
       <c r="A105" s="31">
         <v>826002694</v>
       </c>
@@ -4338,7 +4924,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" hidden="1">
       <c r="A106" s="31">
         <v>830027158</v>
       </c>
@@ -4349,7 +4935,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" hidden="1">
       <c r="A107" s="31">
         <v>900132642</v>
       </c>
@@ -4360,7 +4946,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" hidden="1">
       <c r="A108" s="31">
         <v>901182731</v>
       </c>
@@ -4371,7 +4957,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" hidden="1">
       <c r="A109" s="31">
         <v>900415353</v>
       </c>
@@ -4382,7 +4968,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" hidden="1">
       <c r="A110" s="31">
         <v>901386786</v>
       </c>
@@ -4393,7 +4979,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" hidden="1">
       <c r="A111" s="31">
         <v>890701353</v>
       </c>
@@ -4404,7 +4990,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" hidden="1">
       <c r="A112" s="31">
         <v>890706833</v>
       </c>
@@ -4415,7 +5001,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" hidden="1">
       <c r="A113" s="31">
         <v>809002913</v>
       </c>
@@ -4426,7 +5012,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" hidden="1">
       <c r="A114" s="31">
         <v>900958115</v>
       </c>
@@ -4437,7 +5023,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" hidden="1">
       <c r="A115" s="31">
         <v>900876789</v>
       </c>
@@ -4448,7 +5034,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" hidden="1">
       <c r="A116" s="31">
         <v>800082446</v>
       </c>
@@ -4459,7 +5045,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" hidden="1">
       <c r="A117" s="31">
         <v>816007055</v>
       </c>
@@ -4470,7 +5056,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" hidden="1">
       <c r="A118" s="31">
         <v>900912423</v>
       </c>
@@ -4481,7 +5067,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" hidden="1">
       <c r="A119" s="31">
         <v>900826841</v>
       </c>
@@ -4492,7 +5078,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" hidden="1">
       <c r="A120" s="31">
         <v>901091739</v>
       </c>
@@ -4503,7 +5089,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" hidden="1">
       <c r="A121" s="31">
         <v>900215698</v>
       </c>
@@ -4514,7 +5100,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" hidden="1">
       <c r="A122" s="31">
         <v>901392384</v>
       </c>
@@ -4525,7 +5111,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" hidden="1">
       <c r="A123" s="31">
         <v>828000073</v>
       </c>
@@ -4536,7 +5122,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" hidden="1">
       <c r="A124" s="31">
         <v>901352353</v>
       </c>
@@ -4547,7 +5133,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" hidden="1">
       <c r="A125" s="31">
         <v>900999027</v>
       </c>
@@ -4558,7 +5144,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" hidden="1">
       <c r="A126" s="31">
         <v>800074996</v>
       </c>
@@ -4569,7 +5155,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" hidden="1">
       <c r="A127" s="31">
         <v>901680794</v>
       </c>
@@ -4580,7 +5166,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" hidden="1">
       <c r="A128" s="31">
         <v>900477525</v>
       </c>
@@ -4591,7 +5177,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" hidden="1">
       <c r="A129" s="31">
         <v>900532173</v>
       </c>
@@ -4602,7 +5188,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" hidden="1">
       <c r="A130" s="31">
         <v>900702090</v>
       </c>
@@ -4613,7 +5199,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" hidden="1">
       <c r="A131" s="31">
         <v>890701033</v>
       </c>
@@ -4624,18 +5210,18 @@
         <v>253</v>
       </c>
     </row>
-    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" hidden="1">
       <c r="A132" s="31">
         <v>901625767</v>
       </c>
       <c r="B132" s="32" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C132" s="30" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" hidden="1">
       <c r="A133" s="31">
         <v>900800269</v>
       </c>
@@ -4646,7 +5232,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" hidden="1">
       <c r="A134" s="31">
         <v>901606280</v>
       </c>
@@ -4657,18 +5243,18 @@
         <v>257</v>
       </c>
     </row>
-    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" hidden="1">
       <c r="A135" s="31">
         <v>830508610</v>
       </c>
       <c r="B135" s="32" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C135" s="30" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" hidden="1">
       <c r="A136" s="31">
         <v>900342271</v>
       </c>
@@ -4679,7 +5265,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" hidden="1">
       <c r="A137" s="31">
         <v>800162035</v>
       </c>
@@ -4690,7 +5276,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" hidden="1">
       <c r="A138" s="31">
         <v>800146679</v>
       </c>
@@ -4701,7 +5287,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" hidden="1">
       <c r="A139" s="31">
         <v>901470470</v>
       </c>
@@ -4712,7 +5298,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" hidden="1">
       <c r="A140" s="31">
         <v>800234796</v>
       </c>
@@ -4723,7 +5309,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" hidden="1">
       <c r="A141" s="31">
         <v>900959048</v>
       </c>
@@ -4734,7 +5320,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" hidden="1">
       <c r="A142" s="31">
         <v>890801758</v>
       </c>
@@ -4745,7 +5331,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" hidden="1">
       <c r="A143" s="31">
         <v>805019730</v>
       </c>
@@ -4756,7 +5342,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" hidden="1">
       <c r="A144" s="31">
         <v>820002596</v>
       </c>
@@ -4767,7 +5353,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" hidden="1">
       <c r="A145" s="31">
         <v>900373445</v>
       </c>
@@ -4778,7 +5364,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" hidden="1">
       <c r="A146" s="31">
         <v>900301238</v>
       </c>
@@ -4789,7 +5375,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" hidden="1">
       <c r="A147" s="31">
         <v>900296178</v>
       </c>
@@ -4800,7 +5386,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" hidden="1">
       <c r="A148" s="31">
         <v>900341409</v>
       </c>
@@ -4811,7 +5397,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" hidden="1">
       <c r="A149" s="31">
         <v>813001952</v>
       </c>
@@ -4822,7 +5408,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" hidden="1">
       <c r="A150" s="31">
         <v>800227072</v>
       </c>
@@ -4833,7 +5419,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" hidden="1">
       <c r="A151" s="31">
         <v>800036400</v>
       </c>
@@ -4844,7 +5430,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" hidden="1">
       <c r="A152" s="31">
         <v>809009066</v>
       </c>
@@ -4855,7 +5441,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" hidden="1">
       <c r="A153" s="31">
         <v>900563603</v>
       </c>
@@ -4866,7 +5452,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" hidden="1">
       <c r="A154" s="31">
         <v>890001006</v>
       </c>
@@ -4877,7 +5463,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" hidden="1">
       <c r="A155" s="31">
         <v>901119103</v>
       </c>
@@ -4888,7 +5474,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" hidden="1">
       <c r="A156" s="31">
         <v>900240354</v>
       </c>
@@ -4899,7 +5485,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" hidden="1">
       <c r="A157" s="31">
         <v>900504265</v>
       </c>
@@ -4910,7 +5496,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" hidden="1">
       <c r="A158" s="31">
         <v>813002940</v>
       </c>
@@ -4921,7 +5507,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" hidden="1">
       <c r="A159" s="31">
         <v>830027578</v>
       </c>
@@ -4932,7 +5518,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" hidden="1">
       <c r="A160" s="31">
         <v>822006595</v>
       </c>
@@ -4943,7 +5529,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" hidden="1">
       <c r="A161" s="31">
         <v>900510844</v>
       </c>
@@ -4954,7 +5540,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" hidden="1">
       <c r="A162" s="31">
         <v>900573146</v>
       </c>
@@ -4965,7 +5551,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" hidden="1">
       <c r="A163" s="31">
         <v>890701459</v>
       </c>
@@ -4976,7 +5562,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" hidden="1">
       <c r="A164" s="31">
         <v>900355585</v>
       </c>
@@ -4987,7 +5573,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" hidden="1">
       <c r="A165" s="31">
         <v>860039726</v>
       </c>
@@ -4998,7 +5584,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" hidden="1">
       <c r="A166" s="31">
         <v>800201496</v>
       </c>
@@ -5009,7 +5595,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" hidden="1">
       <c r="A167" s="31">
         <v>891800395</v>
       </c>
@@ -5020,7 +5606,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" hidden="1">
       <c r="A168" s="31">
         <v>900103925</v>
       </c>
@@ -5031,7 +5617,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" hidden="1">
       <c r="A169" s="31">
         <v>800254850</v>
       </c>
@@ -5042,7 +5628,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" hidden="1">
       <c r="A170" s="31">
         <v>830514240</v>
       </c>
@@ -5053,7 +5639,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" hidden="1">
       <c r="A171" s="31">
         <v>900966154</v>
       </c>
@@ -5064,7 +5650,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" hidden="1">
       <c r="A172" s="31">
         <v>892000501</v>
       </c>
@@ -5075,7 +5661,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" hidden="1">
       <c r="A173" s="31">
         <v>860011298</v>
       </c>
@@ -5086,7 +5672,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" hidden="1">
       <c r="A174" s="31">
         <v>820005389</v>
       </c>
@@ -5097,7 +5683,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" hidden="1">
       <c r="A175" s="31">
         <v>830039229</v>
       </c>
@@ -5108,7 +5694,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" hidden="1">
       <c r="A176" s="31">
         <v>900448997</v>
       </c>
@@ -5119,7 +5705,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" hidden="1">
       <c r="A177" s="31">
         <v>900716387</v>
       </c>
@@ -5130,7 +5716,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" hidden="1">
       <c r="A178" s="31">
         <v>901495569</v>
       </c>
@@ -5141,7 +5727,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" hidden="1">
       <c r="A179" s="31">
         <v>900578105</v>
       </c>
@@ -5152,7 +5738,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" hidden="1">
       <c r="A180" s="31">
         <v>79785257</v>
       </c>
@@ -5163,7 +5749,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" hidden="1">
       <c r="A181" s="31">
         <v>80727490</v>
       </c>
@@ -5174,7 +5760,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" hidden="1">
       <c r="A182" s="31">
         <v>809006003</v>
       </c>
@@ -5185,7 +5771,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" hidden="1">
       <c r="A183" s="38">
         <v>832000464</v>
       </c>
@@ -5196,7 +5782,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" ht="15.75" hidden="1">
       <c r="A184" s="31">
         <v>900267104</v>
       </c>
@@ -5207,7 +5793,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" hidden="1">
       <c r="A185" s="31">
         <v>830141132</v>
       </c>
@@ -5218,7 +5804,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" hidden="1">
       <c r="A186" s="31">
         <v>890000600</v>
       </c>
@@ -5229,7 +5815,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" hidden="1">
       <c r="A187" s="31">
         <v>899999063</v>
       </c>
@@ -5240,7 +5826,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" hidden="1">
       <c r="A188" s="31">
         <v>890801517</v>
       </c>
@@ -5251,7 +5837,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" hidden="1">
       <c r="A189" s="31">
         <v>900482620</v>
       </c>
@@ -5262,7 +5848,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" hidden="1">
       <c r="A190" s="31">
         <v>891856161</v>
       </c>
@@ -5273,7 +5859,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" hidden="1">
       <c r="A191" s="31">
         <v>892000458</v>
       </c>
@@ -5284,7 +5870,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" hidden="1">
       <c r="A192" s="31">
         <v>900451858</v>
       </c>
@@ -5295,7 +5881,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" hidden="1">
       <c r="A193" s="31">
         <v>800219192</v>
       </c>
@@ -5306,7 +5892,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" hidden="1">
       <c r="A194" s="31">
         <v>832002436</v>
       </c>
@@ -5317,7 +5903,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" hidden="1">
       <c r="A195" s="31">
         <v>832001966</v>
       </c>
@@ -5328,7 +5914,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" hidden="1">
       <c r="A196" s="31">
         <v>900841132</v>
       </c>
@@ -5339,7 +5925,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" hidden="1">
       <c r="A197" s="31">
         <v>900588182</v>
       </c>
@@ -5350,7 +5936,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" hidden="1">
       <c r="A198" s="31">
         <v>826002144</v>
       </c>
@@ -5361,7 +5947,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" hidden="1">
       <c r="A199" s="31">
         <v>846003067</v>
       </c>
@@ -5372,7 +5958,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" hidden="1">
       <c r="A200" s="31">
         <v>900241765</v>
       </c>
@@ -5383,7 +5969,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" hidden="1">
       <c r="A201" s="31">
         <v>900521595</v>
       </c>
@@ -5394,7 +5980,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" hidden="1">
       <c r="A202" s="31">
         <v>816003270</v>
       </c>
@@ -5405,7 +5991,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" hidden="1">
       <c r="A203" s="31">
         <v>890704555</v>
       </c>
@@ -5416,7 +6002,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" hidden="1">
       <c r="A204" s="31">
         <v>900232301</v>
       </c>
@@ -5427,7 +6013,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" hidden="1">
       <c r="A205" s="31">
         <v>830143831</v>
       </c>
@@ -5438,7 +6024,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" hidden="1">
       <c r="A206" s="31">
         <v>800099652</v>
       </c>
@@ -5449,7 +6035,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" hidden="1">
       <c r="A207" s="31">
         <v>891800570</v>
       </c>
@@ -5460,7 +6046,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" hidden="1">
       <c r="A208" s="31">
         <v>892099421</v>
       </c>
@@ -5471,7 +6057,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" hidden="1">
       <c r="A209" s="31">
         <v>900438068</v>
       </c>
@@ -5482,7 +6068,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" hidden="1">
       <c r="A210" s="31">
         <v>860037950</v>
       </c>
@@ -5493,7 +6079,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" hidden="1">
       <c r="A211" s="31">
         <v>890702408</v>
       </c>
@@ -5504,7 +6090,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" hidden="1">
       <c r="A212" s="31">
         <v>1015392989</v>
       </c>
@@ -5515,7 +6101,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" hidden="1">
       <c r="A213" s="31">
         <v>899999032</v>
       </c>
@@ -5526,7 +6112,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" hidden="1">
       <c r="A214" s="31">
         <v>881862576</v>
       </c>
@@ -5537,7 +6123,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" hidden="1">
       <c r="A215" s="31">
         <v>52411325</v>
       </c>
@@ -5548,7 +6134,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" hidden="1">
       <c r="A216" s="31">
         <v>901544725</v>
       </c>
@@ -5559,7 +6145,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" hidden="1">
       <c r="A217" s="31">
         <v>830009112</v>
       </c>
@@ -5570,7 +6156,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" hidden="1">
       <c r="A218" s="31">
         <v>900614302</v>
       </c>
@@ -5581,7 +6167,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" hidden="1">
       <c r="A219" s="31">
         <v>900055393</v>
       </c>
@@ -5592,7 +6178,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" hidden="1">
       <c r="A220" s="31">
         <v>1020720272</v>
       </c>
@@ -5603,7 +6189,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" hidden="1">
       <c r="A221" s="31">
         <v>844001355</v>
       </c>
@@ -5614,7 +6200,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" hidden="1">
       <c r="A222" s="31">
         <v>801001440</v>
       </c>
@@ -5625,7 +6211,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" hidden="1">
       <c r="A223" s="31">
         <v>800037021</v>
       </c>
@@ -5636,7 +6222,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" hidden="1">
       <c r="A224" s="31">
         <v>19457462</v>
       </c>
@@ -5647,7 +6233,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" hidden="1">
       <c r="A225" s="31">
         <v>890802356</v>
       </c>
@@ -5658,7 +6244,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" hidden="1">
       <c r="A226" s="31">
         <v>890801719</v>
       </c>
@@ -5669,7 +6255,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" hidden="1">
       <c r="A227" s="31">
         <v>901408039</v>
       </c>
@@ -5680,7 +6266,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" hidden="1">
       <c r="A228" s="31">
         <v>860002541</v>
       </c>
@@ -5691,7 +6277,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" hidden="1">
       <c r="A229" s="31">
         <v>900342064</v>
       </c>
@@ -5702,7 +6288,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" hidden="1">
       <c r="A230" s="31">
         <v>890801035</v>
       </c>
@@ -5713,7 +6299,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" hidden="1">
       <c r="A231" s="31">
         <v>802011972</v>
       </c>
@@ -5724,7 +6310,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" hidden="1">
       <c r="A232" s="31">
         <v>900407200</v>
       </c>
@@ -5735,7 +6321,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" hidden="1">
       <c r="A233" s="31">
         <v>813010145</v>
       </c>
@@ -5746,7 +6332,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" hidden="1">
       <c r="A234" s="31">
         <v>860070301</v>
       </c>
@@ -5757,7 +6343,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" hidden="1">
       <c r="A235" s="31">
         <v>890700666</v>
       </c>
@@ -5768,7 +6354,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" hidden="1">
       <c r="A236" s="31">
         <v>900308007</v>
       </c>
@@ -5779,7 +6365,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" hidden="1">
       <c r="A237" s="31">
         <v>891856372</v>
       </c>
@@ -5790,7 +6376,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" hidden="1">
       <c r="A238" s="31">
         <v>800065396</v>
       </c>
@@ -5801,7 +6387,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" hidden="1">
       <c r="A239" s="31">
         <v>901223046</v>
       </c>
@@ -5812,7 +6398,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" hidden="1">
       <c r="A240" s="31">
         <v>809010402</v>
       </c>
@@ -5823,7 +6409,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" hidden="1">
       <c r="A241" s="31">
         <v>891800231</v>
       </c>
@@ -5834,7 +6420,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" hidden="1">
       <c r="A242" s="31">
         <v>800119574</v>
       </c>
@@ -5845,7 +6431,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" hidden="1">
       <c r="A243" s="31">
         <v>80170827</v>
       </c>
@@ -5856,7 +6442,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" hidden="1">
       <c r="A244" s="31">
         <v>10286175</v>
       </c>
@@ -5867,7 +6453,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" hidden="1">
       <c r="A245" s="31">
         <v>900454188</v>
       </c>
@@ -5878,7 +6464,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" hidden="1">
       <c r="A246" s="31">
         <v>900057926</v>
       </c>
@@ -5889,7 +6475,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" hidden="1">
       <c r="A247" s="31">
         <v>844001911</v>
       </c>
@@ -5900,7 +6486,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" hidden="1">
       <c r="A248" s="31">
         <v>900526144</v>
       </c>
@@ -5911,7 +6497,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" hidden="1">
       <c r="A249" s="31">
         <v>900828394</v>
       </c>
@@ -5922,7 +6508,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" hidden="1">
       <c r="A250" s="31">
         <v>844001287</v>
       </c>
@@ -5933,7 +6519,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" hidden="1">
       <c r="A251" s="31">
         <v>900431131</v>
       </c>
@@ -5944,7 +6530,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" hidden="1">
       <c r="A252" s="31">
         <v>800037979</v>
       </c>
@@ -5955,7 +6541,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" hidden="1">
       <c r="A253" s="31">
         <v>890601210</v>
       </c>
@@ -5966,7 +6552,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" hidden="1">
       <c r="A254" s="31">
         <v>801001969</v>
       </c>
@@ -5977,7 +6563,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" hidden="1">
       <c r="A255" s="31">
         <v>890801944</v>
       </c>
@@ -5988,7 +6574,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" hidden="1">
       <c r="A256" s="31">
         <v>19419315</v>
       </c>
@@ -5999,7 +6585,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" hidden="1">
       <c r="A257" s="31">
         <v>900371613</v>
       </c>
@@ -6010,7 +6596,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" hidden="1">
       <c r="A258" s="31">
         <v>860015905</v>
       </c>
@@ -6021,7 +6607,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" hidden="1">
       <c r="A259" s="31">
         <v>900488920</v>
       </c>
@@ -6032,7 +6618,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" hidden="1">
       <c r="A260" s="31">
         <v>810000913</v>
       </c>
@@ -6043,7 +6629,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" hidden="1">
       <c r="A261" s="31">
         <v>900471504</v>
       </c>
@@ -6054,7 +6640,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" hidden="1">
       <c r="A262" s="31">
         <v>844003225</v>
       </c>
@@ -6065,7 +6651,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" hidden="1">
       <c r="A263" s="31">
         <v>830075393</v>
       </c>
@@ -6076,7 +6662,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" hidden="1">
       <c r="A264" s="31">
         <v>900058218</v>
       </c>
@@ -6087,7 +6673,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" hidden="1">
       <c r="A265" s="31">
         <v>901295822</v>
       </c>
@@ -6098,7 +6684,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" hidden="1">
       <c r="A266" s="31">
         <v>900381555</v>
       </c>
@@ -6109,7 +6695,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" hidden="1">
       <c r="A267" s="31">
         <v>830117846</v>
       </c>
@@ -6120,7 +6706,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" hidden="1">
       <c r="A268" s="31">
         <v>901017982</v>
       </c>
@@ -6131,7 +6717,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" hidden="1">
       <c r="A269" s="31">
         <v>900314301</v>
       </c>
@@ -6142,7 +6728,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" hidden="1">
       <c r="A270" s="31">
         <v>901881050</v>
       </c>
@@ -6153,7 +6739,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" hidden="1">
       <c r="A271" s="31">
         <v>891180134</v>
       </c>
@@ -6164,7 +6750,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" hidden="1">
       <c r="A272" s="31">
         <v>900407111</v>
       </c>
@@ -6175,7 +6761,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" hidden="1">
       <c r="A273" s="31">
         <v>900112820</v>
       </c>
@@ -6186,7 +6772,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" hidden="1">
       <c r="A274" s="40">
         <v>901169422</v>
       </c>
@@ -6197,7 +6783,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" hidden="1">
       <c r="A275" s="31">
         <v>900108793</v>
       </c>
@@ -6208,7 +6794,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" hidden="1">
       <c r="A276" s="31">
         <v>900576170</v>
       </c>
@@ -6219,7 +6805,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" hidden="1">
       <c r="A277" s="31">
         <v>891180268</v>
       </c>
@@ -6230,7 +6816,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" hidden="1">
       <c r="A278" s="31">
         <v>900678145</v>
       </c>
@@ -6241,7 +6827,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="279" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" hidden="1">
       <c r="A279" s="31">
         <v>900627725</v>
       </c>
@@ -6252,7 +6838,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" hidden="1">
       <c r="A280" s="31">
         <v>891411743</v>
       </c>
@@ -6263,7 +6849,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" hidden="1">
       <c r="A281" s="31">
         <v>900077520</v>
       </c>
@@ -6274,7 +6860,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" hidden="1">
       <c r="A282" s="31">
         <v>900958564</v>
       </c>
@@ -6285,7 +6871,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" hidden="1">
       <c r="A283" s="31">
         <v>800200789</v>
       </c>
@@ -6296,7 +6882,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" hidden="1">
       <c r="A284" s="31">
         <v>900061048</v>
       </c>
@@ -6307,7 +6893,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" hidden="1">
       <c r="A285" s="31">
         <v>901127904</v>
       </c>
@@ -6318,7 +6904,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" hidden="1">
       <c r="A286" s="31">
         <v>890801562</v>
       </c>
@@ -6329,7 +6915,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" hidden="1">
       <c r="A287" s="31">
         <v>80055710</v>
       </c>
@@ -6340,7 +6926,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" hidden="1">
       <c r="A288" s="31">
         <v>79442674</v>
       </c>
@@ -6351,7 +6937,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" hidden="1">
       <c r="A289" s="31">
         <v>891856507</v>
       </c>
@@ -6362,7 +6948,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" hidden="1">
       <c r="A290" s="31">
         <v>900231829</v>
       </c>
@@ -6373,7 +6959,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" hidden="1">
       <c r="A291" s="31">
         <v>900171988</v>
       </c>
@@ -6384,7 +6970,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" hidden="1">
       <c r="A292" s="31">
         <v>891180098</v>
       </c>
@@ -6395,7 +6981,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="293" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" hidden="1">
       <c r="A293" s="31">
         <v>845000038</v>
       </c>
@@ -6406,7 +6992,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" hidden="1">
       <c r="A294" s="31">
         <v>900817788</v>
       </c>
@@ -6417,7 +7003,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="295" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" hidden="1">
       <c r="A295" s="31">
         <v>899999147</v>
       </c>
@@ -6428,7 +7014,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" hidden="1">
       <c r="A296" s="31">
         <v>900419180</v>
       </c>
@@ -6439,7 +7025,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3">
       <c r="A297" s="31">
         <v>830119200</v>
       </c>
@@ -6450,7 +7036,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" hidden="1">
       <c r="A298" s="31">
         <v>890801495</v>
       </c>
@@ -6461,7 +7047,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="299" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" hidden="1">
       <c r="A299" s="31">
         <v>900582598</v>
       </c>
@@ -6472,7 +7058,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" hidden="1">
       <c r="A300" s="31">
         <v>890802036</v>
       </c>
@@ -6483,7 +7069,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" hidden="1">
       <c r="A301" s="31">
         <v>900462440</v>
       </c>
@@ -6494,7 +7080,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" hidden="1">
       <c r="A302" s="31">
         <v>846000474</v>
       </c>
@@ -6505,7 +7091,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" hidden="1">
       <c r="A303" s="31">
         <v>800000118</v>
       </c>
@@ -6516,7 +7102,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" hidden="1">
       <c r="A304" s="31">
         <v>900211468</v>
       </c>
@@ -6527,7 +7113,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" hidden="1">
       <c r="A305" s="31">
         <v>891855438</v>
       </c>
@@ -6538,7 +7124,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" hidden="1">
       <c r="A306" s="31">
         <v>19364579</v>
       </c>
@@ -6549,7 +7135,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" hidden="1">
       <c r="A307" s="31">
         <v>900004059</v>
       </c>
@@ -6560,7 +7146,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" hidden="1">
       <c r="A308" s="31">
         <v>846003357</v>
       </c>
@@ -6571,7 +7157,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="309" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" hidden="1">
       <c r="A309" s="31">
         <v>901457374</v>
       </c>
@@ -6582,7 +7168,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" hidden="1">
       <c r="A310" s="31">
         <v>830005028</v>
       </c>
@@ -6593,7 +7179,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="311" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" hidden="1">
       <c r="A311" s="31">
         <v>900606412</v>
       </c>
@@ -6604,7 +7190,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" hidden="1">
       <c r="A312" s="31">
         <v>830113849</v>
       </c>
@@ -6615,7 +7201,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="313" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" hidden="1">
       <c r="A313" s="31">
         <v>900232628</v>
       </c>
@@ -6626,7 +7212,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="314" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" hidden="1">
       <c r="A314" s="31">
         <v>890706823</v>
       </c>
@@ -6637,7 +7223,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="315" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" hidden="1">
       <c r="A315" s="31">
         <v>901105417</v>
       </c>
@@ -6648,7 +7234,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" hidden="1">
       <c r="A316" s="31">
         <v>800037202</v>
       </c>
@@ -6659,7 +7245,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" hidden="1">
       <c r="A317" s="38">
         <v>80412859</v>
       </c>
@@ -6670,7 +7256,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="318" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" hidden="1">
       <c r="A318" s="31">
         <v>800180553</v>
       </c>
@@ -6681,7 +7267,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="319" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" hidden="1">
       <c r="A319" s="31">
         <v>891411381</v>
       </c>
@@ -6692,7 +7278,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" hidden="1">
       <c r="A320" s="31">
         <v>814003448</v>
       </c>
@@ -6703,7 +7289,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" hidden="1">
       <c r="A321" s="31">
         <v>891180026</v>
       </c>
@@ -6714,7 +7300,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" hidden="1">
       <c r="A322" s="31">
         <v>900233110</v>
       </c>
@@ -6725,7 +7311,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" hidden="1">
       <c r="A323" s="31">
         <v>860013570</v>
       </c>
@@ -6736,7 +7322,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" hidden="1">
       <c r="A324" s="31">
         <v>901652147</v>
       </c>
@@ -6747,7 +7333,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" hidden="1">
       <c r="A325" s="31">
         <v>901439163</v>
       </c>
@@ -6758,7 +7344,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" hidden="1">
       <c r="A326" s="31">
         <v>822000946</v>
       </c>
@@ -6769,7 +7355,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" hidden="1">
       <c r="A327" s="31">
         <v>810001466</v>
       </c>
@@ -6780,7 +7366,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" hidden="1">
       <c r="A328" s="31">
         <v>900547903</v>
       </c>
@@ -6791,7 +7377,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" hidden="1">
       <c r="A329" s="31">
         <v>800228215</v>
       </c>
@@ -6802,7 +7388,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" hidden="1">
       <c r="A330" s="31">
         <v>890802978</v>
       </c>
@@ -6813,7 +7399,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" hidden="1">
       <c r="A331" s="31">
         <v>800135582</v>
       </c>
@@ -6824,7 +7410,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" hidden="1">
       <c r="A332" s="31">
         <v>900364721</v>
       </c>
@@ -6835,7 +7421,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" hidden="1">
       <c r="A333" s="31">
         <v>899999123</v>
       </c>
@@ -6846,7 +7432,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" hidden="1">
       <c r="A334" s="31">
         <v>890801099</v>
       </c>
@@ -6857,7 +7443,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" hidden="1">
       <c r="A335" s="31">
         <v>830018305</v>
       </c>
@@ -6868,7 +7454,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" hidden="1">
       <c r="A336" s="31">
         <v>809001482</v>
       </c>
@@ -6879,7 +7465,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" hidden="1">
       <c r="A337" s="31">
         <v>900685235</v>
       </c>
@@ -6890,7 +7476,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" hidden="1">
       <c r="A338" s="31">
         <v>800191101</v>
       </c>
@@ -6901,7 +7487,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" hidden="1">
       <c r="A339" s="31">
         <v>891409981</v>
       </c>
@@ -6912,7 +7498,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" hidden="1">
       <c r="A340" s="31">
         <v>900073806</v>
       </c>
@@ -6923,7 +7509,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" hidden="1">
       <c r="A341" s="31">
         <v>900493064</v>
       </c>
@@ -6934,7 +7520,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" hidden="1">
       <c r="A342" s="31">
         <v>800231235</v>
       </c>
@@ -6945,7 +7531,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" hidden="1">
       <c r="A343" s="31">
         <v>860007373</v>
       </c>
@@ -6956,7 +7542,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" hidden="1">
       <c r="A344" s="31">
         <v>900848340</v>
       </c>
@@ -6967,7 +7553,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" hidden="1">
       <c r="A345" s="31">
         <v>900115642</v>
       </c>
@@ -6978,7 +7564,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" hidden="1">
       <c r="A346" s="31">
         <v>79533241</v>
       </c>
@@ -6989,7 +7575,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" hidden="1">
       <c r="A347" s="31">
         <v>830502282</v>
       </c>
@@ -7000,7 +7586,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" hidden="1">
       <c r="A348" s="31">
         <v>900081643</v>
       </c>
@@ -7011,7 +7597,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" hidden="1">
       <c r="A349" s="31">
         <v>891855039</v>
       </c>
@@ -7022,7 +7608,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" hidden="1">
       <c r="A350" s="31">
         <v>805017681</v>
       </c>
@@ -7033,7 +7619,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" hidden="1">
       <c r="A351" s="31">
         <v>820002248</v>
       </c>
@@ -7044,7 +7630,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" hidden="1">
       <c r="A352" s="31">
         <v>860024026</v>
       </c>
@@ -7055,7 +7641,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" hidden="1">
       <c r="A353" s="31">
         <v>71394225</v>
       </c>
@@ -7066,7 +7652,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" hidden="1">
       <c r="A354" s="31">
         <v>832008321</v>
       </c>
@@ -7077,7 +7663,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" hidden="1">
       <c r="A355" s="31">
         <v>901632467</v>
       </c>
@@ -7088,7 +7674,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" hidden="1">
       <c r="A356" s="38">
         <v>891180117</v>
       </c>
@@ -7099,7 +7685,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="15.75" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:3" ht="15.75" hidden="1">
       <c r="A357" s="31">
         <v>900435790</v>
       </c>
@@ -7110,7 +7696,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="358" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" hidden="1">
       <c r="A358" s="31">
         <v>900759329</v>
       </c>
@@ -7121,7 +7707,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="359" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" hidden="1">
       <c r="A359" s="31">
         <v>891800644</v>
       </c>
@@ -7132,7 +7718,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="360" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" hidden="1">
       <c r="A360" s="31">
         <v>800254132</v>
       </c>
@@ -7143,7 +7729,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="361" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" hidden="1">
       <c r="A361" s="31">
         <v>899999158</v>
       </c>
@@ -7154,7 +7740,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="362" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" hidden="1">
       <c r="A362" s="31">
         <v>79624744</v>
       </c>
@@ -7165,7 +7751,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="363" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" hidden="1">
       <c r="A363" s="31">
         <v>891409390</v>
       </c>
@@ -7176,7 +7762,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="364" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" hidden="1">
       <c r="A364" s="31">
         <v>890680014</v>
       </c>
@@ -7187,7 +7773,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="365" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" hidden="1">
       <c r="A365" s="31">
         <v>809006690</v>
       </c>
@@ -7198,7 +7784,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="366" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" hidden="1">
       <c r="A366" s="31">
         <v>900213617</v>
       </c>
@@ -7209,7 +7795,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="367" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" hidden="1">
       <c r="A367" s="31">
         <v>900423816</v>
       </c>
@@ -7220,7 +7806,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="368" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" hidden="1">
       <c r="A368" s="31">
         <v>860015929</v>
       </c>
@@ -7231,7 +7817,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="369" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" hidden="1">
       <c r="A369" s="31">
         <v>890806490</v>
       </c>
@@ -7242,7 +7828,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" hidden="1">
       <c r="A370" s="31">
         <v>860006626</v>
       </c>
@@ -7253,7 +7839,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="371" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" hidden="1">
       <c r="A371" s="31">
         <v>813005295</v>
       </c>
@@ -7264,7 +7850,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="372" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" hidden="1">
       <c r="A372" s="44">
         <v>846001425</v>
       </c>
@@ -7275,7 +7861,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="373" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" hidden="1">
       <c r="A373" s="31">
         <v>800139366</v>
       </c>
@@ -7286,7 +7872,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" hidden="1">
       <c r="A374" s="31">
         <v>816005003</v>
       </c>
@@ -7324,14 +7910,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C371"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="22" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" style="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5703125" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7342,7 +7928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
       <c r="A2" s="4">
         <v>900220590</v>
       </c>
@@ -7353,7 +7939,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
       <c r="A3" s="4">
         <v>891855847</v>
       </c>
@@ -7364,7 +7950,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="18.75" customHeight="1">
       <c r="A4" s="7">
         <v>890801026</v>
       </c>
@@ -7375,7 +7961,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="18.75" customHeight="1">
       <c r="A5" s="7">
         <v>41471570</v>
       </c>
@@ -7386,7 +7972,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
       <c r="A6" s="7">
         <v>900352592</v>
       </c>
@@ -7397,7 +7983,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="18.75" customHeight="1">
       <c r="A7" s="7">
         <v>900385628</v>
       </c>
@@ -7408,7 +7994,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
       <c r="A8" s="7">
         <v>832010240</v>
       </c>
@@ -7419,7 +8005,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="18.75" customHeight="1">
       <c r="A9" s="7">
         <v>899999161</v>
       </c>
@@ -7430,7 +8016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
       <c r="A10" s="7">
         <v>900119357</v>
       </c>
@@ -7441,7 +8027,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="18.75" customHeight="1">
       <c r="A11" s="7">
         <v>830114167</v>
       </c>
@@ -7452,7 +8038,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="18.75" customHeight="1">
       <c r="A12" s="7">
         <v>79781903</v>
       </c>
@@ -7463,7 +8049,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="18.75" customHeight="1">
       <c r="A13" s="7">
         <v>891190011</v>
       </c>
@@ -7474,7 +8060,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="18.75" customHeight="1">
       <c r="A14" s="7">
         <v>891401643</v>
       </c>
@@ -7485,7 +8071,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="18.75" customHeight="1">
       <c r="A15" s="7">
         <v>800174851</v>
       </c>
@@ -7496,7 +8082,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="18.75" customHeight="1">
       <c r="A16" s="7">
         <v>800193490</v>
       </c>
@@ -7507,7 +8093,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="18.75" customHeight="1">
       <c r="A17" s="7">
         <v>900420664</v>
       </c>
@@ -7518,7 +8104,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="18.75" customHeight="1">
       <c r="A18" s="4">
         <v>80041361</v>
       </c>
@@ -7529,7 +8115,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="18.75" customHeight="1">
       <c r="A19" s="7">
         <v>801001406</v>
       </c>
@@ -7540,7 +8126,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="18.75" customHeight="1">
       <c r="A20" s="7">
         <v>860053761</v>
       </c>
@@ -7551,7 +8137,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="18.75" customHeight="1">
       <c r="A21" s="7">
         <v>19274667</v>
       </c>
@@ -7562,7 +8148,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="18.75" customHeight="1">
       <c r="A22" s="7">
         <v>890701718</v>
       </c>
@@ -7573,7 +8159,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="18.75" customHeight="1">
       <c r="A23" s="7">
         <v>800209891</v>
       </c>
@@ -7584,7 +8170,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="18.75" customHeight="1">
       <c r="A24" s="4">
         <v>810003245</v>
       </c>
@@ -7595,7 +8181,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="18.75" customHeight="1">
       <c r="A25" s="7">
         <v>900649963</v>
       </c>
@@ -7606,7 +8192,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="18.75" customHeight="1">
       <c r="A26" s="4">
         <v>52794734</v>
       </c>
@@ -7617,7 +8203,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="18.75" customHeight="1">
       <c r="A27" s="7">
         <v>800231215</v>
       </c>
@@ -7628,7 +8214,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="18.75" customHeight="1">
       <c r="A28" s="7">
         <v>900691301</v>
       </c>
@@ -7639,7 +8225,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="18.75" customHeight="1">
       <c r="A29" s="7">
         <v>800006509</v>
       </c>
@@ -7650,7 +8236,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="18.75" customHeight="1">
       <c r="A30" s="7">
         <v>900193162</v>
       </c>
@@ -7661,7 +8247,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="18.75" customHeight="1">
       <c r="A31" s="7">
         <v>890807591</v>
       </c>
@@ -7672,7 +8258,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="18.75" customHeight="1">
       <c r="A32" s="7">
         <v>900144408</v>
       </c>
@@ -7683,7 +8269,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="18.75" customHeight="1">
       <c r="A33" s="7">
         <v>860010783</v>
       </c>
@@ -7694,7 +8280,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="18.75" customHeight="1">
       <c r="A34" s="7">
         <v>900691056</v>
       </c>
@@ -7705,7 +8291,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="18.75" customHeight="1">
       <c r="A35" s="7">
         <v>901060053</v>
       </c>
@@ -7716,7 +8302,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="18.75" customHeight="1">
       <c r="A36" s="7">
         <v>900215983</v>
       </c>
@@ -7727,7 +8313,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="18.75" customHeight="1">
       <c r="A37" s="7">
         <v>900129308</v>
       </c>
@@ -7738,7 +8324,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="18.75" customHeight="1">
       <c r="A38" s="7">
         <v>892000264</v>
       </c>
@@ -7749,7 +8335,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="18.75" customHeight="1">
       <c r="A39" s="7">
         <v>800218979</v>
       </c>
@@ -7760,7 +8346,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="18.75" customHeight="1">
       <c r="A40" s="7">
         <v>891855029</v>
       </c>
@@ -7771,7 +8357,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="18.75" customHeight="1">
       <c r="A41" s="7">
         <v>900142282</v>
       </c>
@@ -7782,7 +8368,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="18.75" customHeight="1">
       <c r="A42" s="7">
         <v>860006745</v>
       </c>
@@ -7793,7 +8379,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="18.75" customHeight="1">
       <c r="A43" s="7">
         <v>890702369</v>
       </c>
@@ -7804,7 +8390,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="18.75" customHeight="1">
       <c r="A44" s="7">
         <v>800017308</v>
       </c>
@@ -7815,7 +8401,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="18.75" customHeight="1">
       <c r="A45" s="7">
         <v>890000992</v>
       </c>
@@ -7826,7 +8412,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="18.75" customHeight="1">
       <c r="A46" s="7">
         <v>830511298</v>
       </c>
@@ -7837,7 +8423,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="18.75" customHeight="1">
       <c r="A47" s="7">
         <v>832001411</v>
       </c>
@@ -7848,7 +8434,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="18.75" customHeight="1">
       <c r="A48" s="7">
         <v>809010893</v>
       </c>
@@ -7859,7 +8445,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="18.75" customHeight="1">
       <c r="A49" s="7">
         <v>900714297</v>
       </c>
@@ -7870,7 +8456,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="18.75" customHeight="1">
       <c r="A50" s="12">
         <v>900034131</v>
       </c>
@@ -7881,7 +8467,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="18.75" customHeight="1">
       <c r="A51" s="7">
         <v>860015536</v>
       </c>
@@ -7892,7 +8478,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="18.75" customHeight="1">
       <c r="A52" s="7">
         <v>900211460</v>
       </c>
@@ -7903,7 +8489,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="18.75" customHeight="1">
       <c r="A53" s="7">
         <v>860090566</v>
       </c>
@@ -7914,7 +8500,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="18.75" customHeight="1">
       <c r="A54" s="7">
         <v>891800335</v>
       </c>
@@ -7925,7 +8511,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="18.75" customHeight="1">
       <c r="A55" s="7">
         <v>900454994</v>
       </c>
@@ -7936,7 +8522,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="18.75" customHeight="1">
       <c r="A56" s="7">
         <v>820003431</v>
       </c>
@@ -7947,7 +8533,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="18.75" customHeight="1">
       <c r="A57" s="7">
         <v>830070284</v>
       </c>
@@ -7958,7 +8544,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="18.75" customHeight="1">
       <c r="A58" s="7">
         <v>890703630</v>
       </c>
@@ -7969,7 +8555,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="18.75" customHeight="1">
       <c r="A59" s="7">
         <v>800032418</v>
       </c>
@@ -7980,7 +8566,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="18.75" customHeight="1">
       <c r="A60" s="7">
         <v>900211477</v>
       </c>
@@ -7991,7 +8577,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="18.75" customHeight="1">
       <c r="A61" s="7">
         <v>900004894</v>
       </c>
@@ -8002,7 +8588,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="18.75" customHeight="1">
       <c r="A62" s="7">
         <v>901061505</v>
       </c>
@@ -8013,7 +8599,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="18.75" customHeight="1">
       <c r="A63" s="7">
         <v>901622460</v>
       </c>
@@ -8024,7 +8610,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="18.75" customHeight="1">
       <c r="A64" s="7">
         <v>828000386</v>
       </c>
@@ -8035,7 +8621,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="18.75" customHeight="1">
       <c r="A65" s="7">
         <v>891200679</v>
       </c>
@@ -8046,7 +8632,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="18.75" customHeight="1">
       <c r="A66" s="7">
         <v>79451044</v>
       </c>
@@ -8057,7 +8643,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="18.75" customHeight="1">
       <c r="A67" s="7">
         <v>860035992</v>
       </c>
@@ -8068,7 +8654,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="18.75" customHeight="1">
       <c r="A68" s="7">
         <v>900217648</v>
       </c>
@@ -8079,7 +8665,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="18.75" customHeight="1">
       <c r="A69" s="7">
         <v>900130936</v>
       </c>
@@ -8090,7 +8676,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="18.75" customHeight="1">
       <c r="A70" s="7">
         <v>890805923</v>
       </c>
@@ -8101,7 +8687,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="18.75" customHeight="1">
       <c r="A71" s="7">
         <v>900470918</v>
       </c>
@@ -8112,7 +8698,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="18.75" customHeight="1">
       <c r="A72" s="7">
         <v>900236728</v>
       </c>
@@ -8123,7 +8709,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="18.75" customHeight="1">
       <c r="A73" s="7">
         <v>844004197</v>
       </c>
@@ -8134,7 +8720,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="18.75" customHeight="1">
       <c r="A74" s="7">
         <v>900175697</v>
       </c>
@@ -8145,7 +8731,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="18.75" customHeight="1">
       <c r="A75" s="7">
         <v>820003850</v>
       </c>
@@ -8156,7 +8742,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="18.75" customHeight="1">
       <c r="A76" s="7">
         <v>830073010</v>
       </c>
@@ -8167,7 +8753,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="18.75" customHeight="1">
       <c r="A77" s="7">
         <v>860015888</v>
       </c>
@@ -8178,7 +8764,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="18.75" customHeight="1">
       <c r="A78" s="7">
         <v>900210981</v>
       </c>
@@ -8189,7 +8775,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="18.75" customHeight="1">
       <c r="A79" s="7">
         <v>901011962</v>
       </c>
@@ -8200,7 +8786,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="18.75" customHeight="1">
       <c r="A80" s="7">
         <v>900118059</v>
       </c>
@@ -8211,7 +8797,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="18.75" customHeight="1">
       <c r="A81" s="7">
         <v>901447598</v>
       </c>
@@ -8222,7 +8808,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="18.75" customHeight="1">
       <c r="A82" s="7">
         <v>901163080</v>
       </c>
@@ -8233,7 +8819,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="18.75" customHeight="1">
       <c r="A83" s="7">
         <v>900559103</v>
       </c>
@@ -8244,7 +8830,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="18.75" customHeight="1">
       <c r="A84" s="7">
         <v>891480000</v>
       </c>
@@ -8255,7 +8841,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="18.75" customHeight="1">
       <c r="A85" s="7">
         <v>900971006</v>
       </c>
@@ -8266,7 +8852,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="18.75" customHeight="1">
       <c r="A86" s="7">
         <v>900420751</v>
       </c>
@@ -8277,7 +8863,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" ht="18.75" customHeight="1">
       <c r="A87" s="7">
         <v>901102510</v>
       </c>
@@ -8288,7 +8874,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="18.75" customHeight="1">
       <c r="A88" s="7">
         <v>800044967</v>
       </c>
@@ -8299,7 +8885,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="18.75" customHeight="1">
       <c r="A89" s="7">
         <v>832000744</v>
       </c>
@@ -8310,7 +8896,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="18.75" customHeight="1">
       <c r="A90" s="7">
         <v>901631369</v>
       </c>
@@ -8321,7 +8907,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="18.75" customHeight="1">
       <c r="A91" s="7">
         <v>830010671</v>
       </c>
@@ -8332,7 +8918,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="18.75" customHeight="1">
       <c r="A92" s="7">
         <v>900769055</v>
       </c>
@@ -8343,7 +8929,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="18.75" customHeight="1">
       <c r="A93" s="7">
         <v>820001181</v>
       </c>
@@ -8354,7 +8940,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="18.75" customHeight="1">
       <c r="A94" s="7">
         <v>891201578</v>
       </c>
@@ -8365,7 +8951,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="18.75" customHeight="1">
       <c r="A95" s="7">
         <v>901011387</v>
       </c>
@@ -8376,7 +8962,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="18.75" customHeight="1">
       <c r="A96" s="7">
         <v>891480036</v>
       </c>
@@ -8387,7 +8973,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="18.75" customHeight="1">
       <c r="A97" s="7">
         <v>900491982</v>
       </c>
@@ -8398,7 +8984,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="18.75" customHeight="1">
       <c r="A98" s="7">
         <v>832003167</v>
       </c>
@@ -8409,7 +8995,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="18.75" customHeight="1">
       <c r="A99" s="7">
         <v>846000253</v>
       </c>
@@ -8420,7 +9006,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="18.75" customHeight="1">
       <c r="A100" s="7">
         <v>900138555</v>
       </c>
@@ -8431,7 +9017,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" ht="18.75" customHeight="1">
       <c r="A101" s="7">
         <v>826002694</v>
       </c>
@@ -8442,7 +9028,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" ht="18.75" customHeight="1">
       <c r="A102" s="7">
         <v>830027158</v>
       </c>
@@ -8453,7 +9039,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" ht="18.75" customHeight="1">
       <c r="A103" s="7">
         <v>900132642</v>
       </c>
@@ -8464,7 +9050,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" ht="18.75" customHeight="1">
       <c r="A104" s="7">
         <v>901182731</v>
       </c>
@@ -8475,7 +9061,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" ht="18.75" customHeight="1">
       <c r="A105" s="7">
         <v>900415353</v>
       </c>
@@ -8486,7 +9072,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" ht="18.75" customHeight="1">
       <c r="A106" s="7">
         <v>901386786</v>
       </c>
@@ -8497,7 +9083,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" ht="18.75" customHeight="1">
       <c r="A107" s="7">
         <v>890701353</v>
       </c>
@@ -8508,7 +9094,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" ht="18.75" customHeight="1">
       <c r="A108" s="7">
         <v>890706833</v>
       </c>
@@ -8519,7 +9105,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" ht="18.75" customHeight="1">
       <c r="A109" s="7">
         <v>809002913</v>
       </c>
@@ -8530,7 +9116,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" ht="18.75" customHeight="1">
       <c r="A110" s="7">
         <v>900958115</v>
       </c>
@@ -8541,7 +9127,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" ht="18.75" customHeight="1">
       <c r="A111" s="7">
         <v>900876789</v>
       </c>
@@ -8552,7 +9138,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" ht="18.75" customHeight="1">
       <c r="A112" s="7">
         <v>800082446</v>
       </c>
@@ -8563,7 +9149,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" ht="18.75" customHeight="1">
       <c r="A113" s="7">
         <v>816007055</v>
       </c>
@@ -8574,7 +9160,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" ht="18.75" customHeight="1">
       <c r="A114" s="7">
         <v>900912423</v>
       </c>
@@ -8585,7 +9171,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" ht="18.75" customHeight="1">
       <c r="A115" s="7">
         <v>900826841</v>
       </c>
@@ -8596,7 +9182,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" ht="18.75" customHeight="1">
       <c r="A116" s="7">
         <v>901091739</v>
       </c>
@@ -8607,7 +9193,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" ht="18.75" customHeight="1">
       <c r="A117" s="7">
         <v>900215698</v>
       </c>
@@ -8618,7 +9204,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" ht="18.75" customHeight="1">
       <c r="A118" s="7">
         <v>901392384</v>
       </c>
@@ -8629,7 +9215,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" ht="18.75" customHeight="1">
       <c r="A119" s="7">
         <v>828000073</v>
       </c>
@@ -8640,7 +9226,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" ht="18.75" customHeight="1">
       <c r="A120" s="7">
         <v>901352353</v>
       </c>
@@ -8651,7 +9237,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" ht="18.75" customHeight="1">
       <c r="A121" s="7">
         <v>900999027</v>
       </c>
@@ -8662,7 +9248,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" ht="18.75" customHeight="1">
       <c r="A122" s="7">
         <v>800074996</v>
       </c>
@@ -8673,7 +9259,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" ht="18.75" customHeight="1">
       <c r="A123" s="7">
         <v>901680794</v>
       </c>
@@ -8684,7 +9270,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" ht="18.75" customHeight="1">
       <c r="A124" s="7">
         <v>900477525</v>
       </c>
@@ -8695,7 +9281,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" ht="18.75" customHeight="1">
       <c r="A125" s="7">
         <v>900532173</v>
       </c>
@@ -8706,7 +9292,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" ht="18.75" customHeight="1">
       <c r="A126" s="7">
         <v>900702090</v>
       </c>
@@ -8717,7 +9303,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" ht="18.75" customHeight="1">
       <c r="A127" s="7">
         <v>890701033</v>
       </c>
@@ -8728,7 +9314,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" ht="18.75" customHeight="1">
       <c r="A128" s="7">
         <v>900800269</v>
       </c>
@@ -8739,7 +9325,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" ht="18.75" customHeight="1">
       <c r="A129" s="7">
         <v>901606280</v>
       </c>
@@ -8750,7 +9336,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" ht="18.75" customHeight="1">
       <c r="A130" s="7">
         <v>900342271</v>
       </c>
@@ -8761,7 +9347,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" ht="18.75" customHeight="1">
       <c r="A131" s="7">
         <v>800162035</v>
       </c>
@@ -8772,7 +9358,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" ht="18.75" customHeight="1">
       <c r="A132" s="7">
         <v>800146679</v>
       </c>
@@ -8783,7 +9369,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" ht="18.75" customHeight="1">
       <c r="A133" s="7">
         <v>901470470</v>
       </c>
@@ -8794,7 +9380,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" ht="18.75" customHeight="1">
       <c r="A134" s="15">
         <v>890701010</v>
       </c>
@@ -8805,7 +9391,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" ht="18.75" customHeight="1">
       <c r="A135" s="7">
         <v>800234796</v>
       </c>
@@ -8816,7 +9402,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" ht="18.75" customHeight="1">
       <c r="A136" s="7">
         <v>900959048</v>
       </c>
@@ -8827,7 +9413,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" ht="18.75" customHeight="1">
       <c r="A137" s="7">
         <v>890801758</v>
       </c>
@@ -8838,7 +9424,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" ht="18.75" customHeight="1">
       <c r="A138" s="7">
         <v>805019730</v>
       </c>
@@ -8849,7 +9435,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" ht="18.75" customHeight="1">
       <c r="A139" s="7">
         <v>820002596</v>
       </c>
@@ -8860,7 +9446,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" ht="18.75" customHeight="1">
       <c r="A140" s="7">
         <v>900373445</v>
       </c>
@@ -8871,7 +9457,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" ht="18.75" customHeight="1">
       <c r="A141" s="7">
         <v>900301238</v>
       </c>
@@ -8882,7 +9468,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" ht="18.75" customHeight="1">
       <c r="A142" s="7">
         <v>900296178</v>
       </c>
@@ -8893,7 +9479,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" ht="18.75" customHeight="1">
       <c r="A143" s="7">
         <v>900341409</v>
       </c>
@@ -8904,7 +9490,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" ht="18.75" customHeight="1">
       <c r="A144" s="7">
         <v>813001952</v>
       </c>
@@ -8915,7 +9501,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" ht="18.75" customHeight="1">
       <c r="A145" s="7">
         <v>800227072</v>
       </c>
@@ -8926,7 +9512,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" ht="18.75" customHeight="1">
       <c r="A146" s="7">
         <v>800036400</v>
       </c>
@@ -8937,7 +9523,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" ht="18.75" customHeight="1">
       <c r="A147" s="7">
         <v>809009066</v>
       </c>
@@ -8948,7 +9534,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" ht="18.75" customHeight="1">
       <c r="A148" s="7">
         <v>900563603</v>
       </c>
@@ -8959,7 +9545,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" ht="18.75" customHeight="1">
       <c r="A149" s="7">
         <v>890001006</v>
       </c>
@@ -8970,7 +9556,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" ht="18.75" customHeight="1">
       <c r="A150" s="7">
         <v>901119103</v>
       </c>
@@ -8981,7 +9567,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" ht="18.75" customHeight="1">
       <c r="A151" s="7">
         <v>900240354</v>
       </c>
@@ -8992,7 +9578,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" ht="18.75" customHeight="1">
       <c r="A152" s="7">
         <v>900504265</v>
       </c>
@@ -9003,7 +9589,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" ht="18.75" customHeight="1">
       <c r="A153" s="7">
         <v>813002940</v>
       </c>
@@ -9014,7 +9600,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" ht="18.75" customHeight="1">
       <c r="A154" s="7">
         <v>830027578</v>
       </c>
@@ -9025,7 +9611,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" ht="18.75" customHeight="1">
       <c r="A155" s="7">
         <v>822006595</v>
       </c>
@@ -9036,7 +9622,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" ht="18.75" customHeight="1">
       <c r="A156" s="7">
         <v>900510844</v>
       </c>
@@ -9047,7 +9633,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" ht="18.75" customHeight="1">
       <c r="A157" s="7">
         <v>900573146</v>
       </c>
@@ -9058,7 +9644,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" ht="18.75" customHeight="1">
       <c r="A158" s="7">
         <v>890701459</v>
       </c>
@@ -9069,7 +9655,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" ht="18.75" customHeight="1">
       <c r="A159" s="7">
         <v>900355585</v>
       </c>
@@ -9080,7 +9666,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" ht="18.75" customHeight="1">
       <c r="A160" s="7">
         <v>860039726</v>
       </c>
@@ -9091,7 +9677,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" ht="18.75" customHeight="1">
       <c r="A161" s="7">
         <v>800201496</v>
       </c>
@@ -9102,7 +9688,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" ht="18.75" customHeight="1">
       <c r="A162" s="7">
         <v>891800395</v>
       </c>
@@ -9113,7 +9699,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" ht="18.75" customHeight="1">
       <c r="A163" s="7">
         <v>900103925</v>
       </c>
@@ -9124,7 +9710,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" ht="18.75" customHeight="1">
       <c r="A164" s="7">
         <v>800254850</v>
       </c>
@@ -9135,7 +9721,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" ht="18.75" customHeight="1">
       <c r="A165" s="7">
         <v>830514240</v>
       </c>
@@ -9146,7 +9732,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" ht="18.75" customHeight="1">
       <c r="A166" s="7">
         <v>900966154</v>
       </c>
@@ -9157,7 +9743,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" ht="18.75" customHeight="1">
       <c r="A167" s="7">
         <v>892000501</v>
       </c>
@@ -9168,7 +9754,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" ht="18.75" customHeight="1">
       <c r="A168" s="7">
         <v>860011298</v>
       </c>
@@ -9179,7 +9765,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" ht="18.75" customHeight="1">
       <c r="A169" s="7">
         <v>820005389</v>
       </c>
@@ -9190,7 +9776,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="18.75" customHeight="1">
       <c r="A170" s="7">
         <v>830039229</v>
       </c>
@@ -9201,7 +9787,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="18.75" customHeight="1">
       <c r="A171" s="7">
         <v>900448997</v>
       </c>
@@ -9212,7 +9798,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" ht="18.75" customHeight="1">
       <c r="A172" s="7">
         <v>900716387</v>
       </c>
@@ -9223,7 +9809,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="18.75" customHeight="1">
       <c r="A173" s="7">
         <v>901495569</v>
       </c>
@@ -9234,7 +9820,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" ht="18.75" customHeight="1">
       <c r="A174" s="7">
         <v>900578105</v>
       </c>
@@ -9245,7 +9831,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="18.75" customHeight="1">
       <c r="A175" s="7">
         <v>79785257</v>
       </c>
@@ -9256,7 +9842,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" ht="18.75" customHeight="1">
       <c r="A176" s="7">
         <v>80727490</v>
       </c>
@@ -9267,7 +9853,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" ht="18.75" customHeight="1">
       <c r="A177" s="7">
         <v>809006003</v>
       </c>
@@ -9278,7 +9864,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" ht="18.75" customHeight="1">
       <c r="A178" s="7">
         <v>832000464</v>
       </c>
@@ -9289,7 +9875,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" ht="18.75" customHeight="1">
       <c r="A179" s="7">
         <v>900267104</v>
       </c>
@@ -9300,7 +9886,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" ht="18.75" customHeight="1">
       <c r="A180" s="7">
         <v>830141132</v>
       </c>
@@ -9311,7 +9897,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" ht="18.75" customHeight="1">
       <c r="A181" s="7">
         <v>890000600</v>
       </c>
@@ -9322,7 +9908,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" ht="18.75" customHeight="1">
       <c r="A182" s="7">
         <v>899999063</v>
       </c>
@@ -9333,7 +9919,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" ht="18.75" customHeight="1">
       <c r="A183" s="7">
         <v>890801517</v>
       </c>
@@ -9344,7 +9930,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" ht="18.75" customHeight="1">
       <c r="A184" s="7">
         <v>900482620</v>
       </c>
@@ -9355,7 +9941,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" ht="18.75" customHeight="1">
       <c r="A185" s="7">
         <v>891856161</v>
       </c>
@@ -9366,7 +9952,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" ht="18.75" customHeight="1">
       <c r="A186" s="7">
         <v>892000458</v>
       </c>
@@ -9377,7 +9963,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" ht="18.75" customHeight="1">
       <c r="A187" s="7">
         <v>900451858</v>
       </c>
@@ -9388,7 +9974,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" ht="18.75" customHeight="1">
       <c r="A188" s="7">
         <v>800219192</v>
       </c>
@@ -9399,7 +9985,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" ht="18.75" customHeight="1">
       <c r="A189" s="7">
         <v>832002436</v>
       </c>
@@ -9410,7 +9996,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" ht="18.75" customHeight="1">
       <c r="A190" s="7">
         <v>832001966</v>
       </c>
@@ -9421,7 +10007,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" ht="18.75" customHeight="1">
       <c r="A191" s="7">
         <v>900841132</v>
       </c>
@@ -9432,7 +10018,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" ht="18.75" customHeight="1">
       <c r="A192" s="7">
         <v>900588182</v>
       </c>
@@ -9443,7 +10029,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" ht="18.75" customHeight="1">
       <c r="A193" s="7">
         <v>826002144</v>
       </c>
@@ -9454,7 +10040,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" ht="18.75" customHeight="1">
       <c r="A194" s="7">
         <v>846003067</v>
       </c>
@@ -9465,7 +10051,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" ht="18.75" customHeight="1">
       <c r="A195" s="7">
         <v>900241765</v>
       </c>
@@ -9476,7 +10062,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" ht="18.75" customHeight="1">
       <c r="A196" s="7">
         <v>900521595</v>
       </c>
@@ -9487,7 +10073,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" ht="18.75" customHeight="1">
       <c r="A197" s="7">
         <v>816003270</v>
       </c>
@@ -9498,7 +10084,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" ht="18.75" customHeight="1">
       <c r="A198" s="7">
         <v>890704555</v>
       </c>
@@ -9509,7 +10095,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" ht="18.75" customHeight="1">
       <c r="A199" s="7">
         <v>900232301</v>
       </c>
@@ -9520,7 +10106,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" ht="18.75" customHeight="1">
       <c r="A200" s="7">
         <v>830143831</v>
       </c>
@@ -9531,7 +10117,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" ht="18.75" customHeight="1">
       <c r="A201" s="7">
         <v>800099652</v>
       </c>
@@ -9542,7 +10128,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" ht="18.75" customHeight="1">
       <c r="A202" s="7">
         <v>891800570</v>
       </c>
@@ -9553,7 +10139,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" ht="18.75" customHeight="1">
       <c r="A203" s="7">
         <v>892099421</v>
       </c>
@@ -9564,7 +10150,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" ht="18.75" customHeight="1">
       <c r="A204" s="7">
         <v>900438068</v>
       </c>
@@ -9575,7 +10161,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" ht="18.75" customHeight="1">
       <c r="A205" s="7">
         <v>860037950</v>
       </c>
@@ -9586,7 +10172,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" ht="18.75" customHeight="1">
       <c r="A206" s="7">
         <v>890702408</v>
       </c>
@@ -9597,7 +10183,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" ht="18.75" customHeight="1">
       <c r="A207" s="7">
         <v>1015392989</v>
       </c>
@@ -9608,7 +10194,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" ht="18.75" customHeight="1">
       <c r="A208" s="7">
         <v>899999032</v>
       </c>
@@ -9619,7 +10205,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" ht="18.75" customHeight="1">
       <c r="A209" s="7">
         <v>881862576</v>
       </c>
@@ -9630,7 +10216,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" ht="18.75" customHeight="1">
       <c r="A210" s="7">
         <v>52411325</v>
       </c>
@@ -9641,7 +10227,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" ht="18.75" customHeight="1">
       <c r="A211" s="7">
         <v>901544725</v>
       </c>
@@ -9652,7 +10238,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" ht="18.75" customHeight="1">
       <c r="A212" s="7">
         <v>830009112</v>
       </c>
@@ -9663,7 +10249,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" ht="18.75" customHeight="1">
       <c r="A213" s="7">
         <v>900614302</v>
       </c>
@@ -9674,7 +10260,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" ht="18.75" customHeight="1">
       <c r="A214" s="7">
         <v>900055393</v>
       </c>
@@ -9685,7 +10271,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" ht="18.75" customHeight="1">
       <c r="A215" s="7">
         <v>1020720272</v>
       </c>
@@ -9696,7 +10282,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" ht="18.75" customHeight="1">
       <c r="A216" s="7">
         <v>844001355</v>
       </c>
@@ -9707,7 +10293,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" ht="18.75" customHeight="1">
       <c r="A217" s="7">
         <v>801001440</v>
       </c>
@@ -9718,7 +10304,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" ht="18.75" customHeight="1">
       <c r="A218" s="7">
         <v>800037021</v>
       </c>
@@ -9729,7 +10315,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" ht="18.75" customHeight="1">
       <c r="A219" s="7">
         <v>19457462</v>
       </c>
@@ -9740,7 +10326,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" ht="18.75" customHeight="1">
       <c r="A220" s="7">
         <v>890802356</v>
       </c>
@@ -9751,7 +10337,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" ht="18.75" customHeight="1">
       <c r="A221" s="7">
         <v>890801719</v>
       </c>
@@ -9762,7 +10348,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" ht="18.75" customHeight="1">
       <c r="A222" s="7">
         <v>901408039</v>
       </c>
@@ -9773,7 +10359,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" ht="18.75" customHeight="1">
       <c r="A223" s="7">
         <v>860002541</v>
       </c>
@@ -9784,7 +10370,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" ht="18.75" customHeight="1">
       <c r="A224" s="7">
         <v>900342064</v>
       </c>
@@ -9795,7 +10381,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" ht="18.75" customHeight="1">
       <c r="A225" s="7">
         <v>890801035</v>
       </c>
@@ -9806,7 +10392,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" ht="18.75" customHeight="1">
       <c r="A226" s="7">
         <v>802011972</v>
       </c>
@@ -9817,7 +10403,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" ht="18.75" customHeight="1">
       <c r="A227" s="7">
         <v>900407200</v>
       </c>
@@ -9828,7 +10414,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" ht="18.75" customHeight="1">
       <c r="A228" s="7">
         <v>813010145</v>
       </c>
@@ -9839,7 +10425,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" ht="18.75" customHeight="1">
       <c r="A229" s="7">
         <v>860070301</v>
       </c>
@@ -9850,7 +10436,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" ht="18.75" customHeight="1">
       <c r="A230" s="7">
         <v>890700666</v>
       </c>
@@ -9861,7 +10447,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" ht="18.75" customHeight="1">
       <c r="A231" s="7">
         <v>900308007</v>
       </c>
@@ -9872,7 +10458,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" ht="18.75" customHeight="1">
       <c r="A232" s="7">
         <v>891856372</v>
       </c>
@@ -9883,7 +10469,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" ht="18.75" customHeight="1">
       <c r="A233" s="7">
         <v>800065396</v>
       </c>
@@ -9894,7 +10480,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" ht="18.75" customHeight="1">
       <c r="A234" s="7">
         <v>901223046</v>
       </c>
@@ -9905,7 +10491,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" ht="18.75" customHeight="1">
       <c r="A235" s="7">
         <v>809010402</v>
       </c>
@@ -9916,7 +10502,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" ht="18.75" customHeight="1">
       <c r="A236" s="7">
         <v>891800231</v>
       </c>
@@ -9927,7 +10513,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" ht="18.75" customHeight="1">
       <c r="A237" s="7">
         <v>800119574</v>
       </c>
@@ -9938,7 +10524,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" ht="18.75" customHeight="1">
       <c r="A238" s="7">
         <v>80170827</v>
       </c>
@@ -9949,7 +10535,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" ht="18.75" customHeight="1">
       <c r="A239" s="7">
         <v>10286175</v>
       </c>
@@ -9960,7 +10546,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" ht="18.75" customHeight="1">
       <c r="A240" s="7">
         <v>900454188</v>
       </c>
@@ -9971,7 +10557,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" ht="18.75" customHeight="1">
       <c r="A241" s="7">
         <v>900057926</v>
       </c>
@@ -9982,7 +10568,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" ht="18.75" customHeight="1">
       <c r="A242" s="7">
         <v>844001911</v>
       </c>
@@ -9993,7 +10579,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" ht="18.75" customHeight="1">
       <c r="A243" s="7">
         <v>900526144</v>
       </c>
@@ -10004,7 +10590,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" ht="18.75" customHeight="1">
       <c r="A244" s="7">
         <v>900828394</v>
       </c>
@@ -10015,7 +10601,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" ht="18.75" customHeight="1">
       <c r="A245" s="7">
         <v>844001287</v>
       </c>
@@ -10026,7 +10612,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" ht="18.75" customHeight="1">
       <c r="A246" s="7">
         <v>900431131</v>
       </c>
@@ -10037,7 +10623,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" ht="18.75" customHeight="1">
       <c r="A247" s="7">
         <v>800037979</v>
       </c>
@@ -10048,7 +10634,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" ht="18.75" customHeight="1">
       <c r="A248" s="7">
         <v>890601210</v>
       </c>
@@ -10059,7 +10645,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" ht="18.75" customHeight="1">
       <c r="A249" s="7">
         <v>801001969</v>
       </c>
@@ -10070,7 +10656,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" ht="18.75" customHeight="1">
       <c r="A250" s="7">
         <v>890801944</v>
       </c>
@@ -10081,7 +10667,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" ht="18.75" customHeight="1">
       <c r="A251" s="7">
         <v>19419315</v>
       </c>
@@ -10092,7 +10678,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" ht="18.75" customHeight="1">
       <c r="A252" s="7">
         <v>900371613</v>
       </c>
@@ -10103,7 +10689,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" ht="18.75" customHeight="1">
       <c r="A253" s="7">
         <v>860015905</v>
       </c>
@@ -10114,7 +10700,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" ht="18.75" customHeight="1">
       <c r="A254" s="7">
         <v>900488920</v>
       </c>
@@ -10125,7 +10711,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" ht="18.75" customHeight="1">
       <c r="A255" s="7">
         <v>810000913</v>
       </c>
@@ -10136,7 +10722,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" ht="18.75" customHeight="1">
       <c r="A256" s="7">
         <v>900471504</v>
       </c>
@@ -10147,7 +10733,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" ht="18.75" customHeight="1">
       <c r="A257" s="7">
         <v>844003225</v>
       </c>
@@ -10158,7 +10744,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" ht="18.75" customHeight="1">
       <c r="A258" s="7">
         <v>830075393</v>
       </c>
@@ -10169,7 +10755,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" ht="18.75" customHeight="1">
       <c r="A259" s="7">
         <v>900058218</v>
       </c>
@@ -10180,7 +10766,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" ht="18.75" customHeight="1">
       <c r="A260" s="7">
         <v>901295822</v>
       </c>
@@ -10191,7 +10777,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" ht="18.75" customHeight="1">
       <c r="A261" s="4">
         <v>900381555</v>
       </c>
@@ -10202,7 +10788,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" ht="18.75" customHeight="1">
       <c r="A262" s="7">
         <v>830117846</v>
       </c>
@@ -10213,7 +10799,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" ht="18.75" customHeight="1">
       <c r="A263" s="7">
         <v>901017982</v>
       </c>
@@ -10224,7 +10810,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" ht="18.75" customHeight="1">
       <c r="A264" s="4">
         <v>900314301</v>
       </c>
@@ -10235,7 +10821,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" ht="18.75" customHeight="1">
       <c r="A265" s="4">
         <v>901881050</v>
       </c>
@@ -10246,7 +10832,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" ht="18.75" customHeight="1">
       <c r="A266" s="4">
         <v>891180134</v>
       </c>
@@ -10257,7 +10843,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" ht="18.75" customHeight="1">
       <c r="A267" s="7">
         <v>900407111</v>
       </c>
@@ -10268,7 +10854,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" ht="18.75" customHeight="1">
       <c r="A268" s="4">
         <v>900112820</v>
       </c>
@@ -10279,7 +10865,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" ht="18.75" customHeight="1">
       <c r="A269" s="7">
         <v>901169422</v>
       </c>
@@ -10290,7 +10876,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" ht="18.75" customHeight="1">
       <c r="A270" s="4">
         <v>900108793</v>
       </c>
@@ -10301,7 +10887,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" ht="18.75" customHeight="1">
       <c r="A271" s="7">
         <v>900576170</v>
       </c>
@@ -10312,7 +10898,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" ht="18.75" customHeight="1">
       <c r="A272" s="4">
         <v>891180268</v>
       </c>
@@ -10323,7 +10909,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" ht="18.75" customHeight="1">
       <c r="A273" s="7">
         <v>900678145</v>
       </c>
@@ -10334,7 +10920,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" ht="18.75" customHeight="1">
       <c r="A274" s="7">
         <v>900627725</v>
       </c>
@@ -10345,7 +10931,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" ht="18.75" customHeight="1">
       <c r="A275" s="7">
         <v>891411743</v>
       </c>
@@ -10356,7 +10942,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" ht="18.75" customHeight="1">
       <c r="A276" s="7">
         <v>900077520</v>
       </c>
@@ -10367,7 +10953,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" ht="18.75" customHeight="1">
       <c r="A277" s="4">
         <v>900958564</v>
       </c>
@@ -10378,7 +10964,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" ht="18.75" customHeight="1">
       <c r="A278" s="7">
         <v>800200789</v>
       </c>
@@ -10389,7 +10975,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" ht="18.75" customHeight="1">
       <c r="A279" s="7">
         <v>900061048</v>
       </c>
@@ -10400,7 +10986,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" ht="18.75" customHeight="1">
       <c r="A280" s="7">
         <v>901127904</v>
       </c>
@@ -10411,7 +10997,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" ht="18.75" customHeight="1">
       <c r="A281" s="7">
         <v>890801562</v>
       </c>
@@ -10422,7 +11008,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" ht="18.75" customHeight="1">
       <c r="A282" s="4">
         <v>80055710</v>
       </c>
@@ -10433,7 +11019,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" ht="18.75" customHeight="1">
       <c r="A283" s="7">
         <v>79442674</v>
       </c>
@@ -10444,7 +11030,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" ht="18.75" customHeight="1">
       <c r="A284" s="4">
         <v>891856507</v>
       </c>
@@ -10455,7 +11041,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" ht="18.75" customHeight="1">
       <c r="A285" s="7">
         <v>900231829</v>
       </c>
@@ -10466,7 +11052,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" ht="18.75" customHeight="1">
       <c r="A286" s="7">
         <v>900171988</v>
       </c>
@@ -10477,7 +11063,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" ht="18.75" customHeight="1">
       <c r="A287" s="7">
         <v>891180098</v>
       </c>
@@ -10488,7 +11074,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" ht="18.75" customHeight="1">
       <c r="A288" s="7">
         <v>845000038</v>
       </c>
@@ -10499,7 +11085,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" ht="18.75" customHeight="1">
       <c r="A289" s="4">
         <v>900817788</v>
       </c>
@@ -10510,7 +11096,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" ht="18.75" customHeight="1">
       <c r="A290" s="4">
         <v>899999147</v>
       </c>
@@ -10521,7 +11107,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" ht="18.75" customHeight="1">
       <c r="A291" s="4">
         <v>900419180</v>
       </c>
@@ -10532,7 +11118,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" ht="18.75" customHeight="1">
       <c r="A292" s="7">
         <v>830119200</v>
       </c>
@@ -10543,7 +11129,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" ht="18.75" customHeight="1">
       <c r="A293" s="7">
         <v>890801495</v>
       </c>
@@ -10554,7 +11140,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" ht="18.75" customHeight="1">
       <c r="A294" s="4">
         <v>900582598</v>
       </c>
@@ -10565,7 +11151,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" ht="18.75" customHeight="1">
       <c r="A295" s="4">
         <v>890802036</v>
       </c>
@@ -10576,7 +11162,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" ht="18.75" customHeight="1">
       <c r="A296" s="7">
         <v>900462440</v>
       </c>
@@ -10587,7 +11173,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" ht="18.75" customHeight="1">
       <c r="A297" s="4">
         <v>846000474</v>
       </c>
@@ -10598,7 +11184,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" ht="18.75" customHeight="1">
       <c r="A298" s="7">
         <v>800000118</v>
       </c>
@@ -10609,7 +11195,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" ht="18.75" customHeight="1">
       <c r="A299" s="4">
         <v>900211468</v>
       </c>
@@ -10620,7 +11206,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" ht="18.75" customHeight="1">
       <c r="A300" s="4">
         <v>891855438</v>
       </c>
@@ -10631,7 +11217,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" ht="18.75" customHeight="1">
       <c r="A301" s="7">
         <v>19364579</v>
       </c>
@@ -10642,7 +11228,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" ht="18.75" customHeight="1">
       <c r="A302" s="7">
         <v>900004059</v>
       </c>
@@ -10653,7 +11239,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" ht="18.75" customHeight="1">
       <c r="A303" s="7">
         <v>846003357</v>
       </c>
@@ -10664,7 +11250,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" ht="18.75" customHeight="1">
       <c r="A304" s="7">
         <v>901457374</v>
       </c>
@@ -10675,7 +11261,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" ht="18.75" customHeight="1">
       <c r="A305" s="4">
         <v>830005028</v>
       </c>
@@ -10686,7 +11272,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" ht="18.75" customHeight="1">
       <c r="A306" s="4">
         <v>900606412</v>
       </c>
@@ -10697,7 +11283,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" ht="18.75" customHeight="1">
       <c r="A307" s="7">
         <v>830113849</v>
       </c>
@@ -10708,7 +11294,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" ht="18.75" customHeight="1">
       <c r="A308" s="4">
         <v>900232628</v>
       </c>
@@ -10719,7 +11305,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" ht="18.75" customHeight="1">
       <c r="A309" s="7">
         <v>890706823</v>
       </c>
@@ -10730,7 +11316,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" ht="18.75" customHeight="1">
       <c r="A310" s="7">
         <v>901105417</v>
       </c>
@@ -10741,7 +11327,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" ht="18.75" customHeight="1">
       <c r="A311" s="7">
         <v>800037202</v>
       </c>
@@ -10752,7 +11338,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" ht="18.75" customHeight="1">
       <c r="A312" s="7">
         <v>80412859</v>
       </c>
@@ -10763,7 +11349,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" ht="18.75" customHeight="1">
       <c r="A313" s="15">
         <v>800180553</v>
       </c>
@@ -10774,7 +11360,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" ht="18.75" customHeight="1">
       <c r="A314" s="7">
         <v>891411381</v>
       </c>
@@ -10785,7 +11371,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" ht="18.75" customHeight="1">
       <c r="A315" s="7">
         <v>814003448</v>
       </c>
@@ -10796,7 +11382,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3" ht="18.75" customHeight="1">
       <c r="A316" s="7">
         <v>891180026</v>
       </c>
@@ -10807,7 +11393,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:3" ht="18.75" customHeight="1">
       <c r="A317" s="7">
         <v>900233110</v>
       </c>
@@ -10818,7 +11404,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:3" ht="18.75" customHeight="1">
       <c r="A318" s="7">
         <v>860013570</v>
       </c>
@@ -10829,7 +11415,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:3" ht="18.75" customHeight="1">
       <c r="A319" s="7">
         <v>901652147</v>
       </c>
@@ -10840,7 +11426,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:3" ht="18.75" customHeight="1">
       <c r="A320" s="7">
         <v>901439163</v>
       </c>
@@ -10851,7 +11437,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3" ht="18.75" customHeight="1">
       <c r="A321" s="7">
         <v>822000946</v>
       </c>
@@ -10862,7 +11448,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" ht="18.75" customHeight="1">
       <c r="A322" s="7">
         <v>810001466</v>
       </c>
@@ -10873,7 +11459,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:3" ht="18.75" customHeight="1">
       <c r="A323" s="7">
         <v>900547903</v>
       </c>
@@ -10884,7 +11470,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:3" ht="18.75" customHeight="1">
       <c r="A324" s="7">
         <v>800228215</v>
       </c>
@@ -10895,7 +11481,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:3" ht="18.75" customHeight="1">
       <c r="A325" s="7">
         <v>890802978</v>
       </c>
@@ -10906,7 +11492,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3" ht="18.75" customHeight="1">
       <c r="A326" s="7">
         <v>800135582</v>
       </c>
@@ -10917,7 +11503,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" ht="18.75" customHeight="1">
       <c r="A327" s="7">
         <v>900364721</v>
       </c>
@@ -10928,7 +11514,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:3" ht="18.75" customHeight="1">
       <c r="A328" s="7">
         <v>899999123</v>
       </c>
@@ -10939,7 +11525,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3" ht="18.75" customHeight="1">
       <c r="A329" s="7">
         <v>890801099</v>
       </c>
@@ -10950,7 +11536,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:3" ht="18.75" customHeight="1">
       <c r="A330" s="7">
         <v>830018305</v>
       </c>
@@ -10961,7 +11547,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:3" ht="18.75" customHeight="1">
       <c r="A331" s="7">
         <v>809001482</v>
       </c>
@@ -10972,7 +11558,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3" ht="18.75" customHeight="1">
       <c r="A332" s="7">
         <v>900685235</v>
       </c>
@@ -10983,7 +11569,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:3" ht="18.75" customHeight="1">
       <c r="A333" s="7">
         <v>800191101</v>
       </c>
@@ -10994,7 +11580,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:3" ht="18.75" customHeight="1">
       <c r="A334" s="7">
         <v>891409981</v>
       </c>
@@ -11005,7 +11591,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" ht="18.75" customHeight="1">
       <c r="A335" s="7">
         <v>900073806</v>
       </c>
@@ -11016,7 +11602,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:3" ht="18.75" customHeight="1">
       <c r="A336" s="7">
         <v>900493064</v>
       </c>
@@ -11027,7 +11613,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3" ht="18.75" customHeight="1">
       <c r="A337" s="7">
         <v>800231235</v>
       </c>
@@ -11038,7 +11624,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:3" ht="18.75" customHeight="1">
       <c r="A338" s="7">
         <v>860007373</v>
       </c>
@@ -11049,7 +11635,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:3" ht="18.75" customHeight="1">
       <c r="A339" s="7">
         <v>900848340</v>
       </c>
@@ -11060,7 +11646,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:3" ht="18.75" customHeight="1">
       <c r="A340" s="4">
         <v>900115642</v>
       </c>
@@ -11071,7 +11657,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:3" ht="18.75" customHeight="1">
       <c r="A341" s="7">
         <v>79533241</v>
       </c>
@@ -11082,7 +11668,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:3" ht="18.75" customHeight="1">
       <c r="A342" s="4">
         <v>830502282</v>
       </c>
@@ -11093,7 +11679,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:3" ht="18.75" customHeight="1">
       <c r="A343" s="7">
         <v>900081643</v>
       </c>
@@ -11104,7 +11690,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:3" ht="18.75" customHeight="1">
       <c r="A344" s="7">
         <v>891855039</v>
       </c>
@@ -11115,7 +11701,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:3" ht="18.75" customHeight="1">
       <c r="A345" s="7">
         <v>805017681</v>
       </c>
@@ -11126,7 +11712,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:3" ht="18.75" customHeight="1">
       <c r="A346" s="7">
         <v>820002248</v>
       </c>
@@ -11137,7 +11723,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:3" ht="18.75" customHeight="1">
       <c r="A347" s="7">
         <v>860024026</v>
       </c>
@@ -11148,7 +11734,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:3" ht="18.75" customHeight="1">
       <c r="A348" s="7">
         <v>71394225</v>
       </c>
@@ -11159,7 +11745,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:3" ht="18.75" customHeight="1">
       <c r="A349" s="7">
         <v>832008321</v>
       </c>
@@ -11170,7 +11756,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:3" ht="18.75" customHeight="1">
       <c r="A350" s="7">
         <v>901632467</v>
       </c>
@@ -11181,7 +11767,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:3" ht="18.75" customHeight="1">
       <c r="A351" s="7">
         <v>891180117</v>
       </c>
@@ -11192,7 +11778,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:3" ht="18.75" customHeight="1">
       <c r="A352" s="7">
         <v>900759329</v>
       </c>
@@ -11203,7 +11789,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:3" ht="18.75" customHeight="1">
       <c r="A353" s="7">
         <v>891800644</v>
       </c>
@@ -11214,7 +11800,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:3" ht="18.75" customHeight="1">
       <c r="A354" s="4">
         <v>800254132</v>
       </c>
@@ -11225,7 +11811,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:3" ht="18.75" customHeight="1">
       <c r="A355" s="7">
         <v>899999158</v>
       </c>
@@ -11236,7 +11822,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:3" ht="18.75" customHeight="1">
       <c r="A356" s="4">
         <v>79624744</v>
       </c>
@@ -11247,7 +11833,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:3" ht="18.75" customHeight="1">
       <c r="A357" s="7">
         <v>891409390</v>
       </c>
@@ -11258,7 +11844,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:3" ht="18.75" customHeight="1">
       <c r="A358" s="7">
         <v>890680014</v>
       </c>
@@ -11269,7 +11855,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:3" ht="18.75" customHeight="1">
       <c r="A359" s="7">
         <v>809006690</v>
       </c>
@@ -11280,7 +11866,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:3" ht="18.75" customHeight="1">
       <c r="A360" s="7">
         <v>900213617</v>
       </c>
@@ -11291,7 +11877,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:3" ht="18.75" customHeight="1">
       <c r="A361" s="4">
         <v>900423816</v>
       </c>
@@ -11302,7 +11888,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:3" ht="18.75" customHeight="1">
       <c r="A362" s="4">
         <v>860015929</v>
       </c>
@@ -11313,7 +11899,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:3" ht="18.75" customHeight="1">
       <c r="A363" s="4">
         <v>890806490</v>
       </c>
@@ -11324,7 +11910,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:3" ht="18.75" customHeight="1">
       <c r="A364" s="4">
         <v>860006626</v>
       </c>
@@ -11335,7 +11921,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:3" ht="18.75" customHeight="1">
       <c r="A365" s="4">
         <v>813005295</v>
       </c>
@@ -11346,7 +11932,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:3" ht="18.75" customHeight="1">
       <c r="A366" s="4">
         <v>846001425</v>
       </c>
@@ -11357,7 +11943,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:3" ht="18.75" customHeight="1">
       <c r="A367" s="4">
         <v>800139366</v>
       </c>
@@ -11368,7 +11954,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:3" ht="18.75" customHeight="1">
       <c r="A368" s="4">
         <v>816005003</v>
       </c>
@@ -11379,7 +11965,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:3" ht="18.75" customHeight="1">
       <c r="A369" s="4">
         <v>900435790</v>
       </c>
@@ -11390,12 +11976,12 @@
         <v>738</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" ht="18.75" customHeight="1">
       <c r="A370" s="19"/>
       <c r="B370" s="20"/>
       <c r="C370" s="21"/>
     </row>
-    <row r="371" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" ht="18.75" customHeight="1">
       <c r="A371" s="19"/>
       <c r="B371" s="20"/>
       <c r="C371" s="21"/>

--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/SOPORTES DE MEDICION/soportes de medicon.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/SOPORTES DE MEDICION/soportes de medicon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AGS\DESARROLLO\GITHUB\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\SOPORTES DE MEDICION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\SOPORTES DE MEDICION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B168DAE8-BD46-4F5F-AD18-D4488C684B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE8217A-4597-445D-8A15-43CAB650CD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -32,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="790">
   <si>
     <t>NIT</t>
   </si>
@@ -2310,101 +2307,114 @@
     <t>Periodo evaluado</t>
   </si>
   <si>
-    <t>ERIKA ANDREA CHAVES RIVERA</t>
-  </si>
-  <si>
-    <t>JHON FREDY RAMIREZ TANGARIFE</t>
-  </si>
-  <si>
-    <t>YAMIL ANTONIO JIMENEZ DIAZ</t>
-  </si>
-  <si>
-    <t>JUAN GABRIEL NIZO SANABRIA</t>
-  </si>
-  <si>
-    <t>VICTOR ANDRES SOTO HENAO</t>
-  </si>
-  <si>
-    <t>JUAN HEYLER LOPEZ MOSQUERA</t>
-  </si>
-  <si>
-    <t>VIVIANA LOPEZ PATIÑO</t>
-  </si>
-  <si>
-    <t>CHRISTIAN FERNANDO LONDOÑO ARIAS</t>
-  </si>
-  <si>
-    <t>MARIA MARGOTH OSPINA ARROYAVE</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS CAICEDO RAMIREZ</t>
-  </si>
-  <si>
-    <t>DARWIN ANDRES GONZALEZ RIVERA</t>
-  </si>
-  <si>
-    <t>ANDRES ALFONSO ZAMORA GOMEZ</t>
-  </si>
-  <si>
-    <t>GUILLERMO MORALES BARON</t>
-  </si>
-  <si>
-    <t>CALVO SAMUEL VARGAS</t>
-  </si>
-  <si>
-    <t>JOSE DELACRUZ AYALA BUENO</t>
-  </si>
-  <si>
-    <t>LEIDER ENRIQUE LLAMAS DIAZ</t>
-  </si>
-  <si>
-    <t>YOLANDA CAICEDO PRADO</t>
-  </si>
-  <si>
-    <t>MARIA DELSOCORRO GUASCA MORENO</t>
-  </si>
-  <si>
-    <t>YONY RAFAEL PALACIN ALTAHONA</t>
-  </si>
-  <si>
-    <t>CLARA INES AGUDELO HENAO</t>
-  </si>
-  <si>
-    <t>CARLOS ANDRES PEREZ CASTRO</t>
-  </si>
-  <si>
-    <t>ORLANDO CASTRO VEGA</t>
-  </si>
-  <si>
     <t>"CEDULA PACIENTE "</t>
   </si>
   <si>
     <t>NOMBRE DEL PACIENTE</t>
   </si>
   <si>
-    <t>Teniendo en cuenta su experiencia con la atención brindada por el proveedor, por favor califique en una escala del 1 al 5 la atención recibida en donde 1 es “Malo” y 5 es “Excelente” los siguientes at</t>
-  </si>
-  <si>
-    <t>Infraestructura y dotación de las instalaciones de la IPS o calidad de llamada.</t>
-  </si>
-  <si>
-    <t>Calidad en el servicio prestado por parte del profesional de salud</t>
-  </si>
-  <si>
-    <t>Teniendo en cuenta la respuesta anterior, por favor elija una de las siguientes opciones indicando el motivo por el cual no ha solicitado la programación del servicio.</t>
-  </si>
-  <si>
-    <t>I TRIMESTRE</t>
-  </si>
-  <si>
-    <t>Para la siguiente pregunta, por favor responda SI o NO  ¿Tuvo servicio con el prestador?</t>
+    <t xml:space="preserve">HECTOR  MOSQUERA PALACIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS ANGEL URIBE ARBOLEDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HERNANDO DE JESUS PEREZ PEREZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVAN DARIO GRONDONA LAVALLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORGE OMAR TELLEZ LOPEZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEGO  RIVERA  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARID  JAMA GAVIRIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">YEFERSON  PAEZ JIMENEZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AYDE ALEXANDRA LOPEZ SANCHEZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE LEONEL ATEHORTUA  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMAR AUGUSTO ARBOLEDA LOPEZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ELIAS SANABRIA PULIDO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASTRID KARINA TAPIERO ORJUELA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIGUEL EDUARDO AGUILERA MALDONADO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDIES ALFONSO OLAYA JIMENEZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS FERNANDO GARCIA ALFONSO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDER  CACERES MORENO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICTOR EMILIO FRANCO CHICA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIAN CAMILO HERRERA OSORIO </t>
+  </si>
+  <si>
+    <t>ABRIL 2026.</t>
+  </si>
+  <si>
+    <t>El servicio o entrega ya fue realizado</t>
+  </si>
+  <si>
+    <t>LA PRÓTESIS,ORTESIS Y/O INSUMO ENTREGADO CUMPLE CON LAS ESPECIFICACIONES TÉCNICAS DADAS
+  POR EL MÉDICO TRATANTE</t>
+  </si>
+  <si>
+    <t>¿LA PRÓTESIS, ORTESIS Y/O INSUMO LE HA GENERADO ALGUNA LESIÓN DURANTE SU USO?</t>
+  </si>
+  <si>
+    <t>4. OPORTUNIDAD EN LA ATENCIÓN PRESTADA POR LA IPS</t>
+  </si>
+  <si>
+    <t>5. CALIDAD EN EL SERVICIO PRESTADO POR PARTE DEL PROFESIONAL Y/O PERSONAL ADMINISTRATIVO</t>
+  </si>
+  <si>
+    <t>6. INFRAESTRUCTURA Y DOTACIÓN DE LAS INSTALACIONES DE LA IPS</t>
+  </si>
+  <si>
+    <t>Observaciones, por favor poner una observacion puntual que notifique el usuario.</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USUARIO INDICA QUE YA LE REALIZARON LA ENTREGA PERO ESTA A LA ESPERA DE LA NUEVA ENTREGA POR PARTE DE LA IPS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOS PRODUCTOS SON DE MUY BUENA CALIDAD PERO ATENCION AL CLIENTE NUNCA CONTESTAN LOS TELEFONOS, LA DEJAN EN VISTO Y EL TIEMPO DE ESPERA FUE DE CASI 20 DIAS PARA UNA RESPUESTA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La baja calificación se debe a que ellos no viven cerca a la ips y los llaman el mismo día para que se acerquen a las instalaciones lo cual no es posible y ellos ya se lo habían comunicado a la ips </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usuario indica que liner a los 15 dias ya presento fractura y ya reporto a la ips otto bock de este daño </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2572,7 +2582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2708,9 +2718,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3051,705 +3058,757 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" style="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" style="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.5703125" style="26" customWidth="1"/>
     <col min="4" max="4" width="21.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="21.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" customWidth="1"/>
+    <col min="5" max="7" width="21.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" style="25" customWidth="1"/>
+    <col min="9" max="10" width="21.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="150">
-      <c r="A1" s="47" t="s">
-        <v>778</v>
-      </c>
-      <c r="B1" s="47" t="s">
-        <v>779</v>
+    <row r="1" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
+        <v>756</v>
+      </c>
+      <c r="B1" s="46" t="s">
+        <v>757</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>755</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="46" t="s">
+        <v>778</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>779</v>
+      </c>
+      <c r="F1" s="46" t="s">
+        <v>780</v>
+      </c>
+      <c r="G1" s="46" t="s">
+        <v>781</v>
+      </c>
+      <c r="H1" s="46" t="s">
+        <v>782</v>
+      </c>
+      <c r="I1" s="46" t="s">
+        <v>783</v>
+      </c>
+      <c r="J1" s="46" t="s">
+        <v>784</v>
+      </c>
+      <c r="K1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="27" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="25">
+        <v>98593306</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>758</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>739</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>739</v>
+      </c>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46">
+        <v>5</v>
+      </c>
+      <c r="H2" s="46">
+        <v>5</v>
+      </c>
+      <c r="I2" s="46">
+        <v>5</v>
+      </c>
+      <c r="J2" s="46" t="s">
         <v>785</v>
       </c>
-      <c r="E1" s="47" t="s">
-        <v>780</v>
-      </c>
-      <c r="F1" s="47" t="s">
-        <v>781</v>
-      </c>
-      <c r="G1" s="47" t="s">
-        <v>782</v>
-      </c>
-      <c r="H1" s="47" t="s">
-        <v>783</v>
-      </c>
-      <c r="I1" s="27" t="s">
+      <c r="K2" t="s">
+        <v>629</v>
+      </c>
+      <c r="L2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="25">
+        <v>18603619</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>759</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>739</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>739</v>
+      </c>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46">
+        <v>5</v>
+      </c>
+      <c r="H3" s="46">
+        <v>5</v>
+      </c>
+      <c r="I3" s="46">
+        <v>5</v>
+      </c>
+      <c r="J3" s="46" t="s">
+        <v>785</v>
+      </c>
+      <c r="K3" t="s">
+        <v>629</v>
+      </c>
+      <c r="L3" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="25">
+        <v>79360819</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>760</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>739</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G4" s="25">
+        <v>4</v>
+      </c>
+      <c r="H4" s="25">
+        <v>4</v>
+      </c>
+      <c r="I4" s="25">
+        <v>4</v>
+      </c>
+      <c r="J4" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K4" t="s">
+        <v>629</v>
+      </c>
+      <c r="L4" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="25">
+        <v>9101283</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>761</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>739</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G5" s="25">
+        <v>5</v>
+      </c>
+      <c r="H5" s="25">
+        <v>5</v>
+      </c>
+      <c r="I5" s="25">
+        <v>5</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K5" t="s">
+        <v>629</v>
+      </c>
+      <c r="L5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="25">
+        <v>88000467</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>762</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>739</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G6" s="25">
+        <v>3</v>
+      </c>
+      <c r="H6" s="25">
+        <v>5</v>
+      </c>
+      <c r="I6" s="25">
+        <v>4</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K6" t="s">
+        <v>629</v>
+      </c>
+      <c r="L6" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="25">
+        <v>71606391</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>763</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>739</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G7" s="25">
+        <v>5</v>
+      </c>
+      <c r="H7" s="25">
+        <v>5</v>
+      </c>
+      <c r="I7" s="25">
+        <v>5</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K7" t="s">
+        <v>629</v>
+      </c>
+      <c r="L7" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
+        <v>94397050</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>764</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>739</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G8" s="25">
+        <v>5</v>
+      </c>
+      <c r="H8" s="25">
+        <v>5</v>
+      </c>
+      <c r="I8" s="25">
+        <v>5</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K8" t="s">
+        <v>453</v>
+      </c>
+      <c r="L8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" s="25">
+        <v>1003879678</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>765</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>739</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G9" s="25">
+        <v>5</v>
+      </c>
+      <c r="H9" s="25">
+        <v>5</v>
+      </c>
+      <c r="I9" s="25">
+        <v>5</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>786</v>
+      </c>
+      <c r="K9" t="s">
+        <v>453</v>
+      </c>
+      <c r="L9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="A10" s="25">
+        <v>51978011</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>766</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>739</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G10" s="25">
+        <v>3</v>
+      </c>
+      <c r="H10" s="25">
         <v>1</v>
       </c>
-      <c r="J1" s="27" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="30">
-      <c r="A2" s="46">
-        <v>1080000000</v>
-      </c>
-      <c r="B2" s="47" t="s">
-        <v>756</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D2" s="47" t="s">
+      <c r="I10" s="25">
+        <v>5</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>787</v>
+      </c>
+      <c r="K10" t="s">
+        <v>740</v>
+      </c>
+      <c r="L10" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="25">
+        <v>70952968</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>767</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D11" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="E2" s="47">
+      <c r="E11" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G11" s="25">
         <v>5</v>
       </c>
-      <c r="F2" s="47">
+      <c r="H11" s="25">
         <v>5</v>
       </c>
-      <c r="G2" s="47">
+      <c r="I11" s="25">
         <v>5</v>
       </c>
-      <c r="H2" s="47"/>
-      <c r="I2" t="s">
-        <v>421</v>
-      </c>
-      <c r="J2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="30">
-      <c r="A3" s="47">
-        <v>10189175</v>
-      </c>
-      <c r="B3" s="47" t="s">
-        <v>757</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D3" s="47" t="s">
+      <c r="J11" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K11" t="s">
+        <v>683</v>
+      </c>
+      <c r="L11" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="25">
+        <v>98492991</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>768</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D12" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="E3" s="47">
+      <c r="E12" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G12" s="25">
         <v>5</v>
       </c>
-      <c r="F3" s="47">
+      <c r="H12" s="25">
         <v>5</v>
       </c>
-      <c r="G3" s="47">
+      <c r="I12" s="25">
         <v>5</v>
       </c>
-      <c r="H3" s="47"/>
-      <c r="I3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="30">
-      <c r="A4" s="47">
-        <v>12523155</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>758</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D4" s="47" t="s">
+      <c r="J12" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K12" t="s">
+        <v>683</v>
+      </c>
+      <c r="L12" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="25">
+        <v>79043668</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>769</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D13" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="E4" s="47">
+      <c r="E13" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G13" s="25">
         <v>5</v>
       </c>
-      <c r="F4" s="47">
+      <c r="H13" s="25">
         <v>5</v>
       </c>
-      <c r="G4" s="47">
+      <c r="I13" s="25">
         <v>5</v>
       </c>
-      <c r="H4" s="47"/>
-      <c r="I4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="30">
-      <c r="A5" s="46">
-        <v>1080000000</v>
-      </c>
-      <c r="B5" s="47" t="s">
-        <v>759</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D5" s="47" t="s">
+      <c r="J13" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K13" t="s">
+        <v>583</v>
+      </c>
+      <c r="L13" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="25">
+        <v>52951642</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>770</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D14" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E14" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G14" s="25">
         <v>5</v>
       </c>
-      <c r="F5" s="47">
+      <c r="H14" s="25">
         <v>5</v>
       </c>
-      <c r="G5" s="47">
+      <c r="I14" s="25">
         <v>5</v>
       </c>
-      <c r="H5" s="47"/>
-      <c r="I5" t="s">
-        <v>697</v>
-      </c>
-      <c r="J5" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="30">
-      <c r="A6" s="47">
-        <v>16229103</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>760</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D6" s="47" t="s">
+      <c r="J14" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K14" t="s">
+        <v>740</v>
+      </c>
+      <c r="L14" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="25">
+        <v>79535094</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>771</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D15" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E15" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G15" s="25">
         <v>5</v>
       </c>
-      <c r="F6" s="47">
+      <c r="H15" s="25">
         <v>5</v>
       </c>
-      <c r="G6" s="47">
+      <c r="I15" s="25">
+        <v>4</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K15" t="s">
+        <v>740</v>
+      </c>
+      <c r="L15" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="25">
+        <v>19615758</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>772</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>739</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G16" s="25">
         <v>5</v>
       </c>
-      <c r="H6" s="47"/>
-      <c r="I6" t="s">
-        <v>735</v>
-      </c>
-      <c r="J6" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="30">
-      <c r="A7" s="46">
-        <v>1080000000</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>761</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D7" s="47" t="s">
+      <c r="H16" s="25">
+        <v>5</v>
+      </c>
+      <c r="I16" s="25">
+        <v>5</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K16" t="s">
+        <v>740</v>
+      </c>
+      <c r="L16" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="25">
+        <v>19615758</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>772</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D17" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E17" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G17" s="25">
         <v>5</v>
       </c>
-      <c r="F7" s="47">
+      <c r="H17" s="25">
         <v>5</v>
       </c>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" t="s">
-        <v>735</v>
-      </c>
-      <c r="J7" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="30">
-      <c r="A8" s="47">
-        <v>43463667</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>762</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D8" s="47" t="s">
+      <c r="I17" s="25">
+        <v>5</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K17" t="s">
+        <v>740</v>
+      </c>
+      <c r="L17" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="25">
+        <v>3170477</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D18" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E18" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G18" s="25">
         <v>5</v>
       </c>
-      <c r="F8" s="47">
+      <c r="H18" s="25">
         <v>5</v>
       </c>
-      <c r="G8" s="47">
+      <c r="I18" s="25">
         <v>5</v>
       </c>
-      <c r="H8" s="47"/>
-      <c r="I8" t="s">
-        <v>7</v>
-      </c>
-      <c r="J8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="30">
-      <c r="A9" s="46">
-        <v>1090000000</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>763</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D9" s="47" t="s">
+      <c r="J18" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K18" t="s">
+        <v>740</v>
+      </c>
+      <c r="L18" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="A19" s="25">
+        <v>16888656</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>774</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D19" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E19" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G19" s="25">
+        <v>4</v>
+      </c>
+      <c r="H19" s="25">
+        <v>3</v>
+      </c>
+      <c r="I19" s="25">
+        <v>4</v>
+      </c>
+      <c r="J19" s="25" t="s">
+        <v>788</v>
+      </c>
+      <c r="K19" t="s">
+        <v>740</v>
+      </c>
+      <c r="L19" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A20" s="25">
+        <v>1054986234</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>775</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>739</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G20" s="25">
         <v>5</v>
       </c>
-      <c r="F9" s="47">
+      <c r="H20" s="25">
         <v>5</v>
       </c>
-      <c r="G9" s="47">
+      <c r="I20" s="25">
         <v>5</v>
       </c>
-      <c r="H9" s="47"/>
-      <c r="I9" t="s">
-        <v>89</v>
-      </c>
-      <c r="J9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="30">
-      <c r="A10" s="47">
-        <v>42732677</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>764</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D10" s="47" t="s">
+      <c r="J20" s="25" t="s">
+        <v>789</v>
+      </c>
+      <c r="K20" t="s">
+        <v>740</v>
+      </c>
+      <c r="L20" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>1112391381</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>776</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D21" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E21" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="G21" s="25">
         <v>5</v>
       </c>
-      <c r="F10" s="47">
+      <c r="H21" s="25">
+        <v>5</v>
+      </c>
+      <c r="I21" s="25">
         <v>3</v>
       </c>
-      <c r="G10" s="47">
-        <v>3</v>
-      </c>
-      <c r="H10" s="47"/>
-      <c r="I10" t="s">
-        <v>665</v>
-      </c>
-      <c r="J10" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="30">
-      <c r="A11" s="47">
-        <v>96355191</v>
-      </c>
-      <c r="B11" s="47" t="s">
-        <v>765</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E11" s="47">
-        <v>4</v>
-      </c>
-      <c r="F11" s="47">
-        <v>4</v>
-      </c>
-      <c r="G11" s="47">
-        <v>4</v>
-      </c>
-      <c r="H11" s="47"/>
-      <c r="I11" t="s">
-        <v>103</v>
-      </c>
-      <c r="J11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30">
-      <c r="A12" s="47">
-        <v>75094270</v>
-      </c>
-      <c r="B12" s="47" t="s">
-        <v>766</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E12" s="47">
-        <v>5</v>
-      </c>
-      <c r="F12" s="47">
-        <v>5</v>
-      </c>
-      <c r="G12" s="47">
-        <v>5</v>
-      </c>
-      <c r="H12" s="47"/>
-      <c r="I12" t="s">
-        <v>733</v>
-      </c>
-      <c r="J12" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30">
-      <c r="A13" s="46">
-        <v>1080000000</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>767</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D13" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E13" s="47">
-        <v>5</v>
-      </c>
-      <c r="F13" s="47">
-        <v>5</v>
-      </c>
-      <c r="G13" s="47">
-        <v>5</v>
-      </c>
-      <c r="H13" s="47"/>
-      <c r="I13" t="s">
-        <v>709</v>
-      </c>
-      <c r="J13" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30">
-      <c r="A14" s="47">
-        <v>75034165</v>
-      </c>
-      <c r="B14" s="47" t="s">
-        <v>768</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E14" s="47">
-        <v>5</v>
-      </c>
-      <c r="F14" s="47">
-        <v>5</v>
-      </c>
-      <c r="G14" s="47">
-        <v>5</v>
-      </c>
-      <c r="H14" s="47"/>
-      <c r="I14" t="s">
-        <v>561</v>
-      </c>
-      <c r="J14" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30">
-      <c r="A15" s="46">
-        <v>1060000000</v>
-      </c>
-      <c r="B15" s="47" t="s">
-        <v>769</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E15" s="47">
-        <v>5</v>
-      </c>
-      <c r="F15" s="47">
-        <v>5</v>
-      </c>
-      <c r="G15" s="47">
-        <v>5</v>
-      </c>
-      <c r="H15" s="47"/>
-      <c r="I15" t="s">
-        <v>273</v>
-      </c>
-      <c r="J15" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="30">
-      <c r="A16" s="47">
-        <v>15929970</v>
-      </c>
-      <c r="B16" s="47" t="s">
-        <v>770</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E16" s="47">
-        <v>5</v>
-      </c>
-      <c r="F16" s="47">
-        <v>3</v>
-      </c>
-      <c r="G16" s="47">
-        <v>4</v>
-      </c>
-      <c r="H16" s="47"/>
-      <c r="I16" t="s">
-        <v>273</v>
-      </c>
-      <c r="J16" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="30">
-      <c r="A17" s="46">
-        <v>1070000000</v>
-      </c>
-      <c r="B17" s="47" t="s">
-        <v>771</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D17" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E17" s="47">
-        <v>5</v>
-      </c>
-      <c r="F17" s="47">
-        <v>5</v>
-      </c>
-      <c r="G17" s="47">
-        <v>5</v>
-      </c>
-      <c r="H17" s="47"/>
-      <c r="I17" t="s">
-        <v>437</v>
-      </c>
-      <c r="J17" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="30">
-      <c r="A18" s="47">
-        <v>25364210</v>
-      </c>
-      <c r="B18" s="47" t="s">
-        <v>772</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E18" s="47">
-        <v>3</v>
-      </c>
-      <c r="F18" s="47">
-        <v>3</v>
-      </c>
-      <c r="G18" s="47">
-        <v>3</v>
-      </c>
-      <c r="H18" s="47"/>
-      <c r="I18" t="s">
-        <v>515</v>
-      </c>
-      <c r="J18" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="30">
-      <c r="A19" s="47">
-        <v>25280773</v>
-      </c>
-      <c r="B19" s="47" t="s">
-        <v>773</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E19" s="47">
-        <v>5</v>
-      </c>
-      <c r="F19" s="47">
-        <v>5</v>
-      </c>
-      <c r="G19" s="47">
-        <v>5</v>
-      </c>
-      <c r="H19" s="47"/>
-      <c r="I19" t="s">
-        <v>515</v>
-      </c>
-      <c r="J19" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="30">
-      <c r="A20" s="46">
-        <v>1130000000</v>
-      </c>
-      <c r="B20" s="47" t="s">
-        <v>774</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D20" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E20" s="47">
-        <v>5</v>
-      </c>
-      <c r="F20" s="47">
-        <v>5</v>
-      </c>
-      <c r="G20" s="47">
-        <v>5</v>
-      </c>
-      <c r="H20" s="47"/>
-      <c r="I20" t="s">
-        <v>319</v>
-      </c>
-      <c r="J20" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="30">
-      <c r="A21" s="47">
-        <v>24580946</v>
-      </c>
-      <c r="B21" s="47" t="s">
-        <v>775</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D21" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E21" s="47">
-        <v>5</v>
-      </c>
-      <c r="F21" s="47">
-        <v>5</v>
-      </c>
-      <c r="G21" s="47">
-        <v>5</v>
-      </c>
-      <c r="H21" s="47"/>
-      <c r="I21" t="s">
-        <v>319</v>
-      </c>
-      <c r="J21" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="30">
-      <c r="A22" s="47">
-        <v>79794583</v>
-      </c>
-      <c r="B22" s="47" t="s">
-        <v>776</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D22" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E22" s="47">
-        <v>5</v>
-      </c>
-      <c r="F22" s="47">
-        <v>5</v>
-      </c>
-      <c r="G22" s="47">
-        <v>5</v>
-      </c>
-      <c r="H22" s="47"/>
-      <c r="I22" t="s">
-        <v>385</v>
-      </c>
-      <c r="J22" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="30">
-      <c r="A23" s="47">
-        <v>79496136</v>
-      </c>
-      <c r="B23" s="47" t="s">
-        <v>777</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D23" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E23" s="47">
-        <v>5</v>
-      </c>
-      <c r="F23" s="47">
-        <v>5</v>
-      </c>
-      <c r="G23" s="47">
-        <v>5</v>
-      </c>
-      <c r="H23" s="47"/>
-      <c r="I23" t="s">
-        <v>385</v>
-      </c>
-      <c r="J23" t="s">
-        <v>386</v>
+      <c r="J21" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="K21" t="s">
+        <v>740</v>
+      </c>
+      <c r="L21" t="s">
+        <v>741</v>
       </c>
     </row>
   </sheetData>
@@ -3762,14 +3821,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA89662-6597-440B-93CF-3E4C4E5F4B95}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:C374"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="23" customWidth="1"/>
     <col min="2" max="2" width="52.28515625" style="24" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" style="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
@@ -3780,7 +3839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="31">
         <v>900220590</v>
       </c>
@@ -3791,7 +3850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" hidden="1">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31">
         <v>891855847</v>
       </c>
@@ -3802,7 +3861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31">
         <v>890801026</v>
       </c>
@@ -3813,7 +3872,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" hidden="1">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="31">
         <v>41471570</v>
       </c>
@@ -3824,7 +3883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="31">
         <v>900352592</v>
       </c>
@@ -3835,7 +3894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="31">
         <v>900385628</v>
       </c>
@@ -3846,7 +3905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="31">
         <v>832010240</v>
       </c>
@@ -3857,7 +3916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="31">
         <v>899999161</v>
       </c>
@@ -3868,7 +3927,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="31">
         <v>900119357</v>
       </c>
@@ -3879,7 +3938,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="31">
         <v>830114167</v>
       </c>
@@ -3890,7 +3949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="31">
         <v>79781903</v>
       </c>
@@ -3901,7 +3960,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="31">
         <v>891190011</v>
       </c>
@@ -3912,7 +3971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="31">
         <v>891401643</v>
       </c>
@@ -3923,7 +3982,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="31">
         <v>800174851</v>
       </c>
@@ -3934,7 +3993,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="31">
         <v>800193490</v>
       </c>
@@ -3945,7 +4004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="31">
         <v>900420664</v>
       </c>
@@ -3956,7 +4015,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="31">
         <v>80041361</v>
       </c>
@@ -3967,7 +4026,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="31">
         <v>830109997</v>
       </c>
@@ -3978,7 +4037,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="31">
         <v>860053761</v>
       </c>
@@ -3989,7 +4048,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="31">
         <v>19274667</v>
       </c>
@@ -4000,7 +4059,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="31">
         <v>890701718</v>
       </c>
@@ -4011,7 +4070,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="31">
         <v>800209891</v>
       </c>
@@ -4022,7 +4081,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="31">
         <v>860066767</v>
       </c>
@@ -4033,7 +4092,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="31">
         <v>810003245</v>
       </c>
@@ -4044,7 +4103,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="31">
         <v>800085883</v>
       </c>
@@ -4055,7 +4114,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="27" spans="1:3" hidden="1">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="31">
         <v>900649963</v>
       </c>
@@ -4066,7 +4125,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:3" hidden="1">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="31">
         <v>52794734</v>
       </c>
@@ -4077,7 +4136,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="31">
         <v>800231215</v>
       </c>
@@ -4088,7 +4147,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="31">
         <v>900691301</v>
       </c>
@@ -4099,7 +4158,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:3" hidden="1">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="31">
         <v>800006509</v>
       </c>
@@ -4110,7 +4169,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:3" hidden="1">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="31">
         <v>900193162</v>
       </c>
@@ -4121,7 +4180,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:3" hidden="1">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="31">
         <v>890807591</v>
       </c>
@@ -4132,7 +4191,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:3" hidden="1">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="31">
         <v>900144408</v>
       </c>
@@ -4143,7 +4202,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:3" hidden="1">
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="31">
         <v>860010783</v>
       </c>
@@ -4154,7 +4213,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:3" hidden="1">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="31">
         <v>900691056</v>
       </c>
@@ -4165,7 +4224,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:3" hidden="1">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="31">
         <v>901060053</v>
       </c>
@@ -4176,7 +4235,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:3" hidden="1">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="31">
         <v>900215983</v>
       </c>
@@ -4187,7 +4246,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:3" hidden="1">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="31">
         <v>900129308</v>
       </c>
@@ -4198,7 +4257,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:3" hidden="1">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="31">
         <v>892000264</v>
       </c>
@@ -4209,7 +4268,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:3" hidden="1">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="31">
         <v>800218979</v>
       </c>
@@ -4220,7 +4279,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:3" hidden="1">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="31">
         <v>891855029</v>
       </c>
@@ -4231,7 +4290,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:3" hidden="1">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="31">
         <v>900142282</v>
       </c>
@@ -4242,7 +4301,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44" spans="1:3" hidden="1">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="31">
         <v>860006745</v>
       </c>
@@ -4253,7 +4312,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:3" hidden="1">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="31">
         <v>890702369</v>
       </c>
@@ -4264,7 +4323,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="31">
         <v>800017308</v>
       </c>
@@ -4275,7 +4334,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="47" spans="1:3" hidden="1">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="31">
         <v>890000992</v>
       </c>
@@ -4286,7 +4345,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:3" hidden="1">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="31">
         <v>830511298</v>
       </c>
@@ -4297,7 +4356,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="49" spans="1:3" hidden="1">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="31">
         <v>832001411</v>
       </c>
@@ -4308,7 +4367,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="31">
         <v>809010893</v>
       </c>
@@ -4319,7 +4378,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="31">
         <v>900714297</v>
       </c>
@@ -4330,7 +4389,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="52" spans="1:3" hidden="1">
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="31">
         <v>900034131</v>
       </c>
@@ -4341,7 +4400,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1">
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="31">
         <v>860015536</v>
       </c>
@@ -4352,7 +4411,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1">
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="31">
         <v>900211460</v>
       </c>
@@ -4363,7 +4422,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1">
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="31">
         <v>860090566</v>
       </c>
@@ -4374,7 +4433,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1">
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="31">
         <v>891800335</v>
       </c>
@@ -4385,7 +4444,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:3" hidden="1">
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="31">
         <v>900454994</v>
       </c>
@@ -4396,7 +4455,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1">
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="31">
         <v>820003431</v>
       </c>
@@ -4407,7 +4466,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1">
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="31">
         <v>830070284</v>
       </c>
@@ -4418,7 +4477,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:3" hidden="1">
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="31">
         <v>890703630</v>
       </c>
@@ -4429,7 +4488,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1">
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="31">
         <v>800032418</v>
       </c>
@@ -4440,7 +4499,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1">
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="31">
         <v>900211477</v>
       </c>
@@ -4451,7 +4510,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1">
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="31">
         <v>900004894</v>
       </c>
@@ -4462,7 +4521,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="31">
         <v>901061505</v>
       </c>
@@ -4473,7 +4532,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="65" spans="1:3" hidden="1">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="31">
         <v>901622460</v>
       </c>
@@ -4484,7 +4543,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="66" spans="1:3" hidden="1">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="31">
         <v>828000386</v>
       </c>
@@ -4495,7 +4554,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="67" spans="1:3" hidden="1">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="31">
         <v>891200679</v>
       </c>
@@ -4506,7 +4565,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:3" hidden="1">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="31">
         <v>79451044</v>
       </c>
@@ -4517,7 +4576,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="69" spans="1:3" hidden="1">
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="31">
         <v>860035992</v>
       </c>
@@ -4528,7 +4587,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="70" spans="1:3" hidden="1">
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="31">
         <v>900217648</v>
       </c>
@@ -4539,7 +4598,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1">
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="31">
         <v>900130936</v>
       </c>
@@ -4550,7 +4609,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="72" spans="1:3" hidden="1">
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="31">
         <v>890805923</v>
       </c>
@@ -4561,7 +4620,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="73" spans="1:3" hidden="1">
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="31">
         <v>900470918</v>
       </c>
@@ -4572,7 +4631,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="31">
         <v>900236728</v>
       </c>
@@ -4583,7 +4642,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="75" spans="1:3" hidden="1">
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="31">
         <v>844004197</v>
       </c>
@@ -4594,7 +4653,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="31">
         <v>900175697</v>
       </c>
@@ -4605,7 +4664,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="77" spans="1:3" hidden="1">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="31">
         <v>820003850</v>
       </c>
@@ -4616,7 +4675,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="31">
         <v>830073010</v>
       </c>
@@ -4627,7 +4686,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="79" spans="1:3" hidden="1">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="31">
         <v>860015888</v>
       </c>
@@ -4638,7 +4697,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="31">
         <v>900210981</v>
       </c>
@@ -4649,7 +4708,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="31">
         <v>901011962</v>
       </c>
@@ -4660,7 +4719,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="82" spans="1:3" hidden="1">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="31">
         <v>900118059</v>
       </c>
@@ -4671,7 +4730,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="83" spans="1:3" hidden="1">
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="31">
         <v>901447598</v>
       </c>
@@ -4682,7 +4741,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="84" spans="1:3" hidden="1">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="31">
         <v>901163080</v>
       </c>
@@ -4693,7 +4752,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1">
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="31">
         <v>900559103</v>
       </c>
@@ -4704,7 +4763,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="1:3" hidden="1">
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="31">
         <v>891480000</v>
       </c>
@@ -4715,7 +4774,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="87" spans="1:3" hidden="1">
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="31">
         <v>900971006</v>
       </c>
@@ -4726,7 +4785,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:3" hidden="1">
+    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="31">
         <v>900420751</v>
       </c>
@@ -4737,7 +4796,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="89" spans="1:3" hidden="1">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="31">
         <v>901102510</v>
       </c>
@@ -4748,7 +4807,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="90" spans="1:3" hidden="1">
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="31">
         <v>800044967</v>
       </c>
@@ -4759,7 +4818,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="31">
         <v>832000744</v>
       </c>
@@ -4770,7 +4829,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:3" hidden="1">
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="31">
         <v>901631369</v>
       </c>
@@ -4781,7 +4840,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1">
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="31">
         <v>830010671</v>
       </c>
@@ -4792,7 +4851,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="94" spans="1:3" hidden="1">
+    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="31">
         <v>900769055</v>
       </c>
@@ -4803,7 +4862,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1">
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="31">
         <v>820001181</v>
       </c>
@@ -4814,7 +4873,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1">
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="31">
         <v>891201578</v>
       </c>
@@ -4825,7 +4884,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="97" spans="1:3" hidden="1">
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="31">
         <v>901011387</v>
       </c>
@@ -4836,7 +4895,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="98" spans="1:3" hidden="1">
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="31">
         <v>891480036</v>
       </c>
@@ -4847,7 +4906,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="99" spans="1:3" hidden="1">
+    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="31">
         <v>900491982</v>
       </c>
@@ -4858,7 +4917,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="100" spans="1:3" hidden="1">
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="31">
         <v>832003167</v>
       </c>
@@ -4869,7 +4928,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1">
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="31">
         <v>846000253</v>
       </c>
@@ -4880,7 +4939,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="102" spans="1:3" hidden="1">
+    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="31">
         <v>800149384</v>
       </c>
@@ -4891,7 +4950,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1">
+    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="31">
         <v>900138555</v>
       </c>
@@ -4902,7 +4961,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="104" spans="1:3" hidden="1">
+    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="31">
         <v>800066001</v>
       </c>
@@ -4913,7 +4972,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1">
+    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="31">
         <v>826002694</v>
       </c>
@@ -4924,7 +4983,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="106" spans="1:3" hidden="1">
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="31">
         <v>830027158</v>
       </c>
@@ -4935,7 +4994,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1">
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="31">
         <v>900132642</v>
       </c>
@@ -4946,7 +5005,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="108" spans="1:3" hidden="1">
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="31">
         <v>901182731</v>
       </c>
@@ -4957,7 +5016,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="109" spans="1:3" hidden="1">
+    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="31">
         <v>900415353</v>
       </c>
@@ -4968,7 +5027,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="110" spans="1:3" hidden="1">
+    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="31">
         <v>901386786</v>
       </c>
@@ -4979,7 +5038,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="111" spans="1:3" hidden="1">
+    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="31">
         <v>890701353</v>
       </c>
@@ -4990,7 +5049,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="112" spans="1:3" hidden="1">
+    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="31">
         <v>890706833</v>
       </c>
@@ -5001,7 +5060,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="113" spans="1:3" hidden="1">
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="31">
         <v>809002913</v>
       </c>
@@ -5012,7 +5071,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="114" spans="1:3" hidden="1">
+    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="31">
         <v>900958115</v>
       </c>
@@ -5023,7 +5082,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="115" spans="1:3" hidden="1">
+    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="31">
         <v>900876789</v>
       </c>
@@ -5034,7 +5093,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="116" spans="1:3" hidden="1">
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="31">
         <v>800082446</v>
       </c>
@@ -5045,7 +5104,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="117" spans="1:3" hidden="1">
+    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="31">
         <v>816007055</v>
       </c>
@@ -5056,7 +5115,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="118" spans="1:3" hidden="1">
+    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="31">
         <v>900912423</v>
       </c>
@@ -5067,7 +5126,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="119" spans="1:3" hidden="1">
+    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="31">
         <v>900826841</v>
       </c>
@@ -5078,7 +5137,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="120" spans="1:3" hidden="1">
+    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="31">
         <v>901091739</v>
       </c>
@@ -5089,7 +5148,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="121" spans="1:3" hidden="1">
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="31">
         <v>900215698</v>
       </c>
@@ -5100,7 +5159,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1">
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="31">
         <v>901392384</v>
       </c>
@@ -5111,7 +5170,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="123" spans="1:3" hidden="1">
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="31">
         <v>828000073</v>
       </c>
@@ -5122,7 +5181,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="124" spans="1:3" hidden="1">
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="31">
         <v>901352353</v>
       </c>
@@ -5133,7 +5192,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="125" spans="1:3" hidden="1">
+    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="31">
         <v>900999027</v>
       </c>
@@ -5144,7 +5203,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="126" spans="1:3" hidden="1">
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="31">
         <v>800074996</v>
       </c>
@@ -5155,7 +5214,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="127" spans="1:3" hidden="1">
+    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="31">
         <v>901680794</v>
       </c>
@@ -5166,7 +5225,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="128" spans="1:3" hidden="1">
+    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="31">
         <v>900477525</v>
       </c>
@@ -5177,7 +5236,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="129" spans="1:3" hidden="1">
+    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="31">
         <v>900532173</v>
       </c>
@@ -5188,7 +5247,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="130" spans="1:3" hidden="1">
+    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="31">
         <v>900702090</v>
       </c>
@@ -5199,7 +5258,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="131" spans="1:3" hidden="1">
+    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="31">
         <v>890701033</v>
       </c>
@@ -5210,7 +5269,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="132" spans="1:3" hidden="1">
+    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="31">
         <v>901625767</v>
       </c>
@@ -5221,7 +5280,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="133" spans="1:3" hidden="1">
+    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="31">
         <v>900800269</v>
       </c>
@@ -5232,7 +5291,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="134" spans="1:3" hidden="1">
+    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="31">
         <v>901606280</v>
       </c>
@@ -5243,7 +5302,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="135" spans="1:3" hidden="1">
+    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="31">
         <v>830508610</v>
       </c>
@@ -5254,7 +5313,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="136" spans="1:3" hidden="1">
+    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="31">
         <v>900342271</v>
       </c>
@@ -5265,7 +5324,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="137" spans="1:3" hidden="1">
+    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="31">
         <v>800162035</v>
       </c>
@@ -5276,7 +5335,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="138" spans="1:3" hidden="1">
+    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="31">
         <v>800146679</v>
       </c>
@@ -5287,7 +5346,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="139" spans="1:3" hidden="1">
+    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="31">
         <v>901470470</v>
       </c>
@@ -5298,7 +5357,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="140" spans="1:3" hidden="1">
+    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="31">
         <v>800234796</v>
       </c>
@@ -5309,7 +5368,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="141" spans="1:3" hidden="1">
+    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="31">
         <v>900959048</v>
       </c>
@@ -5320,7 +5379,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="142" spans="1:3" hidden="1">
+    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="31">
         <v>890801758</v>
       </c>
@@ -5331,7 +5390,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="143" spans="1:3" hidden="1">
+    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="31">
         <v>805019730</v>
       </c>
@@ -5342,7 +5401,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="144" spans="1:3" hidden="1">
+    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="31">
         <v>820002596</v>
       </c>
@@ -5353,7 +5412,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="145" spans="1:3" hidden="1">
+    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="31">
         <v>900373445</v>
       </c>
@@ -5364,7 +5423,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="146" spans="1:3" hidden="1">
+    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="31">
         <v>900301238</v>
       </c>
@@ -5375,7 +5434,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="147" spans="1:3" hidden="1">
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="31">
         <v>900296178</v>
       </c>
@@ -5386,7 +5445,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="148" spans="1:3" hidden="1">
+    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="31">
         <v>900341409</v>
       </c>
@@ -5397,7 +5456,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="149" spans="1:3" hidden="1">
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="31">
         <v>813001952</v>
       </c>
@@ -5408,7 +5467,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="150" spans="1:3" hidden="1">
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="31">
         <v>800227072</v>
       </c>
@@ -5419,7 +5478,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="151" spans="1:3" hidden="1">
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="31">
         <v>800036400</v>
       </c>
@@ -5430,7 +5489,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="152" spans="1:3" hidden="1">
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="31">
         <v>809009066</v>
       </c>
@@ -5441,7 +5500,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="153" spans="1:3" hidden="1">
+    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="31">
         <v>900563603</v>
       </c>
@@ -5452,7 +5511,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="154" spans="1:3" hidden="1">
+    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="31">
         <v>890001006</v>
       </c>
@@ -5463,7 +5522,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="155" spans="1:3" hidden="1">
+    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="31">
         <v>901119103</v>
       </c>
@@ -5474,7 +5533,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="156" spans="1:3" hidden="1">
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="31">
         <v>900240354</v>
       </c>
@@ -5485,7 +5544,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="157" spans="1:3" hidden="1">
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="31">
         <v>900504265</v>
       </c>
@@ -5496,7 +5555,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="158" spans="1:3" hidden="1">
+    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="31">
         <v>813002940</v>
       </c>
@@ -5507,7 +5566,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="159" spans="1:3" hidden="1">
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="31">
         <v>830027578</v>
       </c>
@@ -5518,7 +5577,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="160" spans="1:3" hidden="1">
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="31">
         <v>822006595</v>
       </c>
@@ -5529,7 +5588,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="161" spans="1:3" hidden="1">
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="31">
         <v>900510844</v>
       </c>
@@ -5540,7 +5599,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="162" spans="1:3" hidden="1">
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="31">
         <v>900573146</v>
       </c>
@@ -5551,7 +5610,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="163" spans="1:3" hidden="1">
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="31">
         <v>890701459</v>
       </c>
@@ -5562,7 +5621,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="164" spans="1:3" hidden="1">
+    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="31">
         <v>900355585</v>
       </c>
@@ -5573,7 +5632,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="165" spans="1:3" hidden="1">
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="31">
         <v>860039726</v>
       </c>
@@ -5584,7 +5643,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="166" spans="1:3" hidden="1">
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="31">
         <v>800201496</v>
       </c>
@@ -5595,7 +5654,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="167" spans="1:3" hidden="1">
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="31">
         <v>891800395</v>
       </c>
@@ -5606,7 +5665,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="168" spans="1:3" hidden="1">
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="31">
         <v>900103925</v>
       </c>
@@ -5617,7 +5676,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="169" spans="1:3" hidden="1">
+    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="31">
         <v>800254850</v>
       </c>
@@ -5628,7 +5687,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="170" spans="1:3" hidden="1">
+    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="31">
         <v>830514240</v>
       </c>
@@ -5639,7 +5698,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="171" spans="1:3" hidden="1">
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="31">
         <v>900966154</v>
       </c>
@@ -5650,7 +5709,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="172" spans="1:3" hidden="1">
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="31">
         <v>892000501</v>
       </c>
@@ -5661,7 +5720,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="173" spans="1:3" hidden="1">
+    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="31">
         <v>860011298</v>
       </c>
@@ -5672,7 +5731,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="174" spans="1:3" hidden="1">
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="31">
         <v>820005389</v>
       </c>
@@ -5683,7 +5742,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="175" spans="1:3" hidden="1">
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="31">
         <v>830039229</v>
       </c>
@@ -5694,7 +5753,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="176" spans="1:3" hidden="1">
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="31">
         <v>900448997</v>
       </c>
@@ -5705,7 +5764,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="177" spans="1:3" hidden="1">
+    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="31">
         <v>900716387</v>
       </c>
@@ -5716,7 +5775,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="178" spans="1:3" hidden="1">
+    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="31">
         <v>901495569</v>
       </c>
@@ -5727,7 +5786,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="179" spans="1:3" hidden="1">
+    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="31">
         <v>900578105</v>
       </c>
@@ -5738,7 +5797,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="180" spans="1:3" hidden="1">
+    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="31">
         <v>79785257</v>
       </c>
@@ -5749,7 +5808,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="181" spans="1:3" hidden="1">
+    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="31">
         <v>80727490</v>
       </c>
@@ -5760,7 +5819,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="182" spans="1:3" hidden="1">
+    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="31">
         <v>809006003</v>
       </c>
@@ -5771,7 +5830,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="183" spans="1:3" hidden="1">
+    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="38">
         <v>832000464</v>
       </c>
@@ -5782,7 +5841,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15.75" hidden="1">
+    <row r="184" spans="1:3" ht="15.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="31">
         <v>900267104</v>
       </c>
@@ -5793,7 +5852,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="185" spans="1:3" hidden="1">
+    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="31">
         <v>830141132</v>
       </c>
@@ -5804,7 +5863,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="186" spans="1:3" hidden="1">
+    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="31">
         <v>890000600</v>
       </c>
@@ -5815,7 +5874,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="187" spans="1:3" hidden="1">
+    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="31">
         <v>899999063</v>
       </c>
@@ -5826,7 +5885,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="188" spans="1:3" hidden="1">
+    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="31">
         <v>890801517</v>
       </c>
@@ -5837,7 +5896,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="189" spans="1:3" hidden="1">
+    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="31">
         <v>900482620</v>
       </c>
@@ -5848,7 +5907,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="190" spans="1:3" hidden="1">
+    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="31">
         <v>891856161</v>
       </c>
@@ -5859,7 +5918,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="191" spans="1:3" hidden="1">
+    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="31">
         <v>892000458</v>
       </c>
@@ -5870,7 +5929,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="192" spans="1:3" hidden="1">
+    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="31">
         <v>900451858</v>
       </c>
@@ -5881,7 +5940,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="193" spans="1:3" hidden="1">
+    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="31">
         <v>800219192</v>
       </c>
@@ -5892,7 +5951,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="194" spans="1:3" hidden="1">
+    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="31">
         <v>832002436</v>
       </c>
@@ -5903,7 +5962,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="195" spans="1:3" hidden="1">
+    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="31">
         <v>832001966</v>
       </c>
@@ -5914,7 +5973,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="196" spans="1:3" hidden="1">
+    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="31">
         <v>900841132</v>
       </c>
@@ -5925,7 +5984,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="197" spans="1:3" hidden="1">
+    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="31">
         <v>900588182</v>
       </c>
@@ -5936,7 +5995,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="198" spans="1:3" hidden="1">
+    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="31">
         <v>826002144</v>
       </c>
@@ -5947,7 +6006,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="199" spans="1:3" hidden="1">
+    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="31">
         <v>846003067</v>
       </c>
@@ -5958,7 +6017,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="200" spans="1:3" hidden="1">
+    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="31">
         <v>900241765</v>
       </c>
@@ -5969,7 +6028,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="201" spans="1:3" hidden="1">
+    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="31">
         <v>900521595</v>
       </c>
@@ -5980,7 +6039,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="202" spans="1:3" hidden="1">
+    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="31">
         <v>816003270</v>
       </c>
@@ -5991,7 +6050,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="203" spans="1:3" hidden="1">
+    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="31">
         <v>890704555</v>
       </c>
@@ -6002,7 +6061,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="204" spans="1:3" hidden="1">
+    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="31">
         <v>900232301</v>
       </c>
@@ -6013,7 +6072,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="205" spans="1:3" hidden="1">
+    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="31">
         <v>830143831</v>
       </c>
@@ -6024,7 +6083,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="206" spans="1:3" hidden="1">
+    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="31">
         <v>800099652</v>
       </c>
@@ -6035,7 +6094,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="207" spans="1:3" hidden="1">
+    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="31">
         <v>891800570</v>
       </c>
@@ -6046,7 +6105,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="208" spans="1:3" hidden="1">
+    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="31">
         <v>892099421</v>
       </c>
@@ -6057,7 +6116,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="209" spans="1:3" hidden="1">
+    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="31">
         <v>900438068</v>
       </c>
@@ -6068,7 +6127,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="210" spans="1:3" hidden="1">
+    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="31">
         <v>860037950</v>
       </c>
@@ -6079,7 +6138,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="211" spans="1:3" hidden="1">
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="31">
         <v>890702408</v>
       </c>
@@ -6090,7 +6149,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="212" spans="1:3" hidden="1">
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="31">
         <v>1015392989</v>
       </c>
@@ -6101,7 +6160,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="213" spans="1:3" hidden="1">
+    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="31">
         <v>899999032</v>
       </c>
@@ -6112,7 +6171,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="214" spans="1:3" hidden="1">
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="31">
         <v>881862576</v>
       </c>
@@ -6123,7 +6182,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="215" spans="1:3" hidden="1">
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="31">
         <v>52411325</v>
       </c>
@@ -6134,7 +6193,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="216" spans="1:3" hidden="1">
+    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="31">
         <v>901544725</v>
       </c>
@@ -6145,7 +6204,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="217" spans="1:3" hidden="1">
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="31">
         <v>830009112</v>
       </c>
@@ -6156,7 +6215,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="218" spans="1:3" hidden="1">
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="31">
         <v>900614302</v>
       </c>
@@ -6167,7 +6226,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="219" spans="1:3" hidden="1">
+    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="31">
         <v>900055393</v>
       </c>
@@ -6178,7 +6237,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="220" spans="1:3" hidden="1">
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="31">
         <v>1020720272</v>
       </c>
@@ -6189,7 +6248,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="221" spans="1:3" hidden="1">
+    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="31">
         <v>844001355</v>
       </c>
@@ -6200,7 +6259,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="222" spans="1:3" hidden="1">
+    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="31">
         <v>801001440</v>
       </c>
@@ -6211,7 +6270,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="223" spans="1:3" hidden="1">
+    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="31">
         <v>800037021</v>
       </c>
@@ -6222,7 +6281,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="224" spans="1:3" hidden="1">
+    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="31">
         <v>19457462</v>
       </c>
@@ -6233,7 +6292,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="225" spans="1:3" hidden="1">
+    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="31">
         <v>890802356</v>
       </c>
@@ -6244,7 +6303,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="226" spans="1:3" hidden="1">
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="31">
         <v>890801719</v>
       </c>
@@ -6255,7 +6314,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="227" spans="1:3" hidden="1">
+    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="31">
         <v>901408039</v>
       </c>
@@ -6266,7 +6325,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="228" spans="1:3" hidden="1">
+    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="31">
         <v>860002541</v>
       </c>
@@ -6277,7 +6336,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="229" spans="1:3" hidden="1">
+    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="31">
         <v>900342064</v>
       </c>
@@ -6288,7 +6347,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="230" spans="1:3" hidden="1">
+    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="31">
         <v>890801035</v>
       </c>
@@ -6299,7 +6358,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="231" spans="1:3" hidden="1">
+    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="31">
         <v>802011972</v>
       </c>
@@ -6310,7 +6369,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="232" spans="1:3" hidden="1">
+    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="31">
         <v>900407200</v>
       </c>
@@ -6321,7 +6380,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="233" spans="1:3" hidden="1">
+    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="31">
         <v>813010145</v>
       </c>
@@ -6332,7 +6391,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="234" spans="1:3" hidden="1">
+    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="31">
         <v>860070301</v>
       </c>
@@ -6343,7 +6402,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="235" spans="1:3" hidden="1">
+    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="31">
         <v>890700666</v>
       </c>
@@ -6354,7 +6413,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="236" spans="1:3" hidden="1">
+    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="31">
         <v>900308007</v>
       </c>
@@ -6365,7 +6424,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="237" spans="1:3" hidden="1">
+    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="31">
         <v>891856372</v>
       </c>
@@ -6376,7 +6435,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="238" spans="1:3" hidden="1">
+    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="31">
         <v>800065396</v>
       </c>
@@ -6387,7 +6446,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="239" spans="1:3" hidden="1">
+    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="31">
         <v>901223046</v>
       </c>
@@ -6398,7 +6457,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="240" spans="1:3" hidden="1">
+    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="31">
         <v>809010402</v>
       </c>
@@ -6409,7 +6468,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="241" spans="1:3" hidden="1">
+    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="31">
         <v>891800231</v>
       </c>
@@ -6420,7 +6479,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="242" spans="1:3" hidden="1">
+    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="31">
         <v>800119574</v>
       </c>
@@ -6431,7 +6490,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="243" spans="1:3" hidden="1">
+    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="31">
         <v>80170827</v>
       </c>
@@ -6442,7 +6501,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="244" spans="1:3" hidden="1">
+    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="31">
         <v>10286175</v>
       </c>
@@ -6453,7 +6512,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="245" spans="1:3" hidden="1">
+    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="31">
         <v>900454188</v>
       </c>
@@ -6464,7 +6523,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="246" spans="1:3" hidden="1">
+    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="31">
         <v>900057926</v>
       </c>
@@ -6475,7 +6534,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="247" spans="1:3" hidden="1">
+    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="31">
         <v>844001911</v>
       </c>
@@ -6486,7 +6545,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="248" spans="1:3" hidden="1">
+    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="31">
         <v>900526144</v>
       </c>
@@ -6497,7 +6556,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="249" spans="1:3" hidden="1">
+    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="31">
         <v>900828394</v>
       </c>
@@ -6508,7 +6567,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="250" spans="1:3" hidden="1">
+    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="31">
         <v>844001287</v>
       </c>
@@ -6519,7 +6578,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="251" spans="1:3" hidden="1">
+    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="31">
         <v>900431131</v>
       </c>
@@ -6530,7 +6589,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="252" spans="1:3" hidden="1">
+    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="31">
         <v>800037979</v>
       </c>
@@ -6541,7 +6600,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="253" spans="1:3" hidden="1">
+    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="31">
         <v>890601210</v>
       </c>
@@ -6552,7 +6611,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="254" spans="1:3" hidden="1">
+    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="31">
         <v>801001969</v>
       </c>
@@ -6563,7 +6622,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="255" spans="1:3" hidden="1">
+    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="31">
         <v>890801944</v>
       </c>
@@ -6574,7 +6633,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="256" spans="1:3" hidden="1">
+    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="31">
         <v>19419315</v>
       </c>
@@ -6585,7 +6644,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="257" spans="1:3" hidden="1">
+    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="31">
         <v>900371613</v>
       </c>
@@ -6596,7 +6655,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="258" spans="1:3" hidden="1">
+    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="31">
         <v>860015905</v>
       </c>
@@ -6607,7 +6666,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="259" spans="1:3" hidden="1">
+    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="31">
         <v>900488920</v>
       </c>
@@ -6618,7 +6677,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="260" spans="1:3" hidden="1">
+    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="31">
         <v>810000913</v>
       </c>
@@ -6629,7 +6688,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="261" spans="1:3" hidden="1">
+    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="31">
         <v>900471504</v>
       </c>
@@ -6640,7 +6699,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="262" spans="1:3" hidden="1">
+    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="31">
         <v>844003225</v>
       </c>
@@ -6651,7 +6710,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="263" spans="1:3" hidden="1">
+    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="31">
         <v>830075393</v>
       </c>
@@ -6662,7 +6721,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="264" spans="1:3" hidden="1">
+    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="31">
         <v>900058218</v>
       </c>
@@ -6673,7 +6732,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="265" spans="1:3" hidden="1">
+    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="31">
         <v>901295822</v>
       </c>
@@ -6684,7 +6743,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="266" spans="1:3" hidden="1">
+    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="31">
         <v>900381555</v>
       </c>
@@ -6695,7 +6754,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="267" spans="1:3" hidden="1">
+    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="31">
         <v>830117846</v>
       </c>
@@ -6706,7 +6765,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="268" spans="1:3" hidden="1">
+    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="31">
         <v>901017982</v>
       </c>
@@ -6717,7 +6776,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="269" spans="1:3" hidden="1">
+    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="31">
         <v>900314301</v>
       </c>
@@ -6728,7 +6787,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="270" spans="1:3" hidden="1">
+    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="31">
         <v>901881050</v>
       </c>
@@ -6739,7 +6798,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="271" spans="1:3" hidden="1">
+    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="31">
         <v>891180134</v>
       </c>
@@ -6750,7 +6809,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="272" spans="1:3" hidden="1">
+    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="31">
         <v>900407111</v>
       </c>
@@ -6761,7 +6820,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="273" spans="1:3" hidden="1">
+    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="31">
         <v>900112820</v>
       </c>
@@ -6772,7 +6831,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="274" spans="1:3" hidden="1">
+    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="40">
         <v>901169422</v>
       </c>
@@ -6783,7 +6842,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="275" spans="1:3" hidden="1">
+    <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="31">
         <v>900108793</v>
       </c>
@@ -6794,7 +6853,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="276" spans="1:3" hidden="1">
+    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="31">
         <v>900576170</v>
       </c>
@@ -6805,7 +6864,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="277" spans="1:3" hidden="1">
+    <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="31">
         <v>891180268</v>
       </c>
@@ -6816,7 +6875,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="278" spans="1:3" hidden="1">
+    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="31">
         <v>900678145</v>
       </c>
@@ -6827,7 +6886,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="279" spans="1:3" hidden="1">
+    <row r="279" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="31">
         <v>900627725</v>
       </c>
@@ -6838,7 +6897,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="280" spans="1:3" hidden="1">
+    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="31">
         <v>891411743</v>
       </c>
@@ -6849,7 +6908,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="281" spans="1:3" hidden="1">
+    <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="31">
         <v>900077520</v>
       </c>
@@ -6860,7 +6919,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="282" spans="1:3" hidden="1">
+    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="31">
         <v>900958564</v>
       </c>
@@ -6871,7 +6930,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="283" spans="1:3" hidden="1">
+    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="31">
         <v>800200789</v>
       </c>
@@ -6882,7 +6941,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="284" spans="1:3" hidden="1">
+    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="31">
         <v>900061048</v>
       </c>
@@ -6893,7 +6952,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="285" spans="1:3" hidden="1">
+    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="31">
         <v>901127904</v>
       </c>
@@ -6904,7 +6963,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="286" spans="1:3" hidden="1">
+    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="31">
         <v>890801562</v>
       </c>
@@ -6915,7 +6974,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="287" spans="1:3" hidden="1">
+    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="31">
         <v>80055710</v>
       </c>
@@ -6926,7 +6985,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="288" spans="1:3" hidden="1">
+    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="31">
         <v>79442674</v>
       </c>
@@ -6937,7 +6996,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="289" spans="1:3" hidden="1">
+    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="31">
         <v>891856507</v>
       </c>
@@ -6948,7 +7007,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="290" spans="1:3" hidden="1">
+    <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="31">
         <v>900231829</v>
       </c>
@@ -6959,7 +7018,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="291" spans="1:3" hidden="1">
+    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="31">
         <v>900171988</v>
       </c>
@@ -6970,7 +7029,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="292" spans="1:3" hidden="1">
+    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="31">
         <v>891180098</v>
       </c>
@@ -6981,7 +7040,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="293" spans="1:3" hidden="1">
+    <row r="293" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="31">
         <v>845000038</v>
       </c>
@@ -6992,7 +7051,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="294" spans="1:3" hidden="1">
+    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="31">
         <v>900817788</v>
       </c>
@@ -7003,7 +7062,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="295" spans="1:3" hidden="1">
+    <row r="295" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="31">
         <v>899999147</v>
       </c>
@@ -7014,7 +7073,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="296" spans="1:3" hidden="1">
+    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="31">
         <v>900419180</v>
       </c>
@@ -7025,7 +7084,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="297" spans="1:3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="31">
         <v>830119200</v>
       </c>
@@ -7036,7 +7095,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="298" spans="1:3" hidden="1">
+    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="31">
         <v>890801495</v>
       </c>
@@ -7047,7 +7106,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="299" spans="1:3" hidden="1">
+    <row r="299" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="31">
         <v>900582598</v>
       </c>
@@ -7058,7 +7117,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="300" spans="1:3" hidden="1">
+    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="31">
         <v>890802036</v>
       </c>
@@ -7069,7 +7128,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="301" spans="1:3" hidden="1">
+    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="31">
         <v>900462440</v>
       </c>
@@ -7080,7 +7139,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="302" spans="1:3" hidden="1">
+    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="31">
         <v>846000474</v>
       </c>
@@ -7091,7 +7150,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="303" spans="1:3" hidden="1">
+    <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="31">
         <v>800000118</v>
       </c>
@@ -7102,7 +7161,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="304" spans="1:3" hidden="1">
+    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="31">
         <v>900211468</v>
       </c>
@@ -7113,7 +7172,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="305" spans="1:3" hidden="1">
+    <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="31">
         <v>891855438</v>
       </c>
@@ -7124,7 +7183,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="306" spans="1:3" hidden="1">
+    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="31">
         <v>19364579</v>
       </c>
@@ -7135,7 +7194,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="307" spans="1:3" hidden="1">
+    <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="31">
         <v>900004059</v>
       </c>
@@ -7146,7 +7205,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="308" spans="1:3" hidden="1">
+    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="31">
         <v>846003357</v>
       </c>
@@ -7157,7 +7216,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="309" spans="1:3" hidden="1">
+    <row r="309" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="31">
         <v>901457374</v>
       </c>
@@ -7168,7 +7227,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="310" spans="1:3" hidden="1">
+    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="31">
         <v>830005028</v>
       </c>
@@ -7179,7 +7238,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="311" spans="1:3" hidden="1">
+    <row r="311" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="31">
         <v>900606412</v>
       </c>
@@ -7190,7 +7249,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="312" spans="1:3" hidden="1">
+    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="31">
         <v>830113849</v>
       </c>
@@ -7201,7 +7260,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="313" spans="1:3" hidden="1">
+    <row r="313" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="31">
         <v>900232628</v>
       </c>
@@ -7212,7 +7271,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="314" spans="1:3" hidden="1">
+    <row r="314" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="31">
         <v>890706823</v>
       </c>
@@ -7223,7 +7282,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="315" spans="1:3" hidden="1">
+    <row r="315" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="31">
         <v>901105417</v>
       </c>
@@ -7234,7 +7293,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="316" spans="1:3" hidden="1">
+    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="31">
         <v>800037202</v>
       </c>
@@ -7245,7 +7304,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="317" spans="1:3" hidden="1">
+    <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="38">
         <v>80412859</v>
       </c>
@@ -7256,7 +7315,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="318" spans="1:3" hidden="1">
+    <row r="318" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="31">
         <v>800180553</v>
       </c>
@@ -7267,7 +7326,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="319" spans="1:3" hidden="1">
+    <row r="319" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="31">
         <v>891411381</v>
       </c>
@@ -7278,7 +7337,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="320" spans="1:3" hidden="1">
+    <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="31">
         <v>814003448</v>
       </c>
@@ -7289,7 +7348,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="321" spans="1:3" hidden="1">
+    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="31">
         <v>891180026</v>
       </c>
@@ -7300,7 +7359,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="322" spans="1:3" hidden="1">
+    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="31">
         <v>900233110</v>
       </c>
@@ -7311,7 +7370,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="323" spans="1:3" hidden="1">
+    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="31">
         <v>860013570</v>
       </c>
@@ -7322,7 +7381,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="324" spans="1:3" hidden="1">
+    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="31">
         <v>901652147</v>
       </c>
@@ -7333,7 +7392,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="325" spans="1:3" hidden="1">
+    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="31">
         <v>901439163</v>
       </c>
@@ -7344,7 +7403,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="326" spans="1:3" hidden="1">
+    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="31">
         <v>822000946</v>
       </c>
@@ -7355,7 +7414,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="327" spans="1:3" hidden="1">
+    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="31">
         <v>810001466</v>
       </c>
@@ -7366,7 +7425,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="328" spans="1:3" hidden="1">
+    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="31">
         <v>900547903</v>
       </c>
@@ -7377,7 +7436,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="329" spans="1:3" hidden="1">
+    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="31">
         <v>800228215</v>
       </c>
@@ -7388,7 +7447,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="330" spans="1:3" hidden="1">
+    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="31">
         <v>890802978</v>
       </c>
@@ -7399,7 +7458,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="331" spans="1:3" hidden="1">
+    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="31">
         <v>800135582</v>
       </c>
@@ -7410,7 +7469,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="332" spans="1:3" hidden="1">
+    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="31">
         <v>900364721</v>
       </c>
@@ -7421,7 +7480,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="333" spans="1:3" hidden="1">
+    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="31">
         <v>899999123</v>
       </c>
@@ -7432,7 +7491,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="334" spans="1:3" hidden="1">
+    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="31">
         <v>890801099</v>
       </c>
@@ -7443,7 +7502,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="335" spans="1:3" hidden="1">
+    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="31">
         <v>830018305</v>
       </c>
@@ -7454,7 +7513,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="336" spans="1:3" hidden="1">
+    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="31">
         <v>809001482</v>
       </c>
@@ -7465,7 +7524,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="337" spans="1:3" hidden="1">
+    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="31">
         <v>900685235</v>
       </c>
@@ -7476,7 +7535,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="338" spans="1:3" hidden="1">
+    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="31">
         <v>800191101</v>
       </c>
@@ -7487,7 +7546,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="339" spans="1:3" hidden="1">
+    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="31">
         <v>891409981</v>
       </c>
@@ -7498,7 +7557,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="340" spans="1:3" hidden="1">
+    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="31">
         <v>900073806</v>
       </c>
@@ -7509,7 +7568,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="341" spans="1:3" hidden="1">
+    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="31">
         <v>900493064</v>
       </c>
@@ -7520,7 +7579,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="342" spans="1:3" hidden="1">
+    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="31">
         <v>800231235</v>
       </c>
@@ -7531,7 +7590,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="343" spans="1:3" hidden="1">
+    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="31">
         <v>860007373</v>
       </c>
@@ -7542,7 +7601,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="344" spans="1:3" hidden="1">
+    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="31">
         <v>900848340</v>
       </c>
@@ -7553,7 +7612,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="345" spans="1:3" hidden="1">
+    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="31">
         <v>900115642</v>
       </c>
@@ -7564,7 +7623,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="346" spans="1:3" hidden="1">
+    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="31">
         <v>79533241</v>
       </c>
@@ -7575,7 +7634,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="347" spans="1:3" hidden="1">
+    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="31">
         <v>830502282</v>
       </c>
@@ -7586,7 +7645,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="348" spans="1:3" hidden="1">
+    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="31">
         <v>900081643</v>
       </c>
@@ -7597,7 +7656,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="349" spans="1:3" hidden="1">
+    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="31">
         <v>891855039</v>
       </c>
@@ -7608,7 +7667,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="350" spans="1:3" hidden="1">
+    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="31">
         <v>805017681</v>
       </c>
@@ -7619,7 +7678,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="351" spans="1:3" hidden="1">
+    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="31">
         <v>820002248</v>
       </c>
@@ -7630,7 +7689,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="352" spans="1:3" hidden="1">
+    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="31">
         <v>860024026</v>
       </c>
@@ -7641,7 +7700,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="353" spans="1:3" hidden="1">
+    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="31">
         <v>71394225</v>
       </c>
@@ -7652,7 +7711,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="354" spans="1:3" hidden="1">
+    <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="31">
         <v>832008321</v>
       </c>
@@ -7663,7 +7722,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="355" spans="1:3" hidden="1">
+    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="31">
         <v>901632467</v>
       </c>
@@ -7674,7 +7733,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="356" spans="1:3" hidden="1">
+    <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="38">
         <v>891180117</v>
       </c>
@@ -7685,7 +7744,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="15.75" hidden="1">
+    <row r="357" spans="1:3" ht="15.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="31">
         <v>900435790</v>
       </c>
@@ -7696,7 +7755,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="358" spans="1:3" hidden="1">
+    <row r="358" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="31">
         <v>900759329</v>
       </c>
@@ -7707,7 +7766,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="359" spans="1:3" hidden="1">
+    <row r="359" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="31">
         <v>891800644</v>
       </c>
@@ -7718,7 +7777,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="360" spans="1:3" hidden="1">
+    <row r="360" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="31">
         <v>800254132</v>
       </c>
@@ -7729,7 +7788,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="361" spans="1:3" hidden="1">
+    <row r="361" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="31">
         <v>899999158</v>
       </c>
@@ -7740,7 +7799,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="362" spans="1:3" hidden="1">
+    <row r="362" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="31">
         <v>79624744</v>
       </c>
@@ -7751,7 +7810,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="363" spans="1:3" hidden="1">
+    <row r="363" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="31">
         <v>891409390</v>
       </c>
@@ -7762,7 +7821,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="364" spans="1:3" hidden="1">
+    <row r="364" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="31">
         <v>890680014</v>
       </c>
@@ -7773,7 +7832,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="365" spans="1:3" hidden="1">
+    <row r="365" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="31">
         <v>809006690</v>
       </c>
@@ -7784,7 +7843,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="366" spans="1:3" hidden="1">
+    <row r="366" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="31">
         <v>900213617</v>
       </c>
@@ -7795,7 +7854,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="367" spans="1:3" hidden="1">
+    <row r="367" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="31">
         <v>900423816</v>
       </c>
@@ -7806,7 +7865,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="368" spans="1:3" hidden="1">
+    <row r="368" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="31">
         <v>860015929</v>
       </c>
@@ -7817,7 +7876,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="369" spans="1:3" hidden="1">
+    <row r="369" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="31">
         <v>890806490</v>
       </c>
@@ -7828,7 +7887,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="370" spans="1:3" hidden="1">
+    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="31">
         <v>860006626</v>
       </c>
@@ -7839,7 +7898,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="371" spans="1:3" hidden="1">
+    <row r="371" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="31">
         <v>813005295</v>
       </c>
@@ -7850,7 +7909,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="372" spans="1:3" hidden="1">
+    <row r="372" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="44">
         <v>846001425</v>
       </c>
@@ -7861,7 +7920,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="373" spans="1:3" hidden="1">
+    <row r="373" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="31">
         <v>800139366</v>
       </c>
@@ -7872,7 +7931,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="374" spans="1:3" hidden="1">
+    <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="31">
         <v>816005003</v>
       </c>
@@ -7910,14 +7969,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C371"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="22" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" style="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5703125" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7928,7 +7987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>900220590</v>
       </c>
@@ -7939,7 +7998,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>891855847</v>
       </c>
@@ -7950,7 +8009,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1">
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>890801026</v>
       </c>
@@ -7961,7 +8020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1">
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>41471570</v>
       </c>
@@ -7972,7 +8031,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>900352592</v>
       </c>
@@ -7983,7 +8042,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18.75" customHeight="1">
+    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>900385628</v>
       </c>
@@ -7994,7 +8053,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>832010240</v>
       </c>
@@ -8005,7 +8064,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>899999161</v>
       </c>
@@ -8016,7 +8075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+    <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>900119357</v>
       </c>
@@ -8027,7 +8086,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18.75" customHeight="1">
+    <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>830114167</v>
       </c>
@@ -8038,7 +8097,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18.75" customHeight="1">
+    <row r="12" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>79781903</v>
       </c>
@@ -8049,7 +8108,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18.75" customHeight="1">
+    <row r="13" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>891190011</v>
       </c>
@@ -8060,7 +8119,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+    <row r="14" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>891401643</v>
       </c>
@@ -8071,7 +8130,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+    <row r="15" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>800174851</v>
       </c>
@@ -8082,7 +8141,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+    <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>800193490</v>
       </c>
@@ -8093,7 +8152,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18.75" customHeight="1">
+    <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>900420664</v>
       </c>
@@ -8104,7 +8163,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18.75" customHeight="1">
+    <row r="18" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>80041361</v>
       </c>
@@ -8115,7 +8174,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+    <row r="19" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>801001406</v>
       </c>
@@ -8126,7 +8185,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18.75" customHeight="1">
+    <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>860053761</v>
       </c>
@@ -8137,7 +8196,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18.75" customHeight="1">
+    <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>19274667</v>
       </c>
@@ -8148,7 +8207,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18.75" customHeight="1">
+    <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>890701718</v>
       </c>
@@ -8159,7 +8218,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18.75" customHeight="1">
+    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>800209891</v>
       </c>
@@ -8170,7 +8229,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>810003245</v>
       </c>
@@ -8181,7 +8240,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18.75" customHeight="1">
+    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>900649963</v>
       </c>
@@ -8192,7 +8251,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18.75" customHeight="1">
+    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>52794734</v>
       </c>
@@ -8203,7 +8262,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18.75" customHeight="1">
+    <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>800231215</v>
       </c>
@@ -8214,7 +8273,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18.75" customHeight="1">
+    <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>900691301</v>
       </c>
@@ -8225,7 +8284,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18.75" customHeight="1">
+    <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>800006509</v>
       </c>
@@ -8236,7 +8295,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18.75" customHeight="1">
+    <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>900193162</v>
       </c>
@@ -8247,7 +8306,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18.75" customHeight="1">
+    <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>890807591</v>
       </c>
@@ -8258,7 +8317,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18.75" customHeight="1">
+    <row r="32" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>900144408</v>
       </c>
@@ -8269,7 +8328,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18.75" customHeight="1">
+    <row r="33" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>860010783</v>
       </c>
@@ -8280,7 +8339,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18.75" customHeight="1">
+    <row r="34" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>900691056</v>
       </c>
@@ -8291,7 +8350,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18.75" customHeight="1">
+    <row r="35" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>901060053</v>
       </c>
@@ -8302,7 +8361,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18.75" customHeight="1">
+    <row r="36" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>900215983</v>
       </c>
@@ -8313,7 +8372,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18.75" customHeight="1">
+    <row r="37" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>900129308</v>
       </c>
@@ -8324,7 +8383,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18.75" customHeight="1">
+    <row r="38" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>892000264</v>
       </c>
@@ -8335,7 +8394,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18.75" customHeight="1">
+    <row r="39" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>800218979</v>
       </c>
@@ -8346,7 +8405,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18.75" customHeight="1">
+    <row r="40" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>891855029</v>
       </c>
@@ -8357,7 +8416,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18.75" customHeight="1">
+    <row r="41" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>900142282</v>
       </c>
@@ -8368,7 +8427,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18.75" customHeight="1">
+    <row r="42" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>860006745</v>
       </c>
@@ -8379,7 +8438,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18.75" customHeight="1">
+    <row r="43" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>890702369</v>
       </c>
@@ -8390,7 +8449,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18.75" customHeight="1">
+    <row r="44" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>800017308</v>
       </c>
@@ -8401,7 +8460,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18.75" customHeight="1">
+    <row r="45" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <v>890000992</v>
       </c>
@@ -8412,7 +8471,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18.75" customHeight="1">
+    <row r="46" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
         <v>830511298</v>
       </c>
@@ -8423,7 +8482,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18.75" customHeight="1">
+    <row r="47" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>832001411</v>
       </c>
@@ -8434,7 +8493,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18.75" customHeight="1">
+    <row r="48" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>809010893</v>
       </c>
@@ -8445,7 +8504,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18.75" customHeight="1">
+    <row r="49" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>900714297</v>
       </c>
@@ -8456,7 +8515,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18.75" customHeight="1">
+    <row r="50" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12">
         <v>900034131</v>
       </c>
@@ -8467,7 +8526,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18.75" customHeight="1">
+    <row r="51" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>860015536</v>
       </c>
@@ -8478,7 +8537,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18.75" customHeight="1">
+    <row r="52" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>900211460</v>
       </c>
@@ -8489,7 +8548,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18.75" customHeight="1">
+    <row r="53" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
         <v>860090566</v>
       </c>
@@ -8500,7 +8559,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18.75" customHeight="1">
+    <row r="54" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <v>891800335</v>
       </c>
@@ -8511,7 +8570,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18.75" customHeight="1">
+    <row r="55" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <v>900454994</v>
       </c>
@@ -8522,7 +8581,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18.75" customHeight="1">
+    <row r="56" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>820003431</v>
       </c>
@@ -8533,7 +8592,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18.75" customHeight="1">
+    <row r="57" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
         <v>830070284</v>
       </c>
@@ -8544,7 +8603,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18.75" customHeight="1">
+    <row r="58" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
         <v>890703630</v>
       </c>
@@ -8555,7 +8614,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18.75" customHeight="1">
+    <row r="59" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
         <v>800032418</v>
       </c>
@@ -8566,7 +8625,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18.75" customHeight="1">
+    <row r="60" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <v>900211477</v>
       </c>
@@ -8577,7 +8636,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18.75" customHeight="1">
+    <row r="61" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
         <v>900004894</v>
       </c>
@@ -8588,7 +8647,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18.75" customHeight="1">
+    <row r="62" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
         <v>901061505</v>
       </c>
@@ -8599,7 +8658,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18.75" customHeight="1">
+    <row r="63" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
         <v>901622460</v>
       </c>
@@ -8610,7 +8669,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18.75" customHeight="1">
+    <row r="64" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <v>828000386</v>
       </c>
@@ -8621,7 +8680,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18.75" customHeight="1">
+    <row r="65" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
         <v>891200679</v>
       </c>
@@ -8632,7 +8691,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18.75" customHeight="1">
+    <row r="66" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <v>79451044</v>
       </c>
@@ -8643,7 +8702,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18.75" customHeight="1">
+    <row r="67" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
         <v>860035992</v>
       </c>
@@ -8654,7 +8713,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18.75" customHeight="1">
+    <row r="68" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <v>900217648</v>
       </c>
@@ -8665,7 +8724,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18.75" customHeight="1">
+    <row r="69" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
         <v>900130936</v>
       </c>
@@ -8676,7 +8735,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18.75" customHeight="1">
+    <row r="70" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
         <v>890805923</v>
       </c>
@@ -8687,7 +8746,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18.75" customHeight="1">
+    <row r="71" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <v>900470918</v>
       </c>
@@ -8698,7 +8757,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18.75" customHeight="1">
+    <row r="72" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
         <v>900236728</v>
       </c>
@@ -8709,7 +8768,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18.75" customHeight="1">
+    <row r="73" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
         <v>844004197</v>
       </c>
@@ -8720,7 +8779,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18.75" customHeight="1">
+    <row r="74" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>900175697</v>
       </c>
@@ -8731,7 +8790,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18.75" customHeight="1">
+    <row r="75" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
         <v>820003850</v>
       </c>
@@ -8742,7 +8801,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18.75" customHeight="1">
+    <row r="76" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
         <v>830073010</v>
       </c>
@@ -8753,7 +8812,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18.75" customHeight="1">
+    <row r="77" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
         <v>860015888</v>
       </c>
@@ -8764,7 +8823,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18.75" customHeight="1">
+    <row r="78" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7">
         <v>900210981</v>
       </c>
@@ -8775,7 +8834,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18.75" customHeight="1">
+    <row r="79" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7">
         <v>901011962</v>
       </c>
@@ -8786,7 +8845,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18.75" customHeight="1">
+    <row r="80" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
         <v>900118059</v>
       </c>
@@ -8797,7 +8856,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18.75" customHeight="1">
+    <row r="81" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
         <v>901447598</v>
       </c>
@@ -8808,7 +8867,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18.75" customHeight="1">
+    <row r="82" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
         <v>901163080</v>
       </c>
@@ -8819,7 +8878,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18.75" customHeight="1">
+    <row r="83" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7">
         <v>900559103</v>
       </c>
@@ -8830,7 +8889,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="18.75" customHeight="1">
+    <row r="84" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
         <v>891480000</v>
       </c>
@@ -8841,7 +8900,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18.75" customHeight="1">
+    <row r="85" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7">
         <v>900971006</v>
       </c>
@@ -8852,7 +8911,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18.75" customHeight="1">
+    <row r="86" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7">
         <v>900420751</v>
       </c>
@@ -8863,7 +8922,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="18.75" customHeight="1">
+    <row r="87" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7">
         <v>901102510</v>
       </c>
@@ -8874,7 +8933,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="18.75" customHeight="1">
+    <row r="88" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
         <v>800044967</v>
       </c>
@@ -8885,7 +8944,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="18.75" customHeight="1">
+    <row r="89" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7">
         <v>832000744</v>
       </c>
@@ -8896,7 +8955,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="18.75" customHeight="1">
+    <row r="90" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
         <v>901631369</v>
       </c>
@@ -8907,7 +8966,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="18.75" customHeight="1">
+    <row r="91" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="7">
         <v>830010671</v>
       </c>
@@ -8918,7 +8977,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18.75" customHeight="1">
+    <row r="92" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7">
         <v>900769055</v>
       </c>
@@ -8929,7 +8988,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18.75" customHeight="1">
+    <row r="93" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="7">
         <v>820001181</v>
       </c>
@@ -8940,7 +8999,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18.75" customHeight="1">
+    <row r="94" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7">
         <v>891201578</v>
       </c>
@@ -8951,7 +9010,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18.75" customHeight="1">
+    <row r="95" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="7">
         <v>901011387</v>
       </c>
@@ -8962,7 +9021,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="18.75" customHeight="1">
+    <row r="96" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7">
         <v>891480036</v>
       </c>
@@ -8973,7 +9032,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18.75" customHeight="1">
+    <row r="97" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7">
         <v>900491982</v>
       </c>
@@ -8984,7 +9043,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18.75" customHeight="1">
+    <row r="98" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
         <v>832003167</v>
       </c>
@@ -8995,7 +9054,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="18.75" customHeight="1">
+    <row r="99" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="7">
         <v>846000253</v>
       </c>
@@ -9006,7 +9065,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="18.75" customHeight="1">
+    <row r="100" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7">
         <v>900138555</v>
       </c>
@@ -9017,7 +9076,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="18.75" customHeight="1">
+    <row r="101" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="7">
         <v>826002694</v>
       </c>
@@ -9028,7 +9087,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="18.75" customHeight="1">
+    <row r="102" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="7">
         <v>830027158</v>
       </c>
@@ -9039,7 +9098,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="18.75" customHeight="1">
+    <row r="103" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="7">
         <v>900132642</v>
       </c>
@@ -9050,7 +9109,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="18.75" customHeight="1">
+    <row r="104" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="7">
         <v>901182731</v>
       </c>
@@ -9061,7 +9120,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="18.75" customHeight="1">
+    <row r="105" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="7">
         <v>900415353</v>
       </c>
@@ -9072,7 +9131,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="18.75" customHeight="1">
+    <row r="106" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
         <v>901386786</v>
       </c>
@@ -9083,7 +9142,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="18.75" customHeight="1">
+    <row r="107" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="7">
         <v>890701353</v>
       </c>
@@ -9094,7 +9153,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="18.75" customHeight="1">
+    <row r="108" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="7">
         <v>890706833</v>
       </c>
@@ -9105,7 +9164,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="18.75" customHeight="1">
+    <row r="109" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="7">
         <v>809002913</v>
       </c>
@@ -9116,7 +9175,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="18.75" customHeight="1">
+    <row r="110" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="7">
         <v>900958115</v>
       </c>
@@ -9127,7 +9186,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="18.75" customHeight="1">
+    <row r="111" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="7">
         <v>900876789</v>
       </c>
@@ -9138,7 +9197,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="18.75" customHeight="1">
+    <row r="112" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="7">
         <v>800082446</v>
       </c>
@@ -9149,7 +9208,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="18.75" customHeight="1">
+    <row r="113" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="7">
         <v>816007055</v>
       </c>
@@ -9160,7 +9219,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="18.75" customHeight="1">
+    <row r="114" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7">
         <v>900912423</v>
       </c>
@@ -9171,7 +9230,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="18.75" customHeight="1">
+    <row r="115" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="7">
         <v>900826841</v>
       </c>
@@ -9182,7 +9241,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="18.75" customHeight="1">
+    <row r="116" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
         <v>901091739</v>
       </c>
@@ -9193,7 +9252,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="18.75" customHeight="1">
+    <row r="117" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="7">
         <v>900215698</v>
       </c>
@@ -9204,7 +9263,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="18.75" customHeight="1">
+    <row r="118" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="7">
         <v>901392384</v>
       </c>
@@ -9215,7 +9274,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="18.75" customHeight="1">
+    <row r="119" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="7">
         <v>828000073</v>
       </c>
@@ -9226,7 +9285,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="18.75" customHeight="1">
+    <row r="120" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="7">
         <v>901352353</v>
       </c>
@@ -9237,7 +9296,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="18.75" customHeight="1">
+    <row r="121" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="7">
         <v>900999027</v>
       </c>
@@ -9248,7 +9307,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="18.75" customHeight="1">
+    <row r="122" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="7">
         <v>800074996</v>
       </c>
@@ -9259,7 +9318,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="18.75" customHeight="1">
+    <row r="123" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="7">
         <v>901680794</v>
       </c>
@@ -9270,7 +9329,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="18.75" customHeight="1">
+    <row r="124" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="7">
         <v>900477525</v>
       </c>
@@ -9281,7 +9340,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="18.75" customHeight="1">
+    <row r="125" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="7">
         <v>900532173</v>
       </c>
@@ -9292,7 +9351,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="18.75" customHeight="1">
+    <row r="126" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="7">
         <v>900702090</v>
       </c>
@@ -9303,7 +9362,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="18.75" customHeight="1">
+    <row r="127" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="7">
         <v>890701033</v>
       </c>
@@ -9314,7 +9373,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="18.75" customHeight="1">
+    <row r="128" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="7">
         <v>900800269</v>
       </c>
@@ -9325,7 +9384,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="18.75" customHeight="1">
+    <row r="129" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="7">
         <v>901606280</v>
       </c>
@@ -9336,7 +9395,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="18.75" customHeight="1">
+    <row r="130" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="7">
         <v>900342271</v>
       </c>
@@ -9347,7 +9406,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="18.75" customHeight="1">
+    <row r="131" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="7">
         <v>800162035</v>
       </c>
@@ -9358,7 +9417,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="18.75" customHeight="1">
+    <row r="132" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="7">
         <v>800146679</v>
       </c>
@@ -9369,7 +9428,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="18.75" customHeight="1">
+    <row r="133" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="7">
         <v>901470470</v>
       </c>
@@ -9380,7 +9439,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="18.75" customHeight="1">
+    <row r="134" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="15">
         <v>890701010</v>
       </c>
@@ -9391,7 +9450,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="18.75" customHeight="1">
+    <row r="135" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="7">
         <v>800234796</v>
       </c>
@@ -9402,7 +9461,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="18.75" customHeight="1">
+    <row r="136" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="7">
         <v>900959048</v>
       </c>
@@ -9413,7 +9472,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="18.75" customHeight="1">
+    <row r="137" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="7">
         <v>890801758</v>
       </c>
@@ -9424,7 +9483,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="18.75" customHeight="1">
+    <row r="138" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="7">
         <v>805019730</v>
       </c>
@@ -9435,7 +9494,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="18.75" customHeight="1">
+    <row r="139" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="7">
         <v>820002596</v>
       </c>
@@ -9446,7 +9505,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="18.75" customHeight="1">
+    <row r="140" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="7">
         <v>900373445</v>
       </c>
@@ -9457,7 +9516,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="18.75" customHeight="1">
+    <row r="141" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="7">
         <v>900301238</v>
       </c>
@@ -9468,7 +9527,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="18.75" customHeight="1">
+    <row r="142" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="7">
         <v>900296178</v>
       </c>
@@ -9479,7 +9538,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="18.75" customHeight="1">
+    <row r="143" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="7">
         <v>900341409</v>
       </c>
@@ -9490,7 +9549,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="18.75" customHeight="1">
+    <row r="144" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="7">
         <v>813001952</v>
       </c>
@@ -9501,7 +9560,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="18.75" customHeight="1">
+    <row r="145" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="7">
         <v>800227072</v>
       </c>
@@ -9512,7 +9571,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="18.75" customHeight="1">
+    <row r="146" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="7">
         <v>800036400</v>
       </c>
@@ -9523,7 +9582,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="18.75" customHeight="1">
+    <row r="147" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="7">
         <v>809009066</v>
       </c>
@@ -9534,7 +9593,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="18.75" customHeight="1">
+    <row r="148" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="7">
         <v>900563603</v>
       </c>
@@ -9545,7 +9604,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="18.75" customHeight="1">
+    <row r="149" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="7">
         <v>890001006</v>
       </c>
@@ -9556,7 +9615,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="18.75" customHeight="1">
+    <row r="150" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="7">
         <v>901119103</v>
       </c>
@@ -9567,7 +9626,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="18.75" customHeight="1">
+    <row r="151" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="7">
         <v>900240354</v>
       </c>
@@ -9578,7 +9637,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="18.75" customHeight="1">
+    <row r="152" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="7">
         <v>900504265</v>
       </c>
@@ -9589,7 +9648,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="18.75" customHeight="1">
+    <row r="153" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="7">
         <v>813002940</v>
       </c>
@@ -9600,7 +9659,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="18.75" customHeight="1">
+    <row r="154" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="7">
         <v>830027578</v>
       </c>
@@ -9611,7 +9670,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="18.75" customHeight="1">
+    <row r="155" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="7">
         <v>822006595</v>
       </c>
@@ -9622,7 +9681,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="18.75" customHeight="1">
+    <row r="156" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="7">
         <v>900510844</v>
       </c>
@@ -9633,7 +9692,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="18.75" customHeight="1">
+    <row r="157" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="7">
         <v>900573146</v>
       </c>
@@ -9644,7 +9703,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="18.75" customHeight="1">
+    <row r="158" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="7">
         <v>890701459</v>
       </c>
@@ -9655,7 +9714,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="18.75" customHeight="1">
+    <row r="159" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="7">
         <v>900355585</v>
       </c>
@@ -9666,7 +9725,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="18.75" customHeight="1">
+    <row r="160" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="7">
         <v>860039726</v>
       </c>
@@ -9677,7 +9736,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="18.75" customHeight="1">
+    <row r="161" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="7">
         <v>800201496</v>
       </c>
@@ -9688,7 +9747,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="18.75" customHeight="1">
+    <row r="162" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="7">
         <v>891800395</v>
       </c>
@@ -9699,7 +9758,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="18.75" customHeight="1">
+    <row r="163" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="7">
         <v>900103925</v>
       </c>
@@ -9710,7 +9769,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="18.75" customHeight="1">
+    <row r="164" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="7">
         <v>800254850</v>
       </c>
@@ -9721,7 +9780,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="18.75" customHeight="1">
+    <row r="165" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="7">
         <v>830514240</v>
       </c>
@@ -9732,7 +9791,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="18.75" customHeight="1">
+    <row r="166" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="7">
         <v>900966154</v>
       </c>
@@ -9743,7 +9802,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="18.75" customHeight="1">
+    <row r="167" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="7">
         <v>892000501</v>
       </c>
@@ -9754,7 +9813,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="18.75" customHeight="1">
+    <row r="168" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="7">
         <v>860011298</v>
       </c>
@@ -9765,7 +9824,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="18.75" customHeight="1">
+    <row r="169" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="7">
         <v>820005389</v>
       </c>
@@ -9776,7 +9835,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="18.75" customHeight="1">
+    <row r="170" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="7">
         <v>830039229</v>
       </c>
@@ -9787,7 +9846,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="18.75" customHeight="1">
+    <row r="171" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="7">
         <v>900448997</v>
       </c>
@@ -9798,7 +9857,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="18.75" customHeight="1">
+    <row r="172" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="7">
         <v>900716387</v>
       </c>
@@ -9809,7 +9868,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="18.75" customHeight="1">
+    <row r="173" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="7">
         <v>901495569</v>
       </c>
@@ -9820,7 +9879,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="18.75" customHeight="1">
+    <row r="174" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="7">
         <v>900578105</v>
       </c>
@@ -9831,7 +9890,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="18.75" customHeight="1">
+    <row r="175" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="7">
         <v>79785257</v>
       </c>
@@ -9842,7 +9901,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="18.75" customHeight="1">
+    <row r="176" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="7">
         <v>80727490</v>
       </c>
@@ -9853,7 +9912,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="18.75" customHeight="1">
+    <row r="177" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="7">
         <v>809006003</v>
       </c>
@@ -9864,7 +9923,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="18.75" customHeight="1">
+    <row r="178" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="7">
         <v>832000464</v>
       </c>
@@ -9875,7 +9934,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="18.75" customHeight="1">
+    <row r="179" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="7">
         <v>900267104</v>
       </c>
@@ -9886,7 +9945,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="18.75" customHeight="1">
+    <row r="180" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="7">
         <v>830141132</v>
       </c>
@@ -9897,7 +9956,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="18.75" customHeight="1">
+    <row r="181" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="7">
         <v>890000600</v>
       </c>
@@ -9908,7 +9967,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="18.75" customHeight="1">
+    <row r="182" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="7">
         <v>899999063</v>
       </c>
@@ -9919,7 +9978,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="18.75" customHeight="1">
+    <row r="183" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="7">
         <v>890801517</v>
       </c>
@@ -9930,7 +9989,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="18.75" customHeight="1">
+    <row r="184" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="7">
         <v>900482620</v>
       </c>
@@ -9941,7 +10000,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="18.75" customHeight="1">
+    <row r="185" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="7">
         <v>891856161</v>
       </c>
@@ -9952,7 +10011,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="18.75" customHeight="1">
+    <row r="186" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="7">
         <v>892000458</v>
       </c>
@@ -9963,7 +10022,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="18.75" customHeight="1">
+    <row r="187" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="7">
         <v>900451858</v>
       </c>
@@ -9974,7 +10033,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="18.75" customHeight="1">
+    <row r="188" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="7">
         <v>800219192</v>
       </c>
@@ -9985,7 +10044,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="18.75" customHeight="1">
+    <row r="189" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="7">
         <v>832002436</v>
       </c>
@@ -9996,7 +10055,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="18.75" customHeight="1">
+    <row r="190" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="7">
         <v>832001966</v>
       </c>
@@ -10007,7 +10066,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="18.75" customHeight="1">
+    <row r="191" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="7">
         <v>900841132</v>
       </c>
@@ -10018,7 +10077,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="18.75" customHeight="1">
+    <row r="192" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="7">
         <v>900588182</v>
       </c>
@@ -10029,7 +10088,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="18.75" customHeight="1">
+    <row r="193" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="7">
         <v>826002144</v>
       </c>
@@ -10040,7 +10099,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="18.75" customHeight="1">
+    <row r="194" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="7">
         <v>846003067</v>
       </c>
@@ -10051,7 +10110,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="18.75" customHeight="1">
+    <row r="195" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="7">
         <v>900241765</v>
       </c>
@@ -10062,7 +10121,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="18.75" customHeight="1">
+    <row r="196" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="7">
         <v>900521595</v>
       </c>
@@ -10073,7 +10132,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="18.75" customHeight="1">
+    <row r="197" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="7">
         <v>816003270</v>
       </c>
@@ -10084,7 +10143,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="18.75" customHeight="1">
+    <row r="198" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="7">
         <v>890704555</v>
       </c>
@@ -10095,7 +10154,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="18.75" customHeight="1">
+    <row r="199" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="7">
         <v>900232301</v>
       </c>
@@ -10106,7 +10165,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="18.75" customHeight="1">
+    <row r="200" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="7">
         <v>830143831</v>
       </c>
@@ -10117,7 +10176,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="18.75" customHeight="1">
+    <row r="201" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="7">
         <v>800099652</v>
       </c>
@@ -10128,7 +10187,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="18.75" customHeight="1">
+    <row r="202" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="7">
         <v>891800570</v>
       </c>
@@ -10139,7 +10198,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="18.75" customHeight="1">
+    <row r="203" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="7">
         <v>892099421</v>
       </c>
@@ -10150,7 +10209,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="18.75" customHeight="1">
+    <row r="204" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="7">
         <v>900438068</v>
       </c>
@@ -10161,7 +10220,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="18.75" customHeight="1">
+    <row r="205" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="7">
         <v>860037950</v>
       </c>
@@ -10172,7 +10231,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="18.75" customHeight="1">
+    <row r="206" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="7">
         <v>890702408</v>
       </c>
@@ -10183,7 +10242,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="18.75" customHeight="1">
+    <row r="207" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="7">
         <v>1015392989</v>
       </c>
@@ -10194,7 +10253,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="18.75" customHeight="1">
+    <row r="208" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="7">
         <v>899999032</v>
       </c>
@@ -10205,7 +10264,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="18.75" customHeight="1">
+    <row r="209" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="7">
         <v>881862576</v>
       </c>
@@ -10216,7 +10275,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="18.75" customHeight="1">
+    <row r="210" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="7">
         <v>52411325</v>
       </c>
@@ -10227,7 +10286,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="18.75" customHeight="1">
+    <row r="211" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="7">
         <v>901544725</v>
       </c>
@@ -10238,7 +10297,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="18.75" customHeight="1">
+    <row r="212" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="7">
         <v>830009112</v>
       </c>
@@ -10249,7 +10308,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="18.75" customHeight="1">
+    <row r="213" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="7">
         <v>900614302</v>
       </c>
@@ -10260,7 +10319,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="18.75" customHeight="1">
+    <row r="214" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="7">
         <v>900055393</v>
       </c>
@@ -10271,7 +10330,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="18.75" customHeight="1">
+    <row r="215" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="7">
         <v>1020720272</v>
       </c>
@@ -10282,7 +10341,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="18.75" customHeight="1">
+    <row r="216" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="7">
         <v>844001355</v>
       </c>
@@ -10293,7 +10352,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="18.75" customHeight="1">
+    <row r="217" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="7">
         <v>801001440</v>
       </c>
@@ -10304,7 +10363,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="18.75" customHeight="1">
+    <row r="218" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="7">
         <v>800037021</v>
       </c>
@@ -10315,7 +10374,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="18.75" customHeight="1">
+    <row r="219" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="7">
         <v>19457462</v>
       </c>
@@ -10326,7 +10385,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="18.75" customHeight="1">
+    <row r="220" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="7">
         <v>890802356</v>
       </c>
@@ -10337,7 +10396,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="18.75" customHeight="1">
+    <row r="221" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="7">
         <v>890801719</v>
       </c>
@@ -10348,7 +10407,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="18.75" customHeight="1">
+    <row r="222" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="7">
         <v>901408039</v>
       </c>
@@ -10359,7 +10418,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="18.75" customHeight="1">
+    <row r="223" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="7">
         <v>860002541</v>
       </c>
@@ -10370,7 +10429,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="18.75" customHeight="1">
+    <row r="224" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="7">
         <v>900342064</v>
       </c>
@@ -10381,7 +10440,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="18.75" customHeight="1">
+    <row r="225" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="7">
         <v>890801035</v>
       </c>
@@ -10392,7 +10451,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="18.75" customHeight="1">
+    <row r="226" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="7">
         <v>802011972</v>
       </c>
@@ -10403,7 +10462,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="18.75" customHeight="1">
+    <row r="227" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="7">
         <v>900407200</v>
       </c>
@@ -10414,7 +10473,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="18.75" customHeight="1">
+    <row r="228" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="7">
         <v>813010145</v>
       </c>
@@ -10425,7 +10484,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="18.75" customHeight="1">
+    <row r="229" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="7">
         <v>860070301</v>
       </c>
@@ -10436,7 +10495,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="18.75" customHeight="1">
+    <row r="230" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="7">
         <v>890700666</v>
       </c>
@@ -10447,7 +10506,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="18.75" customHeight="1">
+    <row r="231" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="7">
         <v>900308007</v>
       </c>
@@ -10458,7 +10517,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="18.75" customHeight="1">
+    <row r="232" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="7">
         <v>891856372</v>
       </c>
@@ -10469,7 +10528,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="18.75" customHeight="1">
+    <row r="233" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="7">
         <v>800065396</v>
       </c>
@@ -10480,7 +10539,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="18.75" customHeight="1">
+    <row r="234" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="7">
         <v>901223046</v>
       </c>
@@ -10491,7 +10550,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="18.75" customHeight="1">
+    <row r="235" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="7">
         <v>809010402</v>
       </c>
@@ -10502,7 +10561,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="18.75" customHeight="1">
+    <row r="236" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="7">
         <v>891800231</v>
       </c>
@@ -10513,7 +10572,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="18.75" customHeight="1">
+    <row r="237" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="7">
         <v>800119574</v>
       </c>
@@ -10524,7 +10583,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="18.75" customHeight="1">
+    <row r="238" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="7">
         <v>80170827</v>
       </c>
@@ -10535,7 +10594,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="18.75" customHeight="1">
+    <row r="239" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="7">
         <v>10286175</v>
       </c>
@@ -10546,7 +10605,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="18.75" customHeight="1">
+    <row r="240" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="7">
         <v>900454188</v>
       </c>
@@ -10557,7 +10616,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="18.75" customHeight="1">
+    <row r="241" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="7">
         <v>900057926</v>
       </c>
@@ -10568,7 +10627,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="18.75" customHeight="1">
+    <row r="242" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="7">
         <v>844001911</v>
       </c>
@@ -10579,7 +10638,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="18.75" customHeight="1">
+    <row r="243" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="7">
         <v>900526144</v>
       </c>
@@ -10590,7 +10649,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="18.75" customHeight="1">
+    <row r="244" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="7">
         <v>900828394</v>
       </c>
@@ -10601,7 +10660,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="18.75" customHeight="1">
+    <row r="245" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="7">
         <v>844001287</v>
       </c>
@@ -10612,7 +10671,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="18.75" customHeight="1">
+    <row r="246" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="7">
         <v>900431131</v>
       </c>
@@ -10623,7 +10682,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="18.75" customHeight="1">
+    <row r="247" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="7">
         <v>800037979</v>
       </c>
@@ -10634,7 +10693,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="18.75" customHeight="1">
+    <row r="248" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="7">
         <v>890601210</v>
       </c>
@@ -10645,7 +10704,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="18.75" customHeight="1">
+    <row r="249" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="7">
         <v>801001969</v>
       </c>
@@ -10656,7 +10715,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="18.75" customHeight="1">
+    <row r="250" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="7">
         <v>890801944</v>
       </c>
@@ -10667,7 +10726,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="18.75" customHeight="1">
+    <row r="251" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="7">
         <v>19419315</v>
       </c>
@@ -10678,7 +10737,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="18.75" customHeight="1">
+    <row r="252" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="7">
         <v>900371613</v>
       </c>
@@ -10689,7 +10748,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="18.75" customHeight="1">
+    <row r="253" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="7">
         <v>860015905</v>
       </c>
@@ -10700,7 +10759,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="18.75" customHeight="1">
+    <row r="254" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="7">
         <v>900488920</v>
       </c>
@@ -10711,7 +10770,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="18.75" customHeight="1">
+    <row r="255" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="7">
         <v>810000913</v>
       </c>
@@ -10722,7 +10781,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="18.75" customHeight="1">
+    <row r="256" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="7">
         <v>900471504</v>
       </c>
@@ -10733,7 +10792,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="18.75" customHeight="1">
+    <row r="257" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="7">
         <v>844003225</v>
       </c>
@@ -10744,7 +10803,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="18.75" customHeight="1">
+    <row r="258" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="7">
         <v>830075393</v>
       </c>
@@ -10755,7 +10814,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="18.75" customHeight="1">
+    <row r="259" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="7">
         <v>900058218</v>
       </c>
@@ -10766,7 +10825,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="18.75" customHeight="1">
+    <row r="260" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="7">
         <v>901295822</v>
       </c>
@@ -10777,7 +10836,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="18.75" customHeight="1">
+    <row r="261" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>900381555</v>
       </c>
@@ -10788,7 +10847,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="18.75" customHeight="1">
+    <row r="262" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="7">
         <v>830117846</v>
       </c>
@@ -10799,7 +10858,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="18.75" customHeight="1">
+    <row r="263" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="7">
         <v>901017982</v>
       </c>
@@ -10810,7 +10869,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="18.75" customHeight="1">
+    <row r="264" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>900314301</v>
       </c>
@@ -10821,7 +10880,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="18.75" customHeight="1">
+    <row r="265" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>901881050</v>
       </c>
@@ -10832,7 +10891,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="18.75" customHeight="1">
+    <row r="266" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>891180134</v>
       </c>
@@ -10843,7 +10902,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="18.75" customHeight="1">
+    <row r="267" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="7">
         <v>900407111</v>
       </c>
@@ -10854,7 +10913,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="18.75" customHeight="1">
+    <row r="268" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>900112820</v>
       </c>
@@ -10865,7 +10924,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="18.75" customHeight="1">
+    <row r="269" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="7">
         <v>901169422</v>
       </c>
@@ -10876,7 +10935,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="18.75" customHeight="1">
+    <row r="270" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>900108793</v>
       </c>
@@ -10887,7 +10946,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="18.75" customHeight="1">
+    <row r="271" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="7">
         <v>900576170</v>
       </c>
@@ -10898,7 +10957,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="18.75" customHeight="1">
+    <row r="272" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>891180268</v>
       </c>
@@ -10909,7 +10968,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="18.75" customHeight="1">
+    <row r="273" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="7">
         <v>900678145</v>
       </c>
@@ -10920,7 +10979,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="18.75" customHeight="1">
+    <row r="274" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="7">
         <v>900627725</v>
       </c>
@@ -10931,7 +10990,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="18.75" customHeight="1">
+    <row r="275" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="7">
         <v>891411743</v>
       </c>
@@ -10942,7 +11001,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="18.75" customHeight="1">
+    <row r="276" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="7">
         <v>900077520</v>
       </c>
@@ -10953,7 +11012,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="18.75" customHeight="1">
+    <row r="277" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>900958564</v>
       </c>
@@ -10964,7 +11023,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="18.75" customHeight="1">
+    <row r="278" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="7">
         <v>800200789</v>
       </c>
@@ -10975,7 +11034,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="18.75" customHeight="1">
+    <row r="279" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="7">
         <v>900061048</v>
       </c>
@@ -10986,7 +11045,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="18.75" customHeight="1">
+    <row r="280" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="7">
         <v>901127904</v>
       </c>
@@ -10997,7 +11056,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="18.75" customHeight="1">
+    <row r="281" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="7">
         <v>890801562</v>
       </c>
@@ -11008,7 +11067,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="18.75" customHeight="1">
+    <row r="282" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4">
         <v>80055710</v>
       </c>
@@ -11019,7 +11078,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="18.75" customHeight="1">
+    <row r="283" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="7">
         <v>79442674</v>
       </c>
@@ -11030,7 +11089,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="18.75" customHeight="1">
+    <row r="284" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4">
         <v>891856507</v>
       </c>
@@ -11041,7 +11100,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="18.75" customHeight="1">
+    <row r="285" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="7">
         <v>900231829</v>
       </c>
@@ -11052,7 +11111,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="18.75" customHeight="1">
+    <row r="286" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="7">
         <v>900171988</v>
       </c>
@@ -11063,7 +11122,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="18.75" customHeight="1">
+    <row r="287" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="7">
         <v>891180098</v>
       </c>
@@ -11074,7 +11133,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="18.75" customHeight="1">
+    <row r="288" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="7">
         <v>845000038</v>
       </c>
@@ -11085,7 +11144,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="18.75" customHeight="1">
+    <row r="289" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4">
         <v>900817788</v>
       </c>
@@ -11096,7 +11155,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="18.75" customHeight="1">
+    <row r="290" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4">
         <v>899999147</v>
       </c>
@@ -11107,7 +11166,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="18.75" customHeight="1">
+    <row r="291" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4">
         <v>900419180</v>
       </c>
@@ -11118,7 +11177,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="18.75" customHeight="1">
+    <row r="292" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="7">
         <v>830119200</v>
       </c>
@@ -11129,7 +11188,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="18.75" customHeight="1">
+    <row r="293" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="7">
         <v>890801495</v>
       </c>
@@ -11140,7 +11199,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="18.75" customHeight="1">
+    <row r="294" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4">
         <v>900582598</v>
       </c>
@@ -11151,7 +11210,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="18.75" customHeight="1">
+    <row r="295" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>890802036</v>
       </c>
@@ -11162,7 +11221,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="18.75" customHeight="1">
+    <row r="296" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="7">
         <v>900462440</v>
       </c>
@@ -11173,7 +11232,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="18.75" customHeight="1">
+    <row r="297" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>846000474</v>
       </c>
@@ -11184,7 +11243,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="18.75" customHeight="1">
+    <row r="298" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="7">
         <v>800000118</v>
       </c>
@@ -11195,7 +11254,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="18.75" customHeight="1">
+    <row r="299" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>900211468</v>
       </c>
@@ -11206,7 +11265,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="18.75" customHeight="1">
+    <row r="300" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
         <v>891855438</v>
       </c>
@@ -11217,7 +11276,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="18.75" customHeight="1">
+    <row r="301" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="7">
         <v>19364579</v>
       </c>
@@ -11228,7 +11287,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="18.75" customHeight="1">
+    <row r="302" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="7">
         <v>900004059</v>
       </c>
@@ -11239,7 +11298,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="18.75" customHeight="1">
+    <row r="303" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="7">
         <v>846003357</v>
       </c>
@@ -11250,7 +11309,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="18.75" customHeight="1">
+    <row r="304" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="7">
         <v>901457374</v>
       </c>
@@ -11261,7 +11320,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="18.75" customHeight="1">
+    <row r="305" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>830005028</v>
       </c>
@@ -11272,7 +11331,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="18.75" customHeight="1">
+    <row r="306" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
         <v>900606412</v>
       </c>
@@ -11283,7 +11342,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="18.75" customHeight="1">
+    <row r="307" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="7">
         <v>830113849</v>
       </c>
@@ -11294,7 +11353,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="18.75" customHeight="1">
+    <row r="308" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
         <v>900232628</v>
       </c>
@@ -11305,7 +11364,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="18.75" customHeight="1">
+    <row r="309" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="7">
         <v>890706823</v>
       </c>
@@ -11316,7 +11375,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="18.75" customHeight="1">
+    <row r="310" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="7">
         <v>901105417</v>
       </c>
@@ -11327,7 +11386,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="18.75" customHeight="1">
+    <row r="311" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="7">
         <v>800037202</v>
       </c>
@@ -11338,7 +11397,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="18.75" customHeight="1">
+    <row r="312" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="7">
         <v>80412859</v>
       </c>
@@ -11349,7 +11408,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="18.75" customHeight="1">
+    <row r="313" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="15">
         <v>800180553</v>
       </c>
@@ -11360,7 +11419,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="18.75" customHeight="1">
+    <row r="314" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="7">
         <v>891411381</v>
       </c>
@@ -11371,7 +11430,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="18.75" customHeight="1">
+    <row r="315" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="7">
         <v>814003448</v>
       </c>
@@ -11382,7 +11441,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="18.75" customHeight="1">
+    <row r="316" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="7">
         <v>891180026</v>
       </c>
@@ -11393,7 +11452,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="18.75" customHeight="1">
+    <row r="317" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="7">
         <v>900233110</v>
       </c>
@@ -11404,7 +11463,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="18.75" customHeight="1">
+    <row r="318" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="7">
         <v>860013570</v>
       </c>
@@ -11415,7 +11474,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="18.75" customHeight="1">
+    <row r="319" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="7">
         <v>901652147</v>
       </c>
@@ -11426,7 +11485,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="18.75" customHeight="1">
+    <row r="320" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="7">
         <v>901439163</v>
       </c>
@@ -11437,7 +11496,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="18.75" customHeight="1">
+    <row r="321" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="7">
         <v>822000946</v>
       </c>
@@ -11448,7 +11507,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="18.75" customHeight="1">
+    <row r="322" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="7">
         <v>810001466</v>
       </c>
@@ -11459,7 +11518,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="18.75" customHeight="1">
+    <row r="323" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="7">
         <v>900547903</v>
       </c>
@@ -11470,7 +11529,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="18.75" customHeight="1">
+    <row r="324" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="7">
         <v>800228215</v>
       </c>
@@ -11481,7 +11540,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="18.75" customHeight="1">
+    <row r="325" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="7">
         <v>890802978</v>
       </c>
@@ -11492,7 +11551,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="18.75" customHeight="1">
+    <row r="326" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="7">
         <v>800135582</v>
       </c>
@@ -11503,7 +11562,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="18.75" customHeight="1">
+    <row r="327" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="7">
         <v>900364721</v>
       </c>
@@ -11514,7 +11573,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="18.75" customHeight="1">
+    <row r="328" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="7">
         <v>899999123</v>
       </c>
@@ -11525,7 +11584,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="18.75" customHeight="1">
+    <row r="329" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="7">
         <v>890801099</v>
       </c>
@@ -11536,7 +11595,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="18.75" customHeight="1">
+    <row r="330" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="7">
         <v>830018305</v>
       </c>
@@ -11547,7 +11606,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="18.75" customHeight="1">
+    <row r="331" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="7">
         <v>809001482</v>
       </c>
@@ -11558,7 +11617,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="18.75" customHeight="1">
+    <row r="332" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="7">
         <v>900685235</v>
       </c>
@@ -11569,7 +11628,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="18.75" customHeight="1">
+    <row r="333" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="7">
         <v>800191101</v>
       </c>
@@ -11580,7 +11639,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="18.75" customHeight="1">
+    <row r="334" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="7">
         <v>891409981</v>
       </c>
@@ -11591,7 +11650,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="18.75" customHeight="1">
+    <row r="335" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="7">
         <v>900073806</v>
       </c>
@@ -11602,7 +11661,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="18.75" customHeight="1">
+    <row r="336" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="7">
         <v>900493064</v>
       </c>
@@ -11613,7 +11672,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="18.75" customHeight="1">
+    <row r="337" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="7">
         <v>800231235</v>
       </c>
@@ -11624,7 +11683,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="18.75" customHeight="1">
+    <row r="338" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="7">
         <v>860007373</v>
       </c>
@@ -11635,7 +11694,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="18.75" customHeight="1">
+    <row r="339" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="7">
         <v>900848340</v>
       </c>
@@ -11646,7 +11705,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="18.75" customHeight="1">
+    <row r="340" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
         <v>900115642</v>
       </c>
@@ -11657,7 +11716,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="18.75" customHeight="1">
+    <row r="341" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="7">
         <v>79533241</v>
       </c>
@@ -11668,7 +11727,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="18.75" customHeight="1">
+    <row r="342" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
         <v>830502282</v>
       </c>
@@ -11679,7 +11738,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="18.75" customHeight="1">
+    <row r="343" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="7">
         <v>900081643</v>
       </c>
@@ -11690,7 +11749,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="18.75" customHeight="1">
+    <row r="344" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="7">
         <v>891855039</v>
       </c>
@@ -11701,7 +11760,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="18.75" customHeight="1">
+    <row r="345" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="7">
         <v>805017681</v>
       </c>
@@ -11712,7 +11771,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="18.75" customHeight="1">
+    <row r="346" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="7">
         <v>820002248</v>
       </c>
@@ -11723,7 +11782,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="18.75" customHeight="1">
+    <row r="347" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="7">
         <v>860024026</v>
       </c>
@@ -11734,7 +11793,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="18.75" customHeight="1">
+    <row r="348" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="7">
         <v>71394225</v>
       </c>
@@ -11745,7 +11804,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="18.75" customHeight="1">
+    <row r="349" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="7">
         <v>832008321</v>
       </c>
@@ -11756,7 +11815,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="18.75" customHeight="1">
+    <row r="350" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="7">
         <v>901632467</v>
       </c>
@@ -11767,7 +11826,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="18.75" customHeight="1">
+    <row r="351" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="7">
         <v>891180117</v>
       </c>
@@ -11778,7 +11837,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="18.75" customHeight="1">
+    <row r="352" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="7">
         <v>900759329</v>
       </c>
@@ -11789,7 +11848,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="18.75" customHeight="1">
+    <row r="353" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="7">
         <v>891800644</v>
       </c>
@@ -11800,7 +11859,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="18.75" customHeight="1">
+    <row r="354" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="4">
         <v>800254132</v>
       </c>
@@ -11811,7 +11870,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="18.75" customHeight="1">
+    <row r="355" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="7">
         <v>899999158</v>
       </c>
@@ -11822,7 +11881,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="18.75" customHeight="1">
+    <row r="356" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="4">
         <v>79624744</v>
       </c>
@@ -11833,7 +11892,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="18.75" customHeight="1">
+    <row r="357" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="7">
         <v>891409390</v>
       </c>
@@ -11844,7 +11903,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="18.75" customHeight="1">
+    <row r="358" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="7">
         <v>890680014</v>
       </c>
@@ -11855,7 +11914,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="18.75" customHeight="1">
+    <row r="359" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="7">
         <v>809006690</v>
       </c>
@@ -11866,7 +11925,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="18.75" customHeight="1">
+    <row r="360" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="7">
         <v>900213617</v>
       </c>
@@ -11877,7 +11936,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="18.75" customHeight="1">
+    <row r="361" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4">
         <v>900423816</v>
       </c>
@@ -11888,7 +11947,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="18.75" customHeight="1">
+    <row r="362" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4">
         <v>860015929</v>
       </c>
@@ -11899,7 +11958,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="18.75" customHeight="1">
+    <row r="363" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4">
         <v>890806490</v>
       </c>
@@ -11910,7 +11969,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="18.75" customHeight="1">
+    <row r="364" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4">
         <v>860006626</v>
       </c>
@@ -11921,7 +11980,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="18.75" customHeight="1">
+    <row r="365" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4">
         <v>813005295</v>
       </c>
@@ -11932,7 +11991,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="18.75" customHeight="1">
+    <row r="366" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4">
         <v>846001425</v>
       </c>
@@ -11943,7 +12002,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="18.75" customHeight="1">
+    <row r="367" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4">
         <v>800139366</v>
       </c>
@@ -11954,7 +12013,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="18.75" customHeight="1">
+    <row r="368" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4">
         <v>816005003</v>
       </c>
@@ -11965,7 +12024,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="18.75" customHeight="1">
+    <row r="369" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="4">
         <v>900435790</v>
       </c>
@@ -11976,12 +12035,12 @@
         <v>738</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="18.75" customHeight="1">
+    <row r="370" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="19"/>
       <c r="B370" s="20"/>
       <c r="C370" s="21"/>
     </row>
-    <row r="371" spans="1:3" ht="18.75" customHeight="1">
+    <row r="371" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="19"/>
       <c r="B371" s="20"/>
       <c r="C371" s="21"/>
